--- a/Legacy_Submitter_Outreach_Tracker.xlsx
+++ b/Legacy_Submitter_Outreach_Tracker.xlsx
@@ -2,10 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Submitters" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email Template" sheetId="2" state="visible" r:id="rId2"/>
@@ -18,21 +14,32 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001C1A10"/>
+      <color rgb="FF1C1A10"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,41 +47,46 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5A623"/>
-        <bgColor rgb="00F5A623"/>
+        <fgColor rgb="FFF5A623"/>
+        <bgColor rgb="FFF5A623"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -147,20 +159,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -184,77 +196,19 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -266,166 +220,135 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -435,30 +358,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q103"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11" customWidth="1" style="4" min="2" max="2"/>
+    <col width="13" customWidth="1" style="4" min="3" max="5"/>
+    <col width="12" customWidth="1" style="4" min="6" max="6"/>
+    <col width="28" customWidth="1" style="4" min="7" max="7"/>
+    <col width="34" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="40" customWidth="1" style="4" min="10" max="10"/>
+    <col width="36" customWidth="1" style="4" min="11" max="11"/>
+    <col width="44" customWidth="1" style="4" min="12" max="12"/>
+    <col width="50" customWidth="1" style="4" min="13" max="13"/>
+    <col width="20" customWidth="1" style="4" min="14" max="14"/>
+    <col width="19.29" customWidth="1" style="4" min="15" max="15"/>
+    <col width="13" customWidth="1" style="4" min="16" max="17"/>
+    <col width="40" customWidth="1" style="4" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" style="4" min="19" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="4">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -531,20 +452,15 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Planned Send Date</t>
+          <t>Date Emailed/Scheduled</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Date Emailed</t>
+          <t>Follow-up Date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Follow-up Date</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -569,8 +485,8 @@
           <t>2015-03-15</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Falcobloemendal@gmail.com</t>
@@ -581,7 +497,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>16 hive(s) logged 2015-03-14 to 2015-03-15 — location not recorded</t>
@@ -607,10 +523,9 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -681,14 +596,13 @@
           <t>No Longer Pursuing</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Email bounced 2026-07-31 (cox.net address dead). Phone (757-651-6543) also confirmed dead — Ronnie tried it, no good. No other contact info found via web search. Dead end for now; revisit only if a better lead on him ever turns up (e.g. through a local NC/VA beekeeping group).</t>
         </is>
@@ -760,13 +674,18 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -834,15 +753,16 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>Email recovered (high confidence) — was truncated to "coastalnet.".</t>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>46246</v>
+      </c>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Email recovered (high confidence) — was truncated to "coastalnet.". Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times). Bounced (Aug 12) — "address not found," coastalnet address (x8x8p2gb@coastalnet.com) could not receive mail.</t>
         </is>
       </c>
     </row>
@@ -912,13 +832,18 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times). Bounced (Aug 11) — "address not found," coatesdd@yahoo.com could not receive mail.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -986,15 +911,16 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Email recovered (high confidence) — was truncated to "yaho".</t>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Email recovered (high confidence) — was truncated to "yaho". Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times). Bounced (Aug 11) — "address not found," Davidabeemaster@yahoo.com could not receive mail.</t>
         </is>
       </c>
     </row>
@@ -1017,8 +943,8 @@
           <t>2015-05-23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>amirbay@hotmail.com</t>
@@ -1029,7 +955,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>6 hive(s) logged 2015-05-23 to 2015-05-23 — location not recorded</t>
@@ -1052,13 +978,18 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1126,13 +1057,18 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), Sent Aug 11, 2026, 9:25 AM.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1200,15 +1136,16 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>Email recovered (high confidence) — was truncated to "juno.".</t>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Email recovered (high confidence) — was truncated to "juno.". Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), Sent Aug 11, 2026, 9:27 AM (this one had been scheduled but fired before this update).</t>
         </is>
       </c>
     </row>
@@ -1281,10 +1218,9 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Same Debbie Delaney already in University_Bee_Research_Contacts.xlsx (Univ. of Delaware, worked with Dr. Tarpy) — do NOT send a duplicate cold outreach email; coordinate with that existing thread instead.</t>
         </is>
@@ -1309,8 +1245,8 @@
           <t>2013-05-15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Cisco.dog@icloud.com</t>
@@ -1321,7 +1257,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>5 hive(s) logged 2013-04-30 to 2013-05-15 — location not recorded</t>
@@ -1344,13 +1280,18 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1421,10 +1362,9 @@
           <t>Emailed</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>Ronnie confirmed correct current email (glennapiaries@gmail.com) — doing notable genetic research on wild colonies. High-priority contact.</t>
         </is>
@@ -1499,10 +1439,9 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>Web research: runs Thompson Valley Bee Farm in Tazewell, VA (bee sanctuary + mentoring + swarm removal). Stored email was truncated before the @ symbol, so no email is recoverable from this data. Best contact paths found: Facebook facebook.com/ThompsonValleyBeeFarm, LinkedIn linkedin.com/in/billiray-armstrong-657365117, or phone (276) 979-7391 (found via web search — note this differs slightly from the phone on file, 276-988-2099; try both). Email unrecoverable — truncated before @, domain lost entirely.</t>
         </is>
@@ -1527,8 +1466,8 @@
           <t>2014-05-05</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Bigpock@gmail.com</t>
@@ -1539,7 +1478,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>4 hive(s) logged 2013-07-08 to 2014-05-05 — location not recorded</t>
@@ -1562,13 +1501,18 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), Sent Aug 11, 2026, 8:36 AM.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1636,15 +1580,16 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>Email recovered (high confidence) — was truncated to "gmail.c".</t>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Email recovered (high confidence) — was truncated to "gmail.c". Draft created in Gmail 2026-08-10 (trimmed template, no [PERSONAL NOTE], all hive links included), now Scheduled to send via Gmail scheduled-send (queued 2026-08-11, going out over the next ~3 days at randomized times).</t>
         </is>
       </c>
     </row>
@@ -1667,8 +1612,8 @@
           <t>2016-05-24</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Claylia@me.com</t>
@@ -1679,7 +1624,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>4 hive(s) logged 2012-08-21 to 2016-05-24 — location not recorded</t>
@@ -1702,13 +1647,18 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
+          <t>Emailed - Replied</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included). Update 2026-08-14: Ronnie used that draft as a starting point, personalized it, and sent it himself directly to Clay (they're old high-school friends) using both Claylia@me.com and cheilman@naturevision.org — confirmed cheilman@naturevision.org is a valid second address for him. Replied Aug 18: hot lead — a feral hive active ~20 years in a barn wall on the Snoqualmie River, WA, and suspects more nearby. Had trouble with the magic-link login (found it in spam, retrying). Follow up to confirm he got logged in and to encourage the river-wide search. UPDATE Aug 22: reply sent. Clay has since logged 2-3 new hives plus updated 2-3 existing ones on the map — one of the most engaged legacy submitters so far. She mentioned being affiliated with a foundation (her old/bounced address was cheilman@naturevision.org) — Ronnie flagged a possible future joint effort with Clay and that foundation; nothing concrete yet, just a back-pocket idea worth revisiting once the Snoqualmie River hive search develops.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1779,10 +1729,13 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1823,7 +1776,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4 hive(s) logged 2008-06-28 to 2012-08-02 — NC</t>
@@ -1846,13 +1799,16 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+          <t>Emailed - Replied</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Replied Aug 18: Franklinton hive likely gone (tree removed); unsure on Chattooga River one; will check the two near Richlands "in a few weeks." No longer keeps bees himself but kept equipment.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1920,15 +1876,18 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Bounced Aug 18 — "address not found," melliphile@yahoo.com could not receive mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="4">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Patrick Schlemmer</t>
@@ -1994,19 +1953,18 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Email recovered (high confidence) — was truncated to "earthlink.ne".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>Emailed - Replied</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Email recovered (high confidence) — was truncated to "earthlink.ne". Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Replied Aug 19: went in and validated a couple of his hives himself (no further action needed — informational).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="4">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Richard Stewart</t>
@@ -2072,19 +2030,18 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>Email recovered (high confidence) — was truncated to "zoomtown.co".</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Email recovered (high confidence) — was truncated to "zoomtown.co". Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Bounced Aug 19 — "address not found," rstewart@zoomtown.com could not receive mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="4">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Sean Williams</t>
@@ -2103,8 +2060,8 @@
           <t>2014-07-07</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>sean@trebron.com</t>
@@ -2115,7 +2072,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>4 hive(s) logged 2014-04-22 to 2014-07-07 — location not recorded</t>
@@ -2138,15 +2095,18 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Bounced Aug 17 — "address not found," sean@trebron.com could not receive mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="4">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Tim Grissom</t>
@@ -2165,8 +2125,8 @@
           <t>2014-02-26</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Travel@ctcn.net</t>
@@ -2177,7 +2137,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>4 hive(s) logged 2013-01-20 to 2014-02-26 — location not recorded</t>
@@ -2200,15 +2160,18 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Bounced Aug 14 — "address not found," travel@ctcn.net could not receive mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="4">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Andrew Thiessen</t>
@@ -2227,8 +2190,8 @@
           <t>2015-01-23</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>andthi30@hotmail.com</t>
@@ -2239,7 +2202,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2013-09-03 to 2015-01-23 — location not recorded</t>
@@ -2265,12 +2228,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="4">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Anna Brown</t>
@@ -2336,15 +2302,18 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
+          <t>Emailed - Replied</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent. Replied Aug 18: moved away from Charlotte area (now near Charlottesville), but confirmed the oak-tree hive (hive 970) held strong 2014-2018. Informational, no reply needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="4">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Bart Kruijt</t>
@@ -2363,8 +2332,8 @@
           <t>2012-09-23</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Info@debijendans.nl</t>
@@ -2375,7 +2344,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2012-09-20 to 2012-09-23 — location not recorded</t>
@@ -2401,12 +2370,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="4">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Bo Sterk</t>
@@ -2475,16 +2443,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "ymail.co".</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1" s="4">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Bryan Zublin</t>
@@ -2553,12 +2520,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="4">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Chad P.</t>
@@ -2597,7 +2563,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2010-05-08 to 2012-08-02 — Chattanooga, Hixson, RED BANK</t>
@@ -2623,12 +2589,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="4">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Christopher Rodesch</t>
@@ -2647,8 +2612,8 @@
           <t>2012-11-26</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>chrisrodesch@hotmail.com</t>
@@ -2659,7 +2624,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2012-11-26 to 2012-11-26 — location not recorded</t>
@@ -2685,12 +2650,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="4">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Colleen Kendrick</t>
@@ -2759,16 +2723,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>Phone field contains stray text "owner's name is Kevi..." (truncated) — hive may have been reported on someone else's behalf. Verify before addressing email. Email recovered (high confidence) — was truncated to "hotma".</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1" s="4">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Dan Brehmer</t>
@@ -2837,12 +2800,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="4">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Dawn Cassello</t>
@@ -2861,8 +2823,8 @@
           <t>2014-06-12</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>ngapiary@gmail.com</t>
@@ -2873,7 +2835,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2013-08-01 to 2014-06-12 — location not recorded</t>
@@ -2899,12 +2861,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="4">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Desiree Kuri</t>
@@ -2973,12 +2934,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="4">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Donna Wilson</t>
@@ -2997,8 +2957,8 @@
           <t>2012-11-19</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>dnn_crump@yahoo.com</t>
@@ -3009,7 +2969,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2012-11-19 to 2012-11-19 — location not recorded</t>
@@ -3035,12 +2995,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="4">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Jasper Stepp</t>
@@ -3059,8 +3018,8 @@
           <t>2014-04-04</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Jasperstepp@gmail.com</t>
@@ -3071,7 +3030,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2014-03-11 to 2014-04-04 — location not recorded</t>
@@ -3097,12 +3056,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="4">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Jimmy Chalmers</t>
@@ -3171,16 +3129,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "yahoo.co".</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1" s="4">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>John Bibb</t>
@@ -3249,12 +3206,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="4">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>John Miles</t>
@@ -3323,16 +3279,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>Email recovered (medium confidence) — was truncated to "windst".</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1" s="4">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Megan Martin</t>
@@ -3401,12 +3356,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="4">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Michael Shantz</t>
@@ -3475,16 +3429,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "sbcglo".</t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1" s="4">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Phoenix Tuttle</t>
@@ -3553,16 +3506,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "gm".</t>
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1" s="4">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Scott Conley</t>
@@ -3631,12 +3583,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="4">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sean Lee</t>
@@ -3705,12 +3656,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="4">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Will White</t>
@@ -3779,12 +3729,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="4">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Zachary Lewellyn</t>
@@ -3803,8 +3752,8 @@
           <t>2013-05-30</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>flewy123@gmail.com</t>
@@ -3815,7 +3764,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
           <t>3 hive(s) logged 2013-05-30 to 2013-05-30 — location not recorded</t>
@@ -3841,12 +3790,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" s="4">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Andrew Marani</t>
@@ -3915,16 +3863,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>Web-confirmed: Andrew Marani co-owns A.R. Marani, Inc. (armarani.com) in Baltimore, MD — beekeeping is a personal hobby alongside the business. Try this business email; if it bounces, Baltimore Backyard Beekeepers Network or Central Maryland Beekeepers Association may know him. Email recovered (high confidence, web-confirmed) — matches A.R. Marani, Inc., his Baltimore construction business domain.</t>
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1" s="4">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>B. Keeper</t>
@@ -3943,8 +3890,8 @@
           <t>2013-06-12</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>jzawislak@uaex.edu</t>
@@ -3955,7 +3902,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="n"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-06-12 to 2013-06-12 — location not recorded</t>
@@ -3981,16 +3928,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>Name looks like a placeholder/pun ("B. Keeper"), but email domain is a real .edu (University of Arkansas Extension) — verify identity before sending.</t>
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1" s="4">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Beverly Knapp</t>
@@ -4009,8 +3955,8 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Bmargknapp@comcast.net</t>
@@ -4021,7 +3967,7 @@
           <t>recovered (medium confidence) — was truncated to "concast.net"</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2012-09-11 to 2012-09-11 — location not recorded</t>
@@ -4047,16 +3993,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>Email recovered (medium confidence) — was truncated to "concast.net".</t>
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1" s="4">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Bill Whitson</t>
@@ -4125,16 +4070,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "gmail.co".</t>
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1" s="4">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Bob Kemper</t>
@@ -4203,16 +4147,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "bellsouth.ne".</t>
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1" s="4">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Bob Williams</t>
@@ -4281,12 +4224,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
+      <c r="Q53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="4">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Bonnie McLaughlin</t>
@@ -4305,8 +4247,8 @@
           <t>2016-10-30</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Bcrent48@rtci.net</t>
@@ -4317,7 +4259,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2015-11-17 to 2016-10-30 — location not recorded</t>
@@ -4343,12 +4285,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" s="4">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Bruce Bell</t>
@@ -4417,12 +4358,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="4">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Cameron Barth</t>
@@ -4491,12 +4431,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="4">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Carie Hett</t>
@@ -4565,12 +4504,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="4">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Chip Braswell</t>
@@ -4639,16 +4577,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "hotma".</t>
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1" s="4">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Christina Teague</t>
@@ -4717,16 +4654,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="inlineStr"/>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="n"/>
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "hotmai".</t>
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1" s="4">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Claes Dahlgren</t>
@@ -4745,8 +4681,8 @@
           <t>2013-07-05</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Claes_dahlgren@hotmail.com</t>
@@ -4757,7 +4693,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="n"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-07-05 to 2013-07-05 — location not recorded</t>
@@ -4783,12 +4719,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" s="4">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>David Wagner</t>
@@ -4827,7 +4762,7 @@
           <t>recovered (low confidence) — was truncated to "outdrs."</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2008-07-23 to 2012-08-02 — Beebe</t>
@@ -4853,16 +4788,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>Email recovered (low confidence) — was truncated to "outdrs.".</t>
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1" s="4">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>David Wright</t>
@@ -4931,12 +4865,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
+      <c r="O62" s="2" t="n"/>
+      <c r="P62" s="2" t="n"/>
+      <c r="Q62" s="2" t="n"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="4">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Debora White</t>
@@ -5005,16 +4938,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>Email recovered (low confidence) — was truncated to "whitebe".</t>
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1" s="4">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Debra Goerger</t>
@@ -5083,16 +5015,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr"/>
-      <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "comcast.".</t>
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1" s="4">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Develon Puckett</t>
@@ -5161,12 +5092,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O65" s="2" t="inlineStr"/>
-      <c r="P65" s="2" t="inlineStr"/>
-      <c r="Q65" s="2" t="inlineStr"/>
-      <c r="R65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="n"/>
+      <c r="Q65" s="2" t="n"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="4">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Donald Shrader</t>
@@ -5235,12 +5165,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr"/>
-      <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" s="4">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Donnie Smith</t>
@@ -5259,8 +5188,8 @@
           <t>2013-01-25</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>dcsmith@centurylink.net</t>
@@ -5271,7 +5200,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="n"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-01-25 to 2013-01-25 — location not recorded</t>
@@ -5297,12 +5226,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
-      <c r="R67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
+      <c r="Q67" s="2" t="n"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" s="4">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Elizabeth Cummings</t>
@@ -5371,12 +5299,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="n"/>
+      <c r="Q68" s="2" t="n"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" s="4">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Erin Forbes</t>
@@ -5445,16 +5372,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n"/>
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>Web-confirmed: Erin Forbes is an EAS Certified Master Beekeeper running Overland Apiaries (overlandhoney.com) in Portland, ME — ~70 hives in Cumberland County. Great candidate, very active in the community. Email recovered (high confidence, web-confirmed) — matches Overland Apiaries/Overland Honey, her real beekeeping business in Portland, ME.</t>
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1" s="4">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Fred Wark</t>
@@ -5523,12 +5449,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
+      <c r="O70" s="2" t="n"/>
+      <c r="P70" s="2" t="n"/>
+      <c r="Q70" s="2" t="n"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" s="4">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Greg Swob</t>
@@ -5597,12 +5522,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
+      <c r="Q71" s="2" t="n"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" s="4">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Gus Ose</t>
@@ -5671,12 +5595,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
+      <c r="Q72" s="2" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="4">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Imkerei Fremuth</t>
@@ -5695,8 +5618,8 @@
           <t>2012-12-13</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>imkerei@fremuth.net</t>
@@ -5707,7 +5630,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="n"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2012-12-08 to 2012-12-13 — location not recorded</t>
@@ -5733,16 +5656,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr">
+      <c r="O73" s="2" t="n"/>
+      <c r="P73" s="2" t="n"/>
+      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>German for 'apiary' — email domain (fremuth.net) matches Wolfgang Fremuth's entry below; likely the same family/operation. Consider one combined outreach instead of two.</t>
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1" s="4">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Jeff Britts</t>
@@ -5761,8 +5683,8 @@
           <t>2012-10-09</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>sweetacreshoney@gmail.com</t>
@@ -5773,7 +5695,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="n"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2012-10-09 to 2012-10-09 — location not recorded</t>
@@ -5799,12 +5721,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
+      <c r="O74" s="2" t="n"/>
+      <c r="P74" s="2" t="n"/>
+      <c r="Q74" s="2" t="n"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="4">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Jimmy Watson</t>
@@ -5843,7 +5764,7 @@
           <t>recovered (high confidence) — was truncated to "yahoo."</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="n"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2008-06-28 to 2012-08-02 — NC</t>
@@ -5869,16 +5790,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="inlineStr"/>
-      <c r="Q75" s="2" t="inlineStr"/>
-      <c r="R75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="n"/>
+      <c r="P75" s="2" t="n"/>
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "yahoo.".</t>
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1" s="4">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>John Bishop</t>
@@ -5947,16 +5867,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="n"/>
+      <c r="P76" s="2" t="n"/>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "twcny.rr.co".</t>
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1" s="4">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>KEITH WHITFIELD</t>
@@ -5995,7 +5914,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="n"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2008-06-28 to 2008-06-28 — NC</t>
@@ -6021,12 +5940,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="2" t="inlineStr"/>
-      <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
+      <c r="O77" s="2" t="n"/>
+      <c r="P77" s="2" t="n"/>
+      <c r="Q77" s="2" t="n"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" s="4">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Kevin Hansen</t>
@@ -6095,12 +6013,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
+      <c r="Q78" s="2" t="n"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="4">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Kristen Yoder</t>
@@ -6169,16 +6086,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="2" t="inlineStr">
+      <c r="O79" s="2" t="n"/>
+      <c r="P79" s="2" t="n"/>
+      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "sbcglo".</t>
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1" s="4">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Larry Edwards</t>
@@ -6247,16 +6163,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
-      <c r="R80" s="2" t="inlineStr">
+      <c r="O80" s="2" t="n"/>
+      <c r="P80" s="2" t="n"/>
+      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "earthlink.".</t>
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1" s="4">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Larry Harwood</t>
@@ -6325,16 +6240,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" s="2" t="inlineStr"/>
-      <c r="Q81" s="2" t="inlineStr"/>
-      <c r="R81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="n"/>
+      <c r="P81" s="2" t="n"/>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "gmail.".</t>
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1" s="4">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Maria Vadeboncoeur</t>
@@ -6353,8 +6267,8 @@
           <t>2013-01-21</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>mgv54@mac.com</t>
@@ -6365,7 +6279,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="n"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-01-21 to 2013-01-21 — location not recorded</t>
@@ -6391,12 +6305,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="inlineStr"/>
-      <c r="Q82" s="2" t="inlineStr"/>
-      <c r="R82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="n"/>
+      <c r="Q82" s="2" t="n"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="4">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Matthew Wills</t>
@@ -6465,16 +6378,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr"/>
-      <c r="P83" s="2" t="inlineStr"/>
-      <c r="Q83" s="2" t="inlineStr"/>
-      <c r="R83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="n"/>
+      <c r="P83" s="2" t="n"/>
+      <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "earthli".</t>
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1" s="4">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Michael Parker</t>
@@ -6493,8 +6405,8 @@
           <t>2013-01-24</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>honeeproducer@yahoo.com</t>
@@ -6505,7 +6417,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="n"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-01-24 to 2013-01-24 — location not recorded</t>
@@ -6531,12 +6443,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
-      <c r="R84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="n"/>
+      <c r="Q84" s="2" t="n"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="4">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Michael Thompson</t>
@@ -6555,8 +6466,8 @@
           <t>2013-04-21</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Mike@expmortgage.com</t>
@@ -6567,7 +6478,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="n"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2012-09-15 to 2013-04-21 — location not recorded</t>
@@ -6593,12 +6504,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="inlineStr"/>
-      <c r="Q85" s="2" t="inlineStr"/>
-      <c r="R85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
+      <c r="O85" s="2" t="n"/>
+      <c r="P85" s="2" t="n"/>
+      <c r="Q85" s="2" t="n"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="4">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Michele Mitchell</t>
@@ -6617,8 +6527,8 @@
           <t>2013-06-11</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Michelebm@verizon.net</t>
@@ -6629,7 +6539,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="n"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-06-11 to 2013-06-11 — location not recorded</t>
@@ -6655,12 +6565,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr"/>
-      <c r="R86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
+      <c r="O86" s="2" t="n"/>
+      <c r="P86" s="2" t="n"/>
+      <c r="Q86" s="2" t="n"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="4">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Richard Gunderman</t>
@@ -6729,12 +6638,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" s="2" t="inlineStr"/>
-      <c r="R87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
+      <c r="O87" s="2" t="n"/>
+      <c r="P87" s="2" t="n"/>
+      <c r="Q87" s="2" t="n"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1" s="4">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Richard Schmauss</t>
@@ -6753,8 +6661,8 @@
           <t>2015-07-04</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>richardschmauss@mac.com</t>
@@ -6765,7 +6673,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="n"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2014-06-08 to 2015-07-04 — location not recorded</t>
@@ -6791,12 +6699,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" s="2" t="inlineStr"/>
-      <c r="R88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="n"/>
+      <c r="Q88" s="2" t="n"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1" s="4">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Rick Bordeaux</t>
@@ -6865,16 +6772,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" s="2" t="inlineStr"/>
-      <c r="R89" s="2" t="inlineStr">
+      <c r="O89" s="2" t="n"/>
+      <c r="P89" s="2" t="n"/>
+      <c r="Q89" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "bellsou".</t>
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1" s="4">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Rob Crook</t>
@@ -6943,16 +6849,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" s="2" t="inlineStr"/>
-      <c r="R90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="2" t="n"/>
+      <c r="Q90" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "bellsout".</t>
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1" s="4">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Rob Donaldson</t>
@@ -6971,8 +6876,8 @@
           <t>2016-03-10</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Robdonaldson@live.com</t>
@@ -6983,7 +6888,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="n"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2016-03-10 to 2016-03-10 — location not recorded</t>
@@ -7009,12 +6914,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr"/>
-      <c r="P91" s="2" t="inlineStr"/>
-      <c r="Q91" s="2" t="inlineStr"/>
-      <c r="R91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
+      <c r="O91" s="2" t="n"/>
+      <c r="P91" s="2" t="n"/>
+      <c r="Q91" s="2" t="n"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1" s="4">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Russ Gibson</t>
@@ -7033,8 +6937,8 @@
           <t>2013-07-25</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>casvallbees@hotmail.com</t>
@@ -7045,7 +6949,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="n"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-07-25 to 2013-07-25 — location not recorded</t>
@@ -7071,12 +6975,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
+      <c r="O92" s="2" t="n"/>
+      <c r="P92" s="2" t="n"/>
+      <c r="Q92" s="2" t="n"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1" s="4">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Scott Martin</t>
@@ -7145,12 +7048,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr"/>
-      <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="2" t="n"/>
+      <c r="Q93" s="2" t="n"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1" s="4">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Steve Hildebrand</t>
@@ -7219,16 +7121,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="n"/>
+      <c r="P94" s="2" t="n"/>
+      <c r="Q94" s="2" t="inlineStr">
         <is>
           <t>Email recovered (medium confidence) — was truncated to "bel".</t>
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1" s="4">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Steven Ames</t>
@@ -7297,16 +7198,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr">
+      <c r="O95" s="2" t="n"/>
+      <c r="P95" s="2" t="n"/>
+      <c r="Q95" s="2" t="inlineStr">
         <is>
           <t>Email recovered (low confidence) — was truncated to "apisindustri".</t>
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1" s="4">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Susan McAllister</t>
@@ -7375,12 +7275,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
+      <c r="O96" s="2" t="n"/>
+      <c r="P96" s="2" t="n"/>
+      <c r="Q96" s="2" t="n"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1" s="4">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Wolfgang Fremuth</t>
@@ -7399,8 +7298,8 @@
           <t>2014-04-02</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Wolfgang@fremuth.net</t>
@@ -7411,7 +7310,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="n"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-03-10 to 2014-04-02 — location not recorded</t>
@@ -7437,12 +7336,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="inlineStr"/>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
+      <c r="O97" s="2" t="n"/>
+      <c r="P97" s="2" t="n"/>
+      <c r="Q97" s="2" t="n"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1" s="4">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>bob combs</t>
@@ -7471,13 +7369,13 @@
           <t>NC, WA</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="n"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2011-08-23 to 2011-08-23 — NC, WA</t>
@@ -7503,16 +7401,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr">
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
+      <c r="Q98" s="2" t="inlineStr">
         <is>
           <t>Web research: no public beekeeping presence found under this name in NC or WA. Too common a name to disambiguate — no email, no phone on file. Lowest-priority / likely a dead end unless Ronnie recognizes them personally.</t>
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1" s="4">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>jacqueline malantoni</t>
@@ -7531,8 +7428,8 @@
           <t>2016-10-30</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
           <t>motbluehen@aol.com</t>
@@ -7543,7 +7440,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="n"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2016-10-30 to 2016-10-30 — location not recorded</t>
@@ -7569,12 +7466,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
+      <c r="O99" s="2" t="n"/>
+      <c r="P99" s="2" t="n"/>
+      <c r="Q99" s="2" t="n"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1" s="4">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>jesse bowles</t>
@@ -7643,16 +7539,15 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="inlineStr"/>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr">
+      <c r="O100" s="2" t="n"/>
+      <c r="P100" s="2" t="n"/>
+      <c r="Q100" s="2" t="inlineStr">
         <is>
           <t>Email recovered (high confidence) — was truncated to "bellso".</t>
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1" s="4">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>michael mcelroy</t>
@@ -7721,12 +7616,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="inlineStr"/>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
+      <c r="O101" s="2" t="n"/>
+      <c r="P101" s="2" t="n"/>
+      <c r="Q101" s="2" t="n"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1" s="4">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>tim ramey</t>
@@ -7795,12 +7689,11 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="inlineStr"/>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
+      <c r="O102" s="2" t="n"/>
+      <c r="P102" s="2" t="n"/>
+      <c r="Q102" s="2" t="n"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" s="4">
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>tomas mozer</t>
@@ -7819,8 +7712,8 @@
           <t>2013-05-20</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t>tommozer@hotmail.com</t>
@@ -7831,7 +7724,7 @@
           <t>verified (complete)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="n"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>2 hive(s) logged 2013-05-17 to 2013-05-20 — location not recorded</t>
@@ -7857,21 +7750,918 @@
           <t>Not yet contacted</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="inlineStr"/>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
-    </row>
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
+      <c r="Q103" s="2" t="n"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1" s="4"/>
+    <row r="105" ht="15.75" customHeight="1" s="4"/>
+    <row r="106" ht="15.75" customHeight="1" s="4"/>
+    <row r="107" ht="15.75" customHeight="1" s="4"/>
+    <row r="108" ht="15.75" customHeight="1" s="4"/>
+    <row r="109" ht="15.75" customHeight="1" s="4"/>
+    <row r="110" ht="15.75" customHeight="1" s="4"/>
+    <row r="111" ht="15.75" customHeight="1" s="4"/>
+    <row r="112" ht="15.75" customHeight="1" s="4"/>
+    <row r="113" ht="15.75" customHeight="1" s="4"/>
+    <row r="114" ht="15.75" customHeight="1" s="4"/>
+    <row r="115" ht="15.75" customHeight="1" s="4"/>
+    <row r="116" ht="15.75" customHeight="1" s="4"/>
+    <row r="117" ht="15.75" customHeight="1" s="4"/>
+    <row r="118" ht="15.75" customHeight="1" s="4"/>
+    <row r="119" ht="15.75" customHeight="1" s="4"/>
+    <row r="120" ht="15.75" customHeight="1" s="4"/>
+    <row r="121" ht="15.75" customHeight="1" s="4"/>
+    <row r="122" ht="15.75" customHeight="1" s="4"/>
+    <row r="123" ht="15.75" customHeight="1" s="4"/>
+    <row r="124" ht="15.75" customHeight="1" s="4"/>
+    <row r="125" ht="15.75" customHeight="1" s="4"/>
+    <row r="126" ht="15.75" customHeight="1" s="4"/>
+    <row r="127" ht="15.75" customHeight="1" s="4"/>
+    <row r="128" ht="15.75" customHeight="1" s="4"/>
+    <row r="129" ht="15.75" customHeight="1" s="4"/>
+    <row r="130" ht="15.75" customHeight="1" s="4"/>
+    <row r="131" ht="15.75" customHeight="1" s="4"/>
+    <row r="132" ht="15.75" customHeight="1" s="4"/>
+    <row r="133" ht="15.75" customHeight="1" s="4"/>
+    <row r="134" ht="15.75" customHeight="1" s="4"/>
+    <row r="135" ht="15.75" customHeight="1" s="4"/>
+    <row r="136" ht="15.75" customHeight="1" s="4"/>
+    <row r="137" ht="15.75" customHeight="1" s="4"/>
+    <row r="138" ht="15.75" customHeight="1" s="4"/>
+    <row r="139" ht="15.75" customHeight="1" s="4"/>
+    <row r="140" ht="15.75" customHeight="1" s="4"/>
+    <row r="141" ht="15.75" customHeight="1" s="4"/>
+    <row r="142" ht="15.75" customHeight="1" s="4"/>
+    <row r="143" ht="15.75" customHeight="1" s="4"/>
+    <row r="144" ht="15.75" customHeight="1" s="4"/>
+    <row r="145" ht="15.75" customHeight="1" s="4"/>
+    <row r="146" ht="15.75" customHeight="1" s="4"/>
+    <row r="147" ht="15.75" customHeight="1" s="4"/>
+    <row r="148" ht="15.75" customHeight="1" s="4"/>
+    <row r="149" ht="15.75" customHeight="1" s="4"/>
+    <row r="150" ht="15.75" customHeight="1" s="4"/>
+    <row r="151" ht="15.75" customHeight="1" s="4"/>
+    <row r="152" ht="15.75" customHeight="1" s="4"/>
+    <row r="153" ht="15.75" customHeight="1" s="4"/>
+    <row r="154" ht="15.75" customHeight="1" s="4"/>
+    <row r="155" ht="15.75" customHeight="1" s="4"/>
+    <row r="156" ht="15.75" customHeight="1" s="4"/>
+    <row r="157" ht="15.75" customHeight="1" s="4"/>
+    <row r="158" ht="15.75" customHeight="1" s="4"/>
+    <row r="159" ht="15.75" customHeight="1" s="4"/>
+    <row r="160" ht="15.75" customHeight="1" s="4"/>
+    <row r="161" ht="15.75" customHeight="1" s="4"/>
+    <row r="162" ht="15.75" customHeight="1" s="4"/>
+    <row r="163" ht="15.75" customHeight="1" s="4"/>
+    <row r="164" ht="15.75" customHeight="1" s="4"/>
+    <row r="165" ht="15.75" customHeight="1" s="4"/>
+    <row r="166" ht="15.75" customHeight="1" s="4"/>
+    <row r="167" ht="15.75" customHeight="1" s="4"/>
+    <row r="168" ht="15.75" customHeight="1" s="4"/>
+    <row r="169" ht="15.75" customHeight="1" s="4"/>
+    <row r="170" ht="15.75" customHeight="1" s="4"/>
+    <row r="171" ht="15.75" customHeight="1" s="4"/>
+    <row r="172" ht="15.75" customHeight="1" s="4"/>
+    <row r="173" ht="15.75" customHeight="1" s="4"/>
+    <row r="174" ht="15.75" customHeight="1" s="4"/>
+    <row r="175" ht="15.75" customHeight="1" s="4"/>
+    <row r="176" ht="15.75" customHeight="1" s="4"/>
+    <row r="177" ht="15.75" customHeight="1" s="4"/>
+    <row r="178" ht="15.75" customHeight="1" s="4"/>
+    <row r="179" ht="15.75" customHeight="1" s="4"/>
+    <row r="180" ht="15.75" customHeight="1" s="4"/>
+    <row r="181" ht="15.75" customHeight="1" s="4"/>
+    <row r="182" ht="15.75" customHeight="1" s="4"/>
+    <row r="183" ht="15.75" customHeight="1" s="4"/>
+    <row r="184" ht="15.75" customHeight="1" s="4"/>
+    <row r="185" ht="15.75" customHeight="1" s="4"/>
+    <row r="186" ht="15.75" customHeight="1" s="4"/>
+    <row r="187" ht="15.75" customHeight="1" s="4"/>
+    <row r="188" ht="15.75" customHeight="1" s="4"/>
+    <row r="189" ht="15.75" customHeight="1" s="4"/>
+    <row r="190" ht="15.75" customHeight="1" s="4"/>
+    <row r="191" ht="15.75" customHeight="1" s="4"/>
+    <row r="192" ht="15.75" customHeight="1" s="4"/>
+    <row r="193" ht="15.75" customHeight="1" s="4"/>
+    <row r="194" ht="15.75" customHeight="1" s="4"/>
+    <row r="195" ht="15.75" customHeight="1" s="4"/>
+    <row r="196" ht="15.75" customHeight="1" s="4"/>
+    <row r="197" ht="15.75" customHeight="1" s="4"/>
+    <row r="198" ht="15.75" customHeight="1" s="4"/>
+    <row r="199" ht="15.75" customHeight="1" s="4"/>
+    <row r="200" ht="15.75" customHeight="1" s="4"/>
+    <row r="201" ht="15.75" customHeight="1" s="4"/>
+    <row r="202" ht="15.75" customHeight="1" s="4"/>
+    <row r="203" ht="15.75" customHeight="1" s="4"/>
+    <row r="204" ht="15.75" customHeight="1" s="4"/>
+    <row r="205" ht="15.75" customHeight="1" s="4"/>
+    <row r="206" ht="15.75" customHeight="1" s="4"/>
+    <row r="207" ht="15.75" customHeight="1" s="4"/>
+    <row r="208" ht="15.75" customHeight="1" s="4"/>
+    <row r="209" ht="15.75" customHeight="1" s="4"/>
+    <row r="210" ht="15.75" customHeight="1" s="4"/>
+    <row r="211" ht="15.75" customHeight="1" s="4"/>
+    <row r="212" ht="15.75" customHeight="1" s="4"/>
+    <row r="213" ht="15.75" customHeight="1" s="4"/>
+    <row r="214" ht="15.75" customHeight="1" s="4"/>
+    <row r="215" ht="15.75" customHeight="1" s="4"/>
+    <row r="216" ht="15.75" customHeight="1" s="4"/>
+    <row r="217" ht="15.75" customHeight="1" s="4"/>
+    <row r="218" ht="15.75" customHeight="1" s="4"/>
+    <row r="219" ht="15.75" customHeight="1" s="4"/>
+    <row r="220" ht="15.75" customHeight="1" s="4"/>
+    <row r="221" ht="15.75" customHeight="1" s="4"/>
+    <row r="222" ht="15.75" customHeight="1" s="4"/>
+    <row r="223" ht="15.75" customHeight="1" s="4"/>
+    <row r="224" ht="15.75" customHeight="1" s="4"/>
+    <row r="225" ht="15.75" customHeight="1" s="4"/>
+    <row r="226" ht="15.75" customHeight="1" s="4"/>
+    <row r="227" ht="15.75" customHeight="1" s="4"/>
+    <row r="228" ht="15.75" customHeight="1" s="4"/>
+    <row r="229" ht="15.75" customHeight="1" s="4"/>
+    <row r="230" ht="15.75" customHeight="1" s="4"/>
+    <row r="231" ht="15.75" customHeight="1" s="4"/>
+    <row r="232" ht="15.75" customHeight="1" s="4"/>
+    <row r="233" ht="15.75" customHeight="1" s="4"/>
+    <row r="234" ht="15.75" customHeight="1" s="4"/>
+    <row r="235" ht="15.75" customHeight="1" s="4"/>
+    <row r="236" ht="15.75" customHeight="1" s="4"/>
+    <row r="237" ht="15.75" customHeight="1" s="4"/>
+    <row r="238" ht="15.75" customHeight="1" s="4"/>
+    <row r="239" ht="15.75" customHeight="1" s="4"/>
+    <row r="240" ht="15.75" customHeight="1" s="4"/>
+    <row r="241" ht="15.75" customHeight="1" s="4"/>
+    <row r="242" ht="15.75" customHeight="1" s="4"/>
+    <row r="243" ht="15.75" customHeight="1" s="4"/>
+    <row r="244" ht="15.75" customHeight="1" s="4"/>
+    <row r="245" ht="15.75" customHeight="1" s="4"/>
+    <row r="246" ht="15.75" customHeight="1" s="4"/>
+    <row r="247" ht="15.75" customHeight="1" s="4"/>
+    <row r="248" ht="15.75" customHeight="1" s="4"/>
+    <row r="249" ht="15.75" customHeight="1" s="4"/>
+    <row r="250" ht="15.75" customHeight="1" s="4"/>
+    <row r="251" ht="15.75" customHeight="1" s="4"/>
+    <row r="252" ht="15.75" customHeight="1" s="4"/>
+    <row r="253" ht="15.75" customHeight="1" s="4"/>
+    <row r="254" ht="15.75" customHeight="1" s="4"/>
+    <row r="255" ht="15.75" customHeight="1" s="4"/>
+    <row r="256" ht="15.75" customHeight="1" s="4"/>
+    <row r="257" ht="15.75" customHeight="1" s="4"/>
+    <row r="258" ht="15.75" customHeight="1" s="4"/>
+    <row r="259" ht="15.75" customHeight="1" s="4"/>
+    <row r="260" ht="15.75" customHeight="1" s="4"/>
+    <row r="261" ht="15.75" customHeight="1" s="4"/>
+    <row r="262" ht="15.75" customHeight="1" s="4"/>
+    <row r="263" ht="15.75" customHeight="1" s="4"/>
+    <row r="264" ht="15.75" customHeight="1" s="4"/>
+    <row r="265" ht="15.75" customHeight="1" s="4"/>
+    <row r="266" ht="15.75" customHeight="1" s="4"/>
+    <row r="267" ht="15.75" customHeight="1" s="4"/>
+    <row r="268" ht="15.75" customHeight="1" s="4"/>
+    <row r="269" ht="15.75" customHeight="1" s="4"/>
+    <row r="270" ht="15.75" customHeight="1" s="4"/>
+    <row r="271" ht="15.75" customHeight="1" s="4"/>
+    <row r="272" ht="15.75" customHeight="1" s="4"/>
+    <row r="273" ht="15.75" customHeight="1" s="4"/>
+    <row r="274" ht="15.75" customHeight="1" s="4"/>
+    <row r="275" ht="15.75" customHeight="1" s="4"/>
+    <row r="276" ht="15.75" customHeight="1" s="4"/>
+    <row r="277" ht="15.75" customHeight="1" s="4"/>
+    <row r="278" ht="15.75" customHeight="1" s="4"/>
+    <row r="279" ht="15.75" customHeight="1" s="4"/>
+    <row r="280" ht="15.75" customHeight="1" s="4"/>
+    <row r="281" ht="15.75" customHeight="1" s="4"/>
+    <row r="282" ht="15.75" customHeight="1" s="4"/>
+    <row r="283" ht="15.75" customHeight="1" s="4"/>
+    <row r="284" ht="15.75" customHeight="1" s="4"/>
+    <row r="285" ht="15.75" customHeight="1" s="4"/>
+    <row r="286" ht="15.75" customHeight="1" s="4"/>
+    <row r="287" ht="15.75" customHeight="1" s="4"/>
+    <row r="288" ht="15.75" customHeight="1" s="4"/>
+    <row r="289" ht="15.75" customHeight="1" s="4"/>
+    <row r="290" ht="15.75" customHeight="1" s="4"/>
+    <row r="291" ht="15.75" customHeight="1" s="4"/>
+    <row r="292" ht="15.75" customHeight="1" s="4"/>
+    <row r="293" ht="15.75" customHeight="1" s="4"/>
+    <row r="294" ht="15.75" customHeight="1" s="4"/>
+    <row r="295" ht="15.75" customHeight="1" s="4"/>
+    <row r="296" ht="15.75" customHeight="1" s="4"/>
+    <row r="297" ht="15.75" customHeight="1" s="4"/>
+    <row r="298" ht="15.75" customHeight="1" s="4"/>
+    <row r="299" ht="15.75" customHeight="1" s="4"/>
+    <row r="300" ht="15.75" customHeight="1" s="4"/>
+    <row r="301" ht="15.75" customHeight="1" s="4"/>
+    <row r="302" ht="15.75" customHeight="1" s="4"/>
+    <row r="303" ht="15.75" customHeight="1" s="4"/>
+    <row r="304" ht="15.75" customHeight="1" s="4"/>
+    <row r="305" ht="15.75" customHeight="1" s="4"/>
+    <row r="306" ht="15.75" customHeight="1" s="4"/>
+    <row r="307" ht="15.75" customHeight="1" s="4"/>
+    <row r="308" ht="15.75" customHeight="1" s="4"/>
+    <row r="309" ht="15.75" customHeight="1" s="4"/>
+    <row r="310" ht="15.75" customHeight="1" s="4"/>
+    <row r="311" ht="15.75" customHeight="1" s="4"/>
+    <row r="312" ht="15.75" customHeight="1" s="4"/>
+    <row r="313" ht="15.75" customHeight="1" s="4"/>
+    <row r="314" ht="15.75" customHeight="1" s="4"/>
+    <row r="315" ht="15.75" customHeight="1" s="4"/>
+    <row r="316" ht="15.75" customHeight="1" s="4"/>
+    <row r="317" ht="15.75" customHeight="1" s="4"/>
+    <row r="318" ht="15.75" customHeight="1" s="4"/>
+    <row r="319" ht="15.75" customHeight="1" s="4"/>
+    <row r="320" ht="15.75" customHeight="1" s="4"/>
+    <row r="321" ht="15.75" customHeight="1" s="4"/>
+    <row r="322" ht="15.75" customHeight="1" s="4"/>
+    <row r="323" ht="15.75" customHeight="1" s="4"/>
+    <row r="324" ht="15.75" customHeight="1" s="4"/>
+    <row r="325" ht="15.75" customHeight="1" s="4"/>
+    <row r="326" ht="15.75" customHeight="1" s="4"/>
+    <row r="327" ht="15.75" customHeight="1" s="4"/>
+    <row r="328" ht="15.75" customHeight="1" s="4"/>
+    <row r="329" ht="15.75" customHeight="1" s="4"/>
+    <row r="330" ht="15.75" customHeight="1" s="4"/>
+    <row r="331" ht="15.75" customHeight="1" s="4"/>
+    <row r="332" ht="15.75" customHeight="1" s="4"/>
+    <row r="333" ht="15.75" customHeight="1" s="4"/>
+    <row r="334" ht="15.75" customHeight="1" s="4"/>
+    <row r="335" ht="15.75" customHeight="1" s="4"/>
+    <row r="336" ht="15.75" customHeight="1" s="4"/>
+    <row r="337" ht="15.75" customHeight="1" s="4"/>
+    <row r="338" ht="15.75" customHeight="1" s="4"/>
+    <row r="339" ht="15.75" customHeight="1" s="4"/>
+    <row r="340" ht="15.75" customHeight="1" s="4"/>
+    <row r="341" ht="15.75" customHeight="1" s="4"/>
+    <row r="342" ht="15.75" customHeight="1" s="4"/>
+    <row r="343" ht="15.75" customHeight="1" s="4"/>
+    <row r="344" ht="15.75" customHeight="1" s="4"/>
+    <row r="345" ht="15.75" customHeight="1" s="4"/>
+    <row r="346" ht="15.75" customHeight="1" s="4"/>
+    <row r="347" ht="15.75" customHeight="1" s="4"/>
+    <row r="348" ht="15.75" customHeight="1" s="4"/>
+    <row r="349" ht="15.75" customHeight="1" s="4"/>
+    <row r="350" ht="15.75" customHeight="1" s="4"/>
+    <row r="351" ht="15.75" customHeight="1" s="4"/>
+    <row r="352" ht="15.75" customHeight="1" s="4"/>
+    <row r="353" ht="15.75" customHeight="1" s="4"/>
+    <row r="354" ht="15.75" customHeight="1" s="4"/>
+    <row r="355" ht="15.75" customHeight="1" s="4"/>
+    <row r="356" ht="15.75" customHeight="1" s="4"/>
+    <row r="357" ht="15.75" customHeight="1" s="4"/>
+    <row r="358" ht="15.75" customHeight="1" s="4"/>
+    <row r="359" ht="15.75" customHeight="1" s="4"/>
+    <row r="360" ht="15.75" customHeight="1" s="4"/>
+    <row r="361" ht="15.75" customHeight="1" s="4"/>
+    <row r="362" ht="15.75" customHeight="1" s="4"/>
+    <row r="363" ht="15.75" customHeight="1" s="4"/>
+    <row r="364" ht="15.75" customHeight="1" s="4"/>
+    <row r="365" ht="15.75" customHeight="1" s="4"/>
+    <row r="366" ht="15.75" customHeight="1" s="4"/>
+    <row r="367" ht="15.75" customHeight="1" s="4"/>
+    <row r="368" ht="15.75" customHeight="1" s="4"/>
+    <row r="369" ht="15.75" customHeight="1" s="4"/>
+    <row r="370" ht="15.75" customHeight="1" s="4"/>
+    <row r="371" ht="15.75" customHeight="1" s="4"/>
+    <row r="372" ht="15.75" customHeight="1" s="4"/>
+    <row r="373" ht="15.75" customHeight="1" s="4"/>
+    <row r="374" ht="15.75" customHeight="1" s="4"/>
+    <row r="375" ht="15.75" customHeight="1" s="4"/>
+    <row r="376" ht="15.75" customHeight="1" s="4"/>
+    <row r="377" ht="15.75" customHeight="1" s="4"/>
+    <row r="378" ht="15.75" customHeight="1" s="4"/>
+    <row r="379" ht="15.75" customHeight="1" s="4"/>
+    <row r="380" ht="15.75" customHeight="1" s="4"/>
+    <row r="381" ht="15.75" customHeight="1" s="4"/>
+    <row r="382" ht="15.75" customHeight="1" s="4"/>
+    <row r="383" ht="15.75" customHeight="1" s="4"/>
+    <row r="384" ht="15.75" customHeight="1" s="4"/>
+    <row r="385" ht="15.75" customHeight="1" s="4"/>
+    <row r="386" ht="15.75" customHeight="1" s="4"/>
+    <row r="387" ht="15.75" customHeight="1" s="4"/>
+    <row r="388" ht="15.75" customHeight="1" s="4"/>
+    <row r="389" ht="15.75" customHeight="1" s="4"/>
+    <row r="390" ht="15.75" customHeight="1" s="4"/>
+    <row r="391" ht="15.75" customHeight="1" s="4"/>
+    <row r="392" ht="15.75" customHeight="1" s="4"/>
+    <row r="393" ht="15.75" customHeight="1" s="4"/>
+    <row r="394" ht="15.75" customHeight="1" s="4"/>
+    <row r="395" ht="15.75" customHeight="1" s="4"/>
+    <row r="396" ht="15.75" customHeight="1" s="4"/>
+    <row r="397" ht="15.75" customHeight="1" s="4"/>
+    <row r="398" ht="15.75" customHeight="1" s="4"/>
+    <row r="399" ht="15.75" customHeight="1" s="4"/>
+    <row r="400" ht="15.75" customHeight="1" s="4"/>
+    <row r="401" ht="15.75" customHeight="1" s="4"/>
+    <row r="402" ht="15.75" customHeight="1" s="4"/>
+    <row r="403" ht="15.75" customHeight="1" s="4"/>
+    <row r="404" ht="15.75" customHeight="1" s="4"/>
+    <row r="405" ht="15.75" customHeight="1" s="4"/>
+    <row r="406" ht="15.75" customHeight="1" s="4"/>
+    <row r="407" ht="15.75" customHeight="1" s="4"/>
+    <row r="408" ht="15.75" customHeight="1" s="4"/>
+    <row r="409" ht="15.75" customHeight="1" s="4"/>
+    <row r="410" ht="15.75" customHeight="1" s="4"/>
+    <row r="411" ht="15.75" customHeight="1" s="4"/>
+    <row r="412" ht="15.75" customHeight="1" s="4"/>
+    <row r="413" ht="15.75" customHeight="1" s="4"/>
+    <row r="414" ht="15.75" customHeight="1" s="4"/>
+    <row r="415" ht="15.75" customHeight="1" s="4"/>
+    <row r="416" ht="15.75" customHeight="1" s="4"/>
+    <row r="417" ht="15.75" customHeight="1" s="4"/>
+    <row r="418" ht="15.75" customHeight="1" s="4"/>
+    <row r="419" ht="15.75" customHeight="1" s="4"/>
+    <row r="420" ht="15.75" customHeight="1" s="4"/>
+    <row r="421" ht="15.75" customHeight="1" s="4"/>
+    <row r="422" ht="15.75" customHeight="1" s="4"/>
+    <row r="423" ht="15.75" customHeight="1" s="4"/>
+    <row r="424" ht="15.75" customHeight="1" s="4"/>
+    <row r="425" ht="15.75" customHeight="1" s="4"/>
+    <row r="426" ht="15.75" customHeight="1" s="4"/>
+    <row r="427" ht="15.75" customHeight="1" s="4"/>
+    <row r="428" ht="15.75" customHeight="1" s="4"/>
+    <row r="429" ht="15.75" customHeight="1" s="4"/>
+    <row r="430" ht="15.75" customHeight="1" s="4"/>
+    <row r="431" ht="15.75" customHeight="1" s="4"/>
+    <row r="432" ht="15.75" customHeight="1" s="4"/>
+    <row r="433" ht="15.75" customHeight="1" s="4"/>
+    <row r="434" ht="15.75" customHeight="1" s="4"/>
+    <row r="435" ht="15.75" customHeight="1" s="4"/>
+    <row r="436" ht="15.75" customHeight="1" s="4"/>
+    <row r="437" ht="15.75" customHeight="1" s="4"/>
+    <row r="438" ht="15.75" customHeight="1" s="4"/>
+    <row r="439" ht="15.75" customHeight="1" s="4"/>
+    <row r="440" ht="15.75" customHeight="1" s="4"/>
+    <row r="441" ht="15.75" customHeight="1" s="4"/>
+    <row r="442" ht="15.75" customHeight="1" s="4"/>
+    <row r="443" ht="15.75" customHeight="1" s="4"/>
+    <row r="444" ht="15.75" customHeight="1" s="4"/>
+    <row r="445" ht="15.75" customHeight="1" s="4"/>
+    <row r="446" ht="15.75" customHeight="1" s="4"/>
+    <row r="447" ht="15.75" customHeight="1" s="4"/>
+    <row r="448" ht="15.75" customHeight="1" s="4"/>
+    <row r="449" ht="15.75" customHeight="1" s="4"/>
+    <row r="450" ht="15.75" customHeight="1" s="4"/>
+    <row r="451" ht="15.75" customHeight="1" s="4"/>
+    <row r="452" ht="15.75" customHeight="1" s="4"/>
+    <row r="453" ht="15.75" customHeight="1" s="4"/>
+    <row r="454" ht="15.75" customHeight="1" s="4"/>
+    <row r="455" ht="15.75" customHeight="1" s="4"/>
+    <row r="456" ht="15.75" customHeight="1" s="4"/>
+    <row r="457" ht="15.75" customHeight="1" s="4"/>
+    <row r="458" ht="15.75" customHeight="1" s="4"/>
+    <row r="459" ht="15.75" customHeight="1" s="4"/>
+    <row r="460" ht="15.75" customHeight="1" s="4"/>
+    <row r="461" ht="15.75" customHeight="1" s="4"/>
+    <row r="462" ht="15.75" customHeight="1" s="4"/>
+    <row r="463" ht="15.75" customHeight="1" s="4"/>
+    <row r="464" ht="15.75" customHeight="1" s="4"/>
+    <row r="465" ht="15.75" customHeight="1" s="4"/>
+    <row r="466" ht="15.75" customHeight="1" s="4"/>
+    <row r="467" ht="15.75" customHeight="1" s="4"/>
+    <row r="468" ht="15.75" customHeight="1" s="4"/>
+    <row r="469" ht="15.75" customHeight="1" s="4"/>
+    <row r="470" ht="15.75" customHeight="1" s="4"/>
+    <row r="471" ht="15.75" customHeight="1" s="4"/>
+    <row r="472" ht="15.75" customHeight="1" s="4"/>
+    <row r="473" ht="15.75" customHeight="1" s="4"/>
+    <row r="474" ht="15.75" customHeight="1" s="4"/>
+    <row r="475" ht="15.75" customHeight="1" s="4"/>
+    <row r="476" ht="15.75" customHeight="1" s="4"/>
+    <row r="477" ht="15.75" customHeight="1" s="4"/>
+    <row r="478" ht="15.75" customHeight="1" s="4"/>
+    <row r="479" ht="15.75" customHeight="1" s="4"/>
+    <row r="480" ht="15.75" customHeight="1" s="4"/>
+    <row r="481" ht="15.75" customHeight="1" s="4"/>
+    <row r="482" ht="15.75" customHeight="1" s="4"/>
+    <row r="483" ht="15.75" customHeight="1" s="4"/>
+    <row r="484" ht="15.75" customHeight="1" s="4"/>
+    <row r="485" ht="15.75" customHeight="1" s="4"/>
+    <row r="486" ht="15.75" customHeight="1" s="4"/>
+    <row r="487" ht="15.75" customHeight="1" s="4"/>
+    <row r="488" ht="15.75" customHeight="1" s="4"/>
+    <row r="489" ht="15.75" customHeight="1" s="4"/>
+    <row r="490" ht="15.75" customHeight="1" s="4"/>
+    <row r="491" ht="15.75" customHeight="1" s="4"/>
+    <row r="492" ht="15.75" customHeight="1" s="4"/>
+    <row r="493" ht="15.75" customHeight="1" s="4"/>
+    <row r="494" ht="15.75" customHeight="1" s="4"/>
+    <row r="495" ht="15.75" customHeight="1" s="4"/>
+    <row r="496" ht="15.75" customHeight="1" s="4"/>
+    <row r="497" ht="15.75" customHeight="1" s="4"/>
+    <row r="498" ht="15.75" customHeight="1" s="4"/>
+    <row r="499" ht="15.75" customHeight="1" s="4"/>
+    <row r="500" ht="15.75" customHeight="1" s="4"/>
+    <row r="501" ht="15.75" customHeight="1" s="4"/>
+    <row r="502" ht="15.75" customHeight="1" s="4"/>
+    <row r="503" ht="15.75" customHeight="1" s="4"/>
+    <row r="504" ht="15.75" customHeight="1" s="4"/>
+    <row r="505" ht="15.75" customHeight="1" s="4"/>
+    <row r="506" ht="15.75" customHeight="1" s="4"/>
+    <row r="507" ht="15.75" customHeight="1" s="4"/>
+    <row r="508" ht="15.75" customHeight="1" s="4"/>
+    <row r="509" ht="15.75" customHeight="1" s="4"/>
+    <row r="510" ht="15.75" customHeight="1" s="4"/>
+    <row r="511" ht="15.75" customHeight="1" s="4"/>
+    <row r="512" ht="15.75" customHeight="1" s="4"/>
+    <row r="513" ht="15.75" customHeight="1" s="4"/>
+    <row r="514" ht="15.75" customHeight="1" s="4"/>
+    <row r="515" ht="15.75" customHeight="1" s="4"/>
+    <row r="516" ht="15.75" customHeight="1" s="4"/>
+    <row r="517" ht="15.75" customHeight="1" s="4"/>
+    <row r="518" ht="15.75" customHeight="1" s="4"/>
+    <row r="519" ht="15.75" customHeight="1" s="4"/>
+    <row r="520" ht="15.75" customHeight="1" s="4"/>
+    <row r="521" ht="15.75" customHeight="1" s="4"/>
+    <row r="522" ht="15.75" customHeight="1" s="4"/>
+    <row r="523" ht="15.75" customHeight="1" s="4"/>
+    <row r="524" ht="15.75" customHeight="1" s="4"/>
+    <row r="525" ht="15.75" customHeight="1" s="4"/>
+    <row r="526" ht="15.75" customHeight="1" s="4"/>
+    <row r="527" ht="15.75" customHeight="1" s="4"/>
+    <row r="528" ht="15.75" customHeight="1" s="4"/>
+    <row r="529" ht="15.75" customHeight="1" s="4"/>
+    <row r="530" ht="15.75" customHeight="1" s="4"/>
+    <row r="531" ht="15.75" customHeight="1" s="4"/>
+    <row r="532" ht="15.75" customHeight="1" s="4"/>
+    <row r="533" ht="15.75" customHeight="1" s="4"/>
+    <row r="534" ht="15.75" customHeight="1" s="4"/>
+    <row r="535" ht="15.75" customHeight="1" s="4"/>
+    <row r="536" ht="15.75" customHeight="1" s="4"/>
+    <row r="537" ht="15.75" customHeight="1" s="4"/>
+    <row r="538" ht="15.75" customHeight="1" s="4"/>
+    <row r="539" ht="15.75" customHeight="1" s="4"/>
+    <row r="540" ht="15.75" customHeight="1" s="4"/>
+    <row r="541" ht="15.75" customHeight="1" s="4"/>
+    <row r="542" ht="15.75" customHeight="1" s="4"/>
+    <row r="543" ht="15.75" customHeight="1" s="4"/>
+    <row r="544" ht="15.75" customHeight="1" s="4"/>
+    <row r="545" ht="15.75" customHeight="1" s="4"/>
+    <row r="546" ht="15.75" customHeight="1" s="4"/>
+    <row r="547" ht="15.75" customHeight="1" s="4"/>
+    <row r="548" ht="15.75" customHeight="1" s="4"/>
+    <row r="549" ht="15.75" customHeight="1" s="4"/>
+    <row r="550" ht="15.75" customHeight="1" s="4"/>
+    <row r="551" ht="15.75" customHeight="1" s="4"/>
+    <row r="552" ht="15.75" customHeight="1" s="4"/>
+    <row r="553" ht="15.75" customHeight="1" s="4"/>
+    <row r="554" ht="15.75" customHeight="1" s="4"/>
+    <row r="555" ht="15.75" customHeight="1" s="4"/>
+    <row r="556" ht="15.75" customHeight="1" s="4"/>
+    <row r="557" ht="15.75" customHeight="1" s="4"/>
+    <row r="558" ht="15.75" customHeight="1" s="4"/>
+    <row r="559" ht="15.75" customHeight="1" s="4"/>
+    <row r="560" ht="15.75" customHeight="1" s="4"/>
+    <row r="561" ht="15.75" customHeight="1" s="4"/>
+    <row r="562" ht="15.75" customHeight="1" s="4"/>
+    <row r="563" ht="15.75" customHeight="1" s="4"/>
+    <row r="564" ht="15.75" customHeight="1" s="4"/>
+    <row r="565" ht="15.75" customHeight="1" s="4"/>
+    <row r="566" ht="15.75" customHeight="1" s="4"/>
+    <row r="567" ht="15.75" customHeight="1" s="4"/>
+    <row r="568" ht="15.75" customHeight="1" s="4"/>
+    <row r="569" ht="15.75" customHeight="1" s="4"/>
+    <row r="570" ht="15.75" customHeight="1" s="4"/>
+    <row r="571" ht="15.75" customHeight="1" s="4"/>
+    <row r="572" ht="15.75" customHeight="1" s="4"/>
+    <row r="573" ht="15.75" customHeight="1" s="4"/>
+    <row r="574" ht="15.75" customHeight="1" s="4"/>
+    <row r="575" ht="15.75" customHeight="1" s="4"/>
+    <row r="576" ht="15.75" customHeight="1" s="4"/>
+    <row r="577" ht="15.75" customHeight="1" s="4"/>
+    <row r="578" ht="15.75" customHeight="1" s="4"/>
+    <row r="579" ht="15.75" customHeight="1" s="4"/>
+    <row r="580" ht="15.75" customHeight="1" s="4"/>
+    <row r="581" ht="15.75" customHeight="1" s="4"/>
+    <row r="582" ht="15.75" customHeight="1" s="4"/>
+    <row r="583" ht="15.75" customHeight="1" s="4"/>
+    <row r="584" ht="15.75" customHeight="1" s="4"/>
+    <row r="585" ht="15.75" customHeight="1" s="4"/>
+    <row r="586" ht="15.75" customHeight="1" s="4"/>
+    <row r="587" ht="15.75" customHeight="1" s="4"/>
+    <row r="588" ht="15.75" customHeight="1" s="4"/>
+    <row r="589" ht="15.75" customHeight="1" s="4"/>
+    <row r="590" ht="15.75" customHeight="1" s="4"/>
+    <row r="591" ht="15.75" customHeight="1" s="4"/>
+    <row r="592" ht="15.75" customHeight="1" s="4"/>
+    <row r="593" ht="15.75" customHeight="1" s="4"/>
+    <row r="594" ht="15.75" customHeight="1" s="4"/>
+    <row r="595" ht="15.75" customHeight="1" s="4"/>
+    <row r="596" ht="15.75" customHeight="1" s="4"/>
+    <row r="597" ht="15.75" customHeight="1" s="4"/>
+    <row r="598" ht="15.75" customHeight="1" s="4"/>
+    <row r="599" ht="15.75" customHeight="1" s="4"/>
+    <row r="600" ht="15.75" customHeight="1" s="4"/>
+    <row r="601" ht="15.75" customHeight="1" s="4"/>
+    <row r="602" ht="15.75" customHeight="1" s="4"/>
+    <row r="603" ht="15.75" customHeight="1" s="4"/>
+    <row r="604" ht="15.75" customHeight="1" s="4"/>
+    <row r="605" ht="15.75" customHeight="1" s="4"/>
+    <row r="606" ht="15.75" customHeight="1" s="4"/>
+    <row r="607" ht="15.75" customHeight="1" s="4"/>
+    <row r="608" ht="15.75" customHeight="1" s="4"/>
+    <row r="609" ht="15.75" customHeight="1" s="4"/>
+    <row r="610" ht="15.75" customHeight="1" s="4"/>
+    <row r="611" ht="15.75" customHeight="1" s="4"/>
+    <row r="612" ht="15.75" customHeight="1" s="4"/>
+    <row r="613" ht="15.75" customHeight="1" s="4"/>
+    <row r="614" ht="15.75" customHeight="1" s="4"/>
+    <row r="615" ht="15.75" customHeight="1" s="4"/>
+    <row r="616" ht="15.75" customHeight="1" s="4"/>
+    <row r="617" ht="15.75" customHeight="1" s="4"/>
+    <row r="618" ht="15.75" customHeight="1" s="4"/>
+    <row r="619" ht="15.75" customHeight="1" s="4"/>
+    <row r="620" ht="15.75" customHeight="1" s="4"/>
+    <row r="621" ht="15.75" customHeight="1" s="4"/>
+    <row r="622" ht="15.75" customHeight="1" s="4"/>
+    <row r="623" ht="15.75" customHeight="1" s="4"/>
+    <row r="624" ht="15.75" customHeight="1" s="4"/>
+    <row r="625" ht="15.75" customHeight="1" s="4"/>
+    <row r="626" ht="15.75" customHeight="1" s="4"/>
+    <row r="627" ht="15.75" customHeight="1" s="4"/>
+    <row r="628" ht="15.75" customHeight="1" s="4"/>
+    <row r="629" ht="15.75" customHeight="1" s="4"/>
+    <row r="630" ht="15.75" customHeight="1" s="4"/>
+    <row r="631" ht="15.75" customHeight="1" s="4"/>
+    <row r="632" ht="15.75" customHeight="1" s="4"/>
+    <row r="633" ht="15.75" customHeight="1" s="4"/>
+    <row r="634" ht="15.75" customHeight="1" s="4"/>
+    <row r="635" ht="15.75" customHeight="1" s="4"/>
+    <row r="636" ht="15.75" customHeight="1" s="4"/>
+    <row r="637" ht="15.75" customHeight="1" s="4"/>
+    <row r="638" ht="15.75" customHeight="1" s="4"/>
+    <row r="639" ht="15.75" customHeight="1" s="4"/>
+    <row r="640" ht="15.75" customHeight="1" s="4"/>
+    <row r="641" ht="15.75" customHeight="1" s="4"/>
+    <row r="642" ht="15.75" customHeight="1" s="4"/>
+    <row r="643" ht="15.75" customHeight="1" s="4"/>
+    <row r="644" ht="15.75" customHeight="1" s="4"/>
+    <row r="645" ht="15.75" customHeight="1" s="4"/>
+    <row r="646" ht="15.75" customHeight="1" s="4"/>
+    <row r="647" ht="15.75" customHeight="1" s="4"/>
+    <row r="648" ht="15.75" customHeight="1" s="4"/>
+    <row r="649" ht="15.75" customHeight="1" s="4"/>
+    <row r="650" ht="15.75" customHeight="1" s="4"/>
+    <row r="651" ht="15.75" customHeight="1" s="4"/>
+    <row r="652" ht="15.75" customHeight="1" s="4"/>
+    <row r="653" ht="15.75" customHeight="1" s="4"/>
+    <row r="654" ht="15.75" customHeight="1" s="4"/>
+    <row r="655" ht="15.75" customHeight="1" s="4"/>
+    <row r="656" ht="15.75" customHeight="1" s="4"/>
+    <row r="657" ht="15.75" customHeight="1" s="4"/>
+    <row r="658" ht="15.75" customHeight="1" s="4"/>
+    <row r="659" ht="15.75" customHeight="1" s="4"/>
+    <row r="660" ht="15.75" customHeight="1" s="4"/>
+    <row r="661" ht="15.75" customHeight="1" s="4"/>
+    <row r="662" ht="15.75" customHeight="1" s="4"/>
+    <row r="663" ht="15.75" customHeight="1" s="4"/>
+    <row r="664" ht="15.75" customHeight="1" s="4"/>
+    <row r="665" ht="15.75" customHeight="1" s="4"/>
+    <row r="666" ht="15.75" customHeight="1" s="4"/>
+    <row r="667" ht="15.75" customHeight="1" s="4"/>
+    <row r="668" ht="15.75" customHeight="1" s="4"/>
+    <row r="669" ht="15.75" customHeight="1" s="4"/>
+    <row r="670" ht="15.75" customHeight="1" s="4"/>
+    <row r="671" ht="15.75" customHeight="1" s="4"/>
+    <row r="672" ht="15.75" customHeight="1" s="4"/>
+    <row r="673" ht="15.75" customHeight="1" s="4"/>
+    <row r="674" ht="15.75" customHeight="1" s="4"/>
+    <row r="675" ht="15.75" customHeight="1" s="4"/>
+    <row r="676" ht="15.75" customHeight="1" s="4"/>
+    <row r="677" ht="15.75" customHeight="1" s="4"/>
+    <row r="678" ht="15.75" customHeight="1" s="4"/>
+    <row r="679" ht="15.75" customHeight="1" s="4"/>
+    <row r="680" ht="15.75" customHeight="1" s="4"/>
+    <row r="681" ht="15.75" customHeight="1" s="4"/>
+    <row r="682" ht="15.75" customHeight="1" s="4"/>
+    <row r="683" ht="15.75" customHeight="1" s="4"/>
+    <row r="684" ht="15.75" customHeight="1" s="4"/>
+    <row r="685" ht="15.75" customHeight="1" s="4"/>
+    <row r="686" ht="15.75" customHeight="1" s="4"/>
+    <row r="687" ht="15.75" customHeight="1" s="4"/>
+    <row r="688" ht="15.75" customHeight="1" s="4"/>
+    <row r="689" ht="15.75" customHeight="1" s="4"/>
+    <row r="690" ht="15.75" customHeight="1" s="4"/>
+    <row r="691" ht="15.75" customHeight="1" s="4"/>
+    <row r="692" ht="15.75" customHeight="1" s="4"/>
+    <row r="693" ht="15.75" customHeight="1" s="4"/>
+    <row r="694" ht="15.75" customHeight="1" s="4"/>
+    <row r="695" ht="15.75" customHeight="1" s="4"/>
+    <row r="696" ht="15.75" customHeight="1" s="4"/>
+    <row r="697" ht="15.75" customHeight="1" s="4"/>
+    <row r="698" ht="15.75" customHeight="1" s="4"/>
+    <row r="699" ht="15.75" customHeight="1" s="4"/>
+    <row r="700" ht="15.75" customHeight="1" s="4"/>
+    <row r="701" ht="15.75" customHeight="1" s="4"/>
+    <row r="702" ht="15.75" customHeight="1" s="4"/>
+    <row r="703" ht="15.75" customHeight="1" s="4"/>
+    <row r="704" ht="15.75" customHeight="1" s="4"/>
+    <row r="705" ht="15.75" customHeight="1" s="4"/>
+    <row r="706" ht="15.75" customHeight="1" s="4"/>
+    <row r="707" ht="15.75" customHeight="1" s="4"/>
+    <row r="708" ht="15.75" customHeight="1" s="4"/>
+    <row r="709" ht="15.75" customHeight="1" s="4"/>
+    <row r="710" ht="15.75" customHeight="1" s="4"/>
+    <row r="711" ht="15.75" customHeight="1" s="4"/>
+    <row r="712" ht="15.75" customHeight="1" s="4"/>
+    <row r="713" ht="15.75" customHeight="1" s="4"/>
+    <row r="714" ht="15.75" customHeight="1" s="4"/>
+    <row r="715" ht="15.75" customHeight="1" s="4"/>
+    <row r="716" ht="15.75" customHeight="1" s="4"/>
+    <row r="717" ht="15.75" customHeight="1" s="4"/>
+    <row r="718" ht="15.75" customHeight="1" s="4"/>
+    <row r="719" ht="15.75" customHeight="1" s="4"/>
+    <row r="720" ht="15.75" customHeight="1" s="4"/>
+    <row r="721" ht="15.75" customHeight="1" s="4"/>
+    <row r="722" ht="15.75" customHeight="1" s="4"/>
+    <row r="723" ht="15.75" customHeight="1" s="4"/>
+    <row r="724" ht="15.75" customHeight="1" s="4"/>
+    <row r="725" ht="15.75" customHeight="1" s="4"/>
+    <row r="726" ht="15.75" customHeight="1" s="4"/>
+    <row r="727" ht="15.75" customHeight="1" s="4"/>
+    <row r="728" ht="15.75" customHeight="1" s="4"/>
+    <row r="729" ht="15.75" customHeight="1" s="4"/>
+    <row r="730" ht="15.75" customHeight="1" s="4"/>
+    <row r="731" ht="15.75" customHeight="1" s="4"/>
+    <row r="732" ht="15.75" customHeight="1" s="4"/>
+    <row r="733" ht="15.75" customHeight="1" s="4"/>
+    <row r="734" ht="15.75" customHeight="1" s="4"/>
+    <row r="735" ht="15.75" customHeight="1" s="4"/>
+    <row r="736" ht="15.75" customHeight="1" s="4"/>
+    <row r="737" ht="15.75" customHeight="1" s="4"/>
+    <row r="738" ht="15.75" customHeight="1" s="4"/>
+    <row r="739" ht="15.75" customHeight="1" s="4"/>
+    <row r="740" ht="15.75" customHeight="1" s="4"/>
+    <row r="741" ht="15.75" customHeight="1" s="4"/>
+    <row r="742" ht="15.75" customHeight="1" s="4"/>
+    <row r="743" ht="15.75" customHeight="1" s="4"/>
+    <row r="744" ht="15.75" customHeight="1" s="4"/>
+    <row r="745" ht="15.75" customHeight="1" s="4"/>
+    <row r="746" ht="15.75" customHeight="1" s="4"/>
+    <row r="747" ht="15.75" customHeight="1" s="4"/>
+    <row r="748" ht="15.75" customHeight="1" s="4"/>
+    <row r="749" ht="15.75" customHeight="1" s="4"/>
+    <row r="750" ht="15.75" customHeight="1" s="4"/>
+    <row r="751" ht="15.75" customHeight="1" s="4"/>
+    <row r="752" ht="15.75" customHeight="1" s="4"/>
+    <row r="753" ht="15.75" customHeight="1" s="4"/>
+    <row r="754" ht="15.75" customHeight="1" s="4"/>
+    <row r="755" ht="15.75" customHeight="1" s="4"/>
+    <row r="756" ht="15.75" customHeight="1" s="4"/>
+    <row r="757" ht="15.75" customHeight="1" s="4"/>
+    <row r="758" ht="15.75" customHeight="1" s="4"/>
+    <row r="759" ht="15.75" customHeight="1" s="4"/>
+    <row r="760" ht="15.75" customHeight="1" s="4"/>
+    <row r="761" ht="15.75" customHeight="1" s="4"/>
+    <row r="762" ht="15.75" customHeight="1" s="4"/>
+    <row r="763" ht="15.75" customHeight="1" s="4"/>
+    <row r="764" ht="15.75" customHeight="1" s="4"/>
+    <row r="765" ht="15.75" customHeight="1" s="4"/>
+    <row r="766" ht="15.75" customHeight="1" s="4"/>
+    <row r="767" ht="15.75" customHeight="1" s="4"/>
+    <row r="768" ht="15.75" customHeight="1" s="4"/>
+    <row r="769" ht="15.75" customHeight="1" s="4"/>
+    <row r="770" ht="15.75" customHeight="1" s="4"/>
+    <row r="771" ht="15.75" customHeight="1" s="4"/>
+    <row r="772" ht="15.75" customHeight="1" s="4"/>
+    <row r="773" ht="15.75" customHeight="1" s="4"/>
+    <row r="774" ht="15.75" customHeight="1" s="4"/>
+    <row r="775" ht="15.75" customHeight="1" s="4"/>
+    <row r="776" ht="15.75" customHeight="1" s="4"/>
+    <row r="777" ht="15.75" customHeight="1" s="4"/>
+    <row r="778" ht="15.75" customHeight="1" s="4"/>
+    <row r="779" ht="15.75" customHeight="1" s="4"/>
+    <row r="780" ht="15.75" customHeight="1" s="4"/>
+    <row r="781" ht="15.75" customHeight="1" s="4"/>
+    <row r="782" ht="15.75" customHeight="1" s="4"/>
+    <row r="783" ht="15.75" customHeight="1" s="4"/>
+    <row r="784" ht="15.75" customHeight="1" s="4"/>
+    <row r="785" ht="15.75" customHeight="1" s="4"/>
+    <row r="786" ht="15.75" customHeight="1" s="4"/>
+    <row r="787" ht="15.75" customHeight="1" s="4"/>
+    <row r="788" ht="15.75" customHeight="1" s="4"/>
+    <row r="789" ht="15.75" customHeight="1" s="4"/>
+    <row r="790" ht="15.75" customHeight="1" s="4"/>
+    <row r="791" ht="15.75" customHeight="1" s="4"/>
+    <row r="792" ht="15.75" customHeight="1" s="4"/>
+    <row r="793" ht="15.75" customHeight="1" s="4"/>
+    <row r="794" ht="15.75" customHeight="1" s="4"/>
+    <row r="795" ht="15.75" customHeight="1" s="4"/>
+    <row r="796" ht="15.75" customHeight="1" s="4"/>
+    <row r="797" ht="15.75" customHeight="1" s="4"/>
+    <row r="798" ht="15.75" customHeight="1" s="4"/>
+    <row r="799" ht="15.75" customHeight="1" s="4"/>
+    <row r="800" ht="15.75" customHeight="1" s="4"/>
+    <row r="801" ht="15.75" customHeight="1" s="4"/>
+    <row r="802" ht="15.75" customHeight="1" s="4"/>
+    <row r="803" ht="15.75" customHeight="1" s="4"/>
+    <row r="804" ht="15.75" customHeight="1" s="4"/>
+    <row r="805" ht="15.75" customHeight="1" s="4"/>
+    <row r="806" ht="15.75" customHeight="1" s="4"/>
+    <row r="807" ht="15.75" customHeight="1" s="4"/>
+    <row r="808" ht="15.75" customHeight="1" s="4"/>
+    <row r="809" ht="15.75" customHeight="1" s="4"/>
+    <row r="810" ht="15.75" customHeight="1" s="4"/>
+    <row r="811" ht="15.75" customHeight="1" s="4"/>
+    <row r="812" ht="15.75" customHeight="1" s="4"/>
+    <row r="813" ht="15.75" customHeight="1" s="4"/>
+    <row r="814" ht="15.75" customHeight="1" s="4"/>
+    <row r="815" ht="15.75" customHeight="1" s="4"/>
+    <row r="816" ht="15.75" customHeight="1" s="4"/>
+    <row r="817" ht="15.75" customHeight="1" s="4"/>
+    <row r="818" ht="15.75" customHeight="1" s="4"/>
+    <row r="819" ht="15.75" customHeight="1" s="4"/>
+    <row r="820" ht="15.75" customHeight="1" s="4"/>
+    <row r="821" ht="15.75" customHeight="1" s="4"/>
+    <row r="822" ht="15.75" customHeight="1" s="4"/>
+    <row r="823" ht="15.75" customHeight="1" s="4"/>
+    <row r="824" ht="15.75" customHeight="1" s="4"/>
+    <row r="825" ht="15.75" customHeight="1" s="4"/>
+    <row r="826" ht="15.75" customHeight="1" s="4"/>
+    <row r="827" ht="15.75" customHeight="1" s="4"/>
+    <row r="828" ht="15.75" customHeight="1" s="4"/>
+    <row r="829" ht="15.75" customHeight="1" s="4"/>
+    <row r="830" ht="15.75" customHeight="1" s="4"/>
+    <row r="831" ht="15.75" customHeight="1" s="4"/>
+    <row r="832" ht="15.75" customHeight="1" s="4"/>
+    <row r="833" ht="15.75" customHeight="1" s="4"/>
+    <row r="834" ht="15.75" customHeight="1" s="4"/>
+    <row r="835" ht="15.75" customHeight="1" s="4"/>
+    <row r="836" ht="15.75" customHeight="1" s="4"/>
+    <row r="837" ht="15.75" customHeight="1" s="4"/>
+    <row r="838" ht="15.75" customHeight="1" s="4"/>
+    <row r="839" ht="15.75" customHeight="1" s="4"/>
+    <row r="840" ht="15.75" customHeight="1" s="4"/>
+    <row r="841" ht="15.75" customHeight="1" s="4"/>
+    <row r="842" ht="15.75" customHeight="1" s="4"/>
+    <row r="843" ht="15.75" customHeight="1" s="4"/>
+    <row r="844" ht="15.75" customHeight="1" s="4"/>
+    <row r="845" ht="15.75" customHeight="1" s="4"/>
+    <row r="846" ht="15.75" customHeight="1" s="4"/>
+    <row r="847" ht="15.75" customHeight="1" s="4"/>
+    <row r="848" ht="15.75" customHeight="1" s="4"/>
+    <row r="849" ht="15.75" customHeight="1" s="4"/>
+    <row r="850" ht="15.75" customHeight="1" s="4"/>
+    <row r="851" ht="15.75" customHeight="1" s="4"/>
+    <row r="852" ht="15.75" customHeight="1" s="4"/>
+    <row r="853" ht="15.75" customHeight="1" s="4"/>
+    <row r="854" ht="15.75" customHeight="1" s="4"/>
+    <row r="855" ht="15.75" customHeight="1" s="4"/>
+    <row r="856" ht="15.75" customHeight="1" s="4"/>
+    <row r="857" ht="15.75" customHeight="1" s="4"/>
+    <row r="858" ht="15.75" customHeight="1" s="4"/>
+    <row r="859" ht="15.75" customHeight="1" s="4"/>
+    <row r="860" ht="15.75" customHeight="1" s="4"/>
+    <row r="861" ht="15.75" customHeight="1" s="4"/>
+    <row r="862" ht="15.75" customHeight="1" s="4"/>
+    <row r="863" ht="15.75" customHeight="1" s="4"/>
+    <row r="864" ht="15.75" customHeight="1" s="4"/>
+    <row r="865" ht="15.75" customHeight="1" s="4"/>
+    <row r="866" ht="15.75" customHeight="1" s="4"/>
+    <row r="867" ht="15.75" customHeight="1" s="4"/>
+    <row r="868" ht="15.75" customHeight="1" s="4"/>
+    <row r="869" ht="15.75" customHeight="1" s="4"/>
+    <row r="870" ht="15.75" customHeight="1" s="4"/>
+    <row r="871" ht="15.75" customHeight="1" s="4"/>
+    <row r="872" ht="15.75" customHeight="1" s="4"/>
+    <row r="873" ht="15.75" customHeight="1" s="4"/>
+    <row r="874" ht="15.75" customHeight="1" s="4"/>
+    <row r="875" ht="15.75" customHeight="1" s="4"/>
+    <row r="876" ht="15.75" customHeight="1" s="4"/>
+    <row r="877" ht="15.75" customHeight="1" s="4"/>
+    <row r="878" ht="15.75" customHeight="1" s="4"/>
+    <row r="879" ht="15.75" customHeight="1" s="4"/>
+    <row r="880" ht="15.75" customHeight="1" s="4"/>
+    <row r="881" ht="15.75" customHeight="1" s="4"/>
+    <row r="882" ht="15.75" customHeight="1" s="4"/>
+    <row r="883" ht="15.75" customHeight="1" s="4"/>
+    <row r="884" ht="15.75" customHeight="1" s="4"/>
+    <row r="885" ht="15.75" customHeight="1" s="4"/>
+    <row r="886" ht="15.75" customHeight="1" s="4"/>
+    <row r="887" ht="15.75" customHeight="1" s="4"/>
+    <row r="888" ht="15.75" customHeight="1" s="4"/>
+    <row r="889" ht="15.75" customHeight="1" s="4"/>
+    <row r="890" ht="15.75" customHeight="1" s="4"/>
+    <row r="891" ht="15.75" customHeight="1" s="4"/>
+    <row r="892" ht="15.75" customHeight="1" s="4"/>
+    <row r="893" ht="15.75" customHeight="1" s="4"/>
+    <row r="894" ht="15.75" customHeight="1" s="4"/>
+    <row r="895" ht="15.75" customHeight="1" s="4"/>
+    <row r="896" ht="15.75" customHeight="1" s="4"/>
+    <row r="897" ht="15.75" customHeight="1" s="4"/>
+    <row r="898" ht="15.75" customHeight="1" s="4"/>
+    <row r="899" ht="15.75" customHeight="1" s="4"/>
+    <row r="900" ht="15.75" customHeight="1" s="4"/>
+    <row r="901" ht="15.75" customHeight="1" s="4"/>
+    <row r="902" ht="15.75" customHeight="1" s="4"/>
+    <row r="903" ht="15.75" customHeight="1" s="4"/>
+    <row r="904" ht="15.75" customHeight="1" s="4"/>
+    <row r="905" ht="15.75" customHeight="1" s="4"/>
+    <row r="906" ht="15.75" customHeight="1" s="4"/>
+    <row r="907" ht="15.75" customHeight="1" s="4"/>
+    <row r="908" ht="15.75" customHeight="1" s="4"/>
+    <row r="909" ht="15.75" customHeight="1" s="4"/>
+    <row r="910" ht="15.75" customHeight="1" s="4"/>
+    <row r="911" ht="15.75" customHeight="1" s="4"/>
+    <row r="912" ht="15.75" customHeight="1" s="4"/>
+    <row r="913" ht="15.75" customHeight="1" s="4"/>
+    <row r="914" ht="15.75" customHeight="1" s="4"/>
+    <row r="915" ht="15.75" customHeight="1" s="4"/>
+    <row r="916" ht="15.75" customHeight="1" s="4"/>
+    <row r="917" ht="15.75" customHeight="1" s="4"/>
+    <row r="918" ht="15.75" customHeight="1" s="4"/>
+    <row r="919" ht="15.75" customHeight="1" s="4"/>
+    <row r="920" ht="15.75" customHeight="1" s="4"/>
+    <row r="921" ht="15.75" customHeight="1" s="4"/>
+    <row r="922" ht="15.75" customHeight="1" s="4"/>
+    <row r="923" ht="15.75" customHeight="1" s="4"/>
+    <row r="924" ht="15.75" customHeight="1" s="4"/>
+    <row r="925" ht="15.75" customHeight="1" s="4"/>
+    <row r="926" ht="15.75" customHeight="1" s="4"/>
+    <row r="927" ht="15.75" customHeight="1" s="4"/>
+    <row r="928" ht="15.75" customHeight="1" s="4"/>
+    <row r="929" ht="15.75" customHeight="1" s="4"/>
+    <row r="930" ht="15.75" customHeight="1" s="4"/>
+    <row r="931" ht="15.75" customHeight="1" s="4"/>
+    <row r="932" ht="15.75" customHeight="1" s="4"/>
+    <row r="933" ht="15.75" customHeight="1" s="4"/>
+    <row r="934" ht="15.75" customHeight="1" s="4"/>
+    <row r="935" ht="15.75" customHeight="1" s="4"/>
+    <row r="936" ht="15.75" customHeight="1" s="4"/>
+    <row r="937" ht="15.75" customHeight="1" s="4"/>
+    <row r="938" ht="15.75" customHeight="1" s="4"/>
+    <row r="939" ht="15.75" customHeight="1" s="4"/>
+    <row r="940" ht="15.75" customHeight="1" s="4"/>
+    <row r="941" ht="15.75" customHeight="1" s="4"/>
+    <row r="942" ht="15.75" customHeight="1" s="4"/>
+    <row r="943" ht="15.75" customHeight="1" s="4"/>
+    <row r="944" ht="15.75" customHeight="1" s="4"/>
+    <row r="945" ht="15.75" customHeight="1" s="4"/>
+    <row r="946" ht="15.75" customHeight="1" s="4"/>
+    <row r="947" ht="15.75" customHeight="1" s="4"/>
+    <row r="948" ht="15.75" customHeight="1" s="4"/>
+    <row r="949" ht="15.75" customHeight="1" s="4"/>
+    <row r="950" ht="15.75" customHeight="1" s="4"/>
+    <row r="951" ht="15.75" customHeight="1" s="4"/>
+    <row r="952" ht="15.75" customHeight="1" s="4"/>
+    <row r="953" ht="15.75" customHeight="1" s="4"/>
+    <row r="954" ht="15.75" customHeight="1" s="4"/>
+    <row r="955" ht="15.75" customHeight="1" s="4"/>
+    <row r="956" ht="15.75" customHeight="1" s="4"/>
+    <row r="957" ht="15.75" customHeight="1" s="4"/>
+    <row r="958" ht="15.75" customHeight="1" s="4"/>
+    <row r="959" ht="15.75" customHeight="1" s="4"/>
+    <row r="960" ht="15.75" customHeight="1" s="4"/>
+    <row r="961" ht="15.75" customHeight="1" s="4"/>
+    <row r="962" ht="15.75" customHeight="1" s="4"/>
+    <row r="963" ht="15.75" customHeight="1" s="4"/>
+    <row r="964" ht="15.75" customHeight="1" s="4"/>
+    <row r="965" ht="15.75" customHeight="1" s="4"/>
+    <row r="966" ht="15.75" customHeight="1" s="4"/>
+    <row r="967" ht="15.75" customHeight="1" s="4"/>
+    <row r="968" ht="15.75" customHeight="1" s="4"/>
+    <row r="969" ht="15.75" customHeight="1" s="4"/>
+    <row r="970" ht="15.75" customHeight="1" s="4"/>
+    <row r="971" ht="15.75" customHeight="1" s="4"/>
+    <row r="972" ht="15.75" customHeight="1" s="4"/>
+    <row r="973" ht="15.75" customHeight="1" s="4"/>
+    <row r="974" ht="15.75" customHeight="1" s="4"/>
+    <row r="975" ht="15.75" customHeight="1" s="4"/>
+    <row r="976" ht="15.75" customHeight="1" s="4"/>
+    <row r="977" ht="15.75" customHeight="1" s="4"/>
+    <row r="978" ht="15.75" customHeight="1" s="4"/>
+    <row r="979" ht="15.75" customHeight="1" s="4"/>
+    <row r="980" ht="15.75" customHeight="1" s="4"/>
+    <row r="981" ht="15.75" customHeight="1" s="4"/>
+    <row r="982" ht="15.75" customHeight="1" s="4"/>
+    <row r="983" ht="15.75" customHeight="1" s="4"/>
+    <row r="984" ht="15.75" customHeight="1" s="4"/>
+    <row r="985" ht="15.75" customHeight="1" s="4"/>
+    <row r="986" ht="15.75" customHeight="1" s="4"/>
+    <row r="987" ht="15.75" customHeight="1" s="4"/>
+    <row r="988" ht="15.75" customHeight="1" s="4"/>
+    <row r="989" ht="15.75" customHeight="1" s="4"/>
+    <row r="990" ht="15.75" customHeight="1" s="4"/>
+    <row r="991" ht="15.75" customHeight="1" s="4"/>
+    <row r="992" ht="15.75" customHeight="1" s="4"/>
+    <row r="993" ht="15.75" customHeight="1" s="4"/>
+    <row r="994" ht="15.75" customHeight="1" s="4"/>
+    <row r="995" ht="15.75" customHeight="1" s="4"/>
+    <row r="996" ht="15.75" customHeight="1" s="4"/>
+    <row r="997" ht="15.75" customHeight="1" s="4"/>
+    <row r="998" ht="15.75" customHeight="1" s="4"/>
+    <row r="999" ht="15.75" customHeight="1" s="4"/>
+    <row r="1000" ht="15.75" customHeight="1" s="4"/>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation sqref="E2:E103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Northeast,Midwest,South,West,International,Unknown"</formula1>
+    </dataValidation>
     <dataValidation sqref="N2:N103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not yet contacted,Emailed,Emailed - Bounced,Awaiting Reply,Replied,Validated a Hive!,Declined,No Longer Pursuing,Already Tracked Elsewhere"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Northeast,Midwest,South,West,International,Unknown"</formula1>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -7882,10 +8672,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" style="4" min="1" max="1"/>
+    <col width="90" customWidth="1" style="4" min="2" max="2"/>
+    <col width="8.710000000000001" customWidth="1" style="4" min="3" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8012,8 +8803,989 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="15.75" customHeight="1" s="4"/>
+    <row r="22" ht="15.75" customHeight="1" s="4"/>
+    <row r="23" ht="15.75" customHeight="1" s="4"/>
+    <row r="24" ht="15.75" customHeight="1" s="4"/>
+    <row r="25" ht="15.75" customHeight="1" s="4"/>
+    <row r="26" ht="15.75" customHeight="1" s="4"/>
+    <row r="27" ht="15.75" customHeight="1" s="4"/>
+    <row r="28" ht="15.75" customHeight="1" s="4"/>
+    <row r="29" ht="15.75" customHeight="1" s="4"/>
+    <row r="30" ht="15.75" customHeight="1" s="4"/>
+    <row r="31" ht="15.75" customHeight="1" s="4"/>
+    <row r="32" ht="15.75" customHeight="1" s="4"/>
+    <row r="33" ht="15.75" customHeight="1" s="4"/>
+    <row r="34" ht="15.75" customHeight="1" s="4"/>
+    <row r="35" ht="15.75" customHeight="1" s="4"/>
+    <row r="36" ht="15.75" customHeight="1" s="4"/>
+    <row r="37" ht="15.75" customHeight="1" s="4"/>
+    <row r="38" ht="15.75" customHeight="1" s="4"/>
+    <row r="39" ht="15.75" customHeight="1" s="4"/>
+    <row r="40" ht="15.75" customHeight="1" s="4"/>
+    <row r="41" ht="15.75" customHeight="1" s="4"/>
+    <row r="42" ht="15.75" customHeight="1" s="4"/>
+    <row r="43" ht="15.75" customHeight="1" s="4"/>
+    <row r="44" ht="15.75" customHeight="1" s="4"/>
+    <row r="45" ht="15.75" customHeight="1" s="4"/>
+    <row r="46" ht="15.75" customHeight="1" s="4"/>
+    <row r="47" ht="15.75" customHeight="1" s="4"/>
+    <row r="48" ht="15.75" customHeight="1" s="4"/>
+    <row r="49" ht="15.75" customHeight="1" s="4"/>
+    <row r="50" ht="15.75" customHeight="1" s="4"/>
+    <row r="51" ht="15.75" customHeight="1" s="4"/>
+    <row r="52" ht="15.75" customHeight="1" s="4"/>
+    <row r="53" ht="15.75" customHeight="1" s="4"/>
+    <row r="54" ht="15.75" customHeight="1" s="4"/>
+    <row r="55" ht="15.75" customHeight="1" s="4"/>
+    <row r="56" ht="15.75" customHeight="1" s="4"/>
+    <row r="57" ht="15.75" customHeight="1" s="4"/>
+    <row r="58" ht="15.75" customHeight="1" s="4"/>
+    <row r="59" ht="15.75" customHeight="1" s="4"/>
+    <row r="60" ht="15.75" customHeight="1" s="4"/>
+    <row r="61" ht="15.75" customHeight="1" s="4"/>
+    <row r="62" ht="15.75" customHeight="1" s="4"/>
+    <row r="63" ht="15.75" customHeight="1" s="4"/>
+    <row r="64" ht="15.75" customHeight="1" s="4"/>
+    <row r="65" ht="15.75" customHeight="1" s="4"/>
+    <row r="66" ht="15.75" customHeight="1" s="4"/>
+    <row r="67" ht="15.75" customHeight="1" s="4"/>
+    <row r="68" ht="15.75" customHeight="1" s="4"/>
+    <row r="69" ht="15.75" customHeight="1" s="4"/>
+    <row r="70" ht="15.75" customHeight="1" s="4"/>
+    <row r="71" ht="15.75" customHeight="1" s="4"/>
+    <row r="72" ht="15.75" customHeight="1" s="4"/>
+    <row r="73" ht="15.75" customHeight="1" s="4"/>
+    <row r="74" ht="15.75" customHeight="1" s="4"/>
+    <row r="75" ht="15.75" customHeight="1" s="4"/>
+    <row r="76" ht="15.75" customHeight="1" s="4"/>
+    <row r="77" ht="15.75" customHeight="1" s="4"/>
+    <row r="78" ht="15.75" customHeight="1" s="4"/>
+    <row r="79" ht="15.75" customHeight="1" s="4"/>
+    <row r="80" ht="15.75" customHeight="1" s="4"/>
+    <row r="81" ht="15.75" customHeight="1" s="4"/>
+    <row r="82" ht="15.75" customHeight="1" s="4"/>
+    <row r="83" ht="15.75" customHeight="1" s="4"/>
+    <row r="84" ht="15.75" customHeight="1" s="4"/>
+    <row r="85" ht="15.75" customHeight="1" s="4"/>
+    <row r="86" ht="15.75" customHeight="1" s="4"/>
+    <row r="87" ht="15.75" customHeight="1" s="4"/>
+    <row r="88" ht="15.75" customHeight="1" s="4"/>
+    <row r="89" ht="15.75" customHeight="1" s="4"/>
+    <row r="90" ht="15.75" customHeight="1" s="4"/>
+    <row r="91" ht="15.75" customHeight="1" s="4"/>
+    <row r="92" ht="15.75" customHeight="1" s="4"/>
+    <row r="93" ht="15.75" customHeight="1" s="4"/>
+    <row r="94" ht="15.75" customHeight="1" s="4"/>
+    <row r="95" ht="15.75" customHeight="1" s="4"/>
+    <row r="96" ht="15.75" customHeight="1" s="4"/>
+    <row r="97" ht="15.75" customHeight="1" s="4"/>
+    <row r="98" ht="15.75" customHeight="1" s="4"/>
+    <row r="99" ht="15.75" customHeight="1" s="4"/>
+    <row r="100" ht="15.75" customHeight="1" s="4"/>
+    <row r="101" ht="15.75" customHeight="1" s="4"/>
+    <row r="102" ht="15.75" customHeight="1" s="4"/>
+    <row r="103" ht="15.75" customHeight="1" s="4"/>
+    <row r="104" ht="15.75" customHeight="1" s="4"/>
+    <row r="105" ht="15.75" customHeight="1" s="4"/>
+    <row r="106" ht="15.75" customHeight="1" s="4"/>
+    <row r="107" ht="15.75" customHeight="1" s="4"/>
+    <row r="108" ht="15.75" customHeight="1" s="4"/>
+    <row r="109" ht="15.75" customHeight="1" s="4"/>
+    <row r="110" ht="15.75" customHeight="1" s="4"/>
+    <row r="111" ht="15.75" customHeight="1" s="4"/>
+    <row r="112" ht="15.75" customHeight="1" s="4"/>
+    <row r="113" ht="15.75" customHeight="1" s="4"/>
+    <row r="114" ht="15.75" customHeight="1" s="4"/>
+    <row r="115" ht="15.75" customHeight="1" s="4"/>
+    <row r="116" ht="15.75" customHeight="1" s="4"/>
+    <row r="117" ht="15.75" customHeight="1" s="4"/>
+    <row r="118" ht="15.75" customHeight="1" s="4"/>
+    <row r="119" ht="15.75" customHeight="1" s="4"/>
+    <row r="120" ht="15.75" customHeight="1" s="4"/>
+    <row r="121" ht="15.75" customHeight="1" s="4"/>
+    <row r="122" ht="15.75" customHeight="1" s="4"/>
+    <row r="123" ht="15.75" customHeight="1" s="4"/>
+    <row r="124" ht="15.75" customHeight="1" s="4"/>
+    <row r="125" ht="15.75" customHeight="1" s="4"/>
+    <row r="126" ht="15.75" customHeight="1" s="4"/>
+    <row r="127" ht="15.75" customHeight="1" s="4"/>
+    <row r="128" ht="15.75" customHeight="1" s="4"/>
+    <row r="129" ht="15.75" customHeight="1" s="4"/>
+    <row r="130" ht="15.75" customHeight="1" s="4"/>
+    <row r="131" ht="15.75" customHeight="1" s="4"/>
+    <row r="132" ht="15.75" customHeight="1" s="4"/>
+    <row r="133" ht="15.75" customHeight="1" s="4"/>
+    <row r="134" ht="15.75" customHeight="1" s="4"/>
+    <row r="135" ht="15.75" customHeight="1" s="4"/>
+    <row r="136" ht="15.75" customHeight="1" s="4"/>
+    <row r="137" ht="15.75" customHeight="1" s="4"/>
+    <row r="138" ht="15.75" customHeight="1" s="4"/>
+    <row r="139" ht="15.75" customHeight="1" s="4"/>
+    <row r="140" ht="15.75" customHeight="1" s="4"/>
+    <row r="141" ht="15.75" customHeight="1" s="4"/>
+    <row r="142" ht="15.75" customHeight="1" s="4"/>
+    <row r="143" ht="15.75" customHeight="1" s="4"/>
+    <row r="144" ht="15.75" customHeight="1" s="4"/>
+    <row r="145" ht="15.75" customHeight="1" s="4"/>
+    <row r="146" ht="15.75" customHeight="1" s="4"/>
+    <row r="147" ht="15.75" customHeight="1" s="4"/>
+    <row r="148" ht="15.75" customHeight="1" s="4"/>
+    <row r="149" ht="15.75" customHeight="1" s="4"/>
+    <row r="150" ht="15.75" customHeight="1" s="4"/>
+    <row r="151" ht="15.75" customHeight="1" s="4"/>
+    <row r="152" ht="15.75" customHeight="1" s="4"/>
+    <row r="153" ht="15.75" customHeight="1" s="4"/>
+    <row r="154" ht="15.75" customHeight="1" s="4"/>
+    <row r="155" ht="15.75" customHeight="1" s="4"/>
+    <row r="156" ht="15.75" customHeight="1" s="4"/>
+    <row r="157" ht="15.75" customHeight="1" s="4"/>
+    <row r="158" ht="15.75" customHeight="1" s="4"/>
+    <row r="159" ht="15.75" customHeight="1" s="4"/>
+    <row r="160" ht="15.75" customHeight="1" s="4"/>
+    <row r="161" ht="15.75" customHeight="1" s="4"/>
+    <row r="162" ht="15.75" customHeight="1" s="4"/>
+    <row r="163" ht="15.75" customHeight="1" s="4"/>
+    <row r="164" ht="15.75" customHeight="1" s="4"/>
+    <row r="165" ht="15.75" customHeight="1" s="4"/>
+    <row r="166" ht="15.75" customHeight="1" s="4"/>
+    <row r="167" ht="15.75" customHeight="1" s="4"/>
+    <row r="168" ht="15.75" customHeight="1" s="4"/>
+    <row r="169" ht="15.75" customHeight="1" s="4"/>
+    <row r="170" ht="15.75" customHeight="1" s="4"/>
+    <row r="171" ht="15.75" customHeight="1" s="4"/>
+    <row r="172" ht="15.75" customHeight="1" s="4"/>
+    <row r="173" ht="15.75" customHeight="1" s="4"/>
+    <row r="174" ht="15.75" customHeight="1" s="4"/>
+    <row r="175" ht="15.75" customHeight="1" s="4"/>
+    <row r="176" ht="15.75" customHeight="1" s="4"/>
+    <row r="177" ht="15.75" customHeight="1" s="4"/>
+    <row r="178" ht="15.75" customHeight="1" s="4"/>
+    <row r="179" ht="15.75" customHeight="1" s="4"/>
+    <row r="180" ht="15.75" customHeight="1" s="4"/>
+    <row r="181" ht="15.75" customHeight="1" s="4"/>
+    <row r="182" ht="15.75" customHeight="1" s="4"/>
+    <row r="183" ht="15.75" customHeight="1" s="4"/>
+    <row r="184" ht="15.75" customHeight="1" s="4"/>
+    <row r="185" ht="15.75" customHeight="1" s="4"/>
+    <row r="186" ht="15.75" customHeight="1" s="4"/>
+    <row r="187" ht="15.75" customHeight="1" s="4"/>
+    <row r="188" ht="15.75" customHeight="1" s="4"/>
+    <row r="189" ht="15.75" customHeight="1" s="4"/>
+    <row r="190" ht="15.75" customHeight="1" s="4"/>
+    <row r="191" ht="15.75" customHeight="1" s="4"/>
+    <row r="192" ht="15.75" customHeight="1" s="4"/>
+    <row r="193" ht="15.75" customHeight="1" s="4"/>
+    <row r="194" ht="15.75" customHeight="1" s="4"/>
+    <row r="195" ht="15.75" customHeight="1" s="4"/>
+    <row r="196" ht="15.75" customHeight="1" s="4"/>
+    <row r="197" ht="15.75" customHeight="1" s="4"/>
+    <row r="198" ht="15.75" customHeight="1" s="4"/>
+    <row r="199" ht="15.75" customHeight="1" s="4"/>
+    <row r="200" ht="15.75" customHeight="1" s="4"/>
+    <row r="201" ht="15.75" customHeight="1" s="4"/>
+    <row r="202" ht="15.75" customHeight="1" s="4"/>
+    <row r="203" ht="15.75" customHeight="1" s="4"/>
+    <row r="204" ht="15.75" customHeight="1" s="4"/>
+    <row r="205" ht="15.75" customHeight="1" s="4"/>
+    <row r="206" ht="15.75" customHeight="1" s="4"/>
+    <row r="207" ht="15.75" customHeight="1" s="4"/>
+    <row r="208" ht="15.75" customHeight="1" s="4"/>
+    <row r="209" ht="15.75" customHeight="1" s="4"/>
+    <row r="210" ht="15.75" customHeight="1" s="4"/>
+    <row r="211" ht="15.75" customHeight="1" s="4"/>
+    <row r="212" ht="15.75" customHeight="1" s="4"/>
+    <row r="213" ht="15.75" customHeight="1" s="4"/>
+    <row r="214" ht="15.75" customHeight="1" s="4"/>
+    <row r="215" ht="15.75" customHeight="1" s="4"/>
+    <row r="216" ht="15.75" customHeight="1" s="4"/>
+    <row r="217" ht="15.75" customHeight="1" s="4"/>
+    <row r="218" ht="15.75" customHeight="1" s="4"/>
+    <row r="219" ht="15.75" customHeight="1" s="4"/>
+    <row r="220" ht="15.75" customHeight="1" s="4"/>
+    <row r="221" ht="15.75" customHeight="1" s="4"/>
+    <row r="222" ht="15.75" customHeight="1" s="4"/>
+    <row r="223" ht="15.75" customHeight="1" s="4"/>
+    <row r="224" ht="15.75" customHeight="1" s="4"/>
+    <row r="225" ht="15.75" customHeight="1" s="4"/>
+    <row r="226" ht="15.75" customHeight="1" s="4"/>
+    <row r="227" ht="15.75" customHeight="1" s="4"/>
+    <row r="228" ht="15.75" customHeight="1" s="4"/>
+    <row r="229" ht="15.75" customHeight="1" s="4"/>
+    <row r="230" ht="15.75" customHeight="1" s="4"/>
+    <row r="231" ht="15.75" customHeight="1" s="4"/>
+    <row r="232" ht="15.75" customHeight="1" s="4"/>
+    <row r="233" ht="15.75" customHeight="1" s="4"/>
+    <row r="234" ht="15.75" customHeight="1" s="4"/>
+    <row r="235" ht="15.75" customHeight="1" s="4"/>
+    <row r="236" ht="15.75" customHeight="1" s="4"/>
+    <row r="237" ht="15.75" customHeight="1" s="4"/>
+    <row r="238" ht="15.75" customHeight="1" s="4"/>
+    <row r="239" ht="15.75" customHeight="1" s="4"/>
+    <row r="240" ht="15.75" customHeight="1" s="4"/>
+    <row r="241" ht="15.75" customHeight="1" s="4"/>
+    <row r="242" ht="15.75" customHeight="1" s="4"/>
+    <row r="243" ht="15.75" customHeight="1" s="4"/>
+    <row r="244" ht="15.75" customHeight="1" s="4"/>
+    <row r="245" ht="15.75" customHeight="1" s="4"/>
+    <row r="246" ht="15.75" customHeight="1" s="4"/>
+    <row r="247" ht="15.75" customHeight="1" s="4"/>
+    <row r="248" ht="15.75" customHeight="1" s="4"/>
+    <row r="249" ht="15.75" customHeight="1" s="4"/>
+    <row r="250" ht="15.75" customHeight="1" s="4"/>
+    <row r="251" ht="15.75" customHeight="1" s="4"/>
+    <row r="252" ht="15.75" customHeight="1" s="4"/>
+    <row r="253" ht="15.75" customHeight="1" s="4"/>
+    <row r="254" ht="15.75" customHeight="1" s="4"/>
+    <row r="255" ht="15.75" customHeight="1" s="4"/>
+    <row r="256" ht="15.75" customHeight="1" s="4"/>
+    <row r="257" ht="15.75" customHeight="1" s="4"/>
+    <row r="258" ht="15.75" customHeight="1" s="4"/>
+    <row r="259" ht="15.75" customHeight="1" s="4"/>
+    <row r="260" ht="15.75" customHeight="1" s="4"/>
+    <row r="261" ht="15.75" customHeight="1" s="4"/>
+    <row r="262" ht="15.75" customHeight="1" s="4"/>
+    <row r="263" ht="15.75" customHeight="1" s="4"/>
+    <row r="264" ht="15.75" customHeight="1" s="4"/>
+    <row r="265" ht="15.75" customHeight="1" s="4"/>
+    <row r="266" ht="15.75" customHeight="1" s="4"/>
+    <row r="267" ht="15.75" customHeight="1" s="4"/>
+    <row r="268" ht="15.75" customHeight="1" s="4"/>
+    <row r="269" ht="15.75" customHeight="1" s="4"/>
+    <row r="270" ht="15.75" customHeight="1" s="4"/>
+    <row r="271" ht="15.75" customHeight="1" s="4"/>
+    <row r="272" ht="15.75" customHeight="1" s="4"/>
+    <row r="273" ht="15.75" customHeight="1" s="4"/>
+    <row r="274" ht="15.75" customHeight="1" s="4"/>
+    <row r="275" ht="15.75" customHeight="1" s="4"/>
+    <row r="276" ht="15.75" customHeight="1" s="4"/>
+    <row r="277" ht="15.75" customHeight="1" s="4"/>
+    <row r="278" ht="15.75" customHeight="1" s="4"/>
+    <row r="279" ht="15.75" customHeight="1" s="4"/>
+    <row r="280" ht="15.75" customHeight="1" s="4"/>
+    <row r="281" ht="15.75" customHeight="1" s="4"/>
+    <row r="282" ht="15.75" customHeight="1" s="4"/>
+    <row r="283" ht="15.75" customHeight="1" s="4"/>
+    <row r="284" ht="15.75" customHeight="1" s="4"/>
+    <row r="285" ht="15.75" customHeight="1" s="4"/>
+    <row r="286" ht="15.75" customHeight="1" s="4"/>
+    <row r="287" ht="15.75" customHeight="1" s="4"/>
+    <row r="288" ht="15.75" customHeight="1" s="4"/>
+    <row r="289" ht="15.75" customHeight="1" s="4"/>
+    <row r="290" ht="15.75" customHeight="1" s="4"/>
+    <row r="291" ht="15.75" customHeight="1" s="4"/>
+    <row r="292" ht="15.75" customHeight="1" s="4"/>
+    <row r="293" ht="15.75" customHeight="1" s="4"/>
+    <row r="294" ht="15.75" customHeight="1" s="4"/>
+    <row r="295" ht="15.75" customHeight="1" s="4"/>
+    <row r="296" ht="15.75" customHeight="1" s="4"/>
+    <row r="297" ht="15.75" customHeight="1" s="4"/>
+    <row r="298" ht="15.75" customHeight="1" s="4"/>
+    <row r="299" ht="15.75" customHeight="1" s="4"/>
+    <row r="300" ht="15.75" customHeight="1" s="4"/>
+    <row r="301" ht="15.75" customHeight="1" s="4"/>
+    <row r="302" ht="15.75" customHeight="1" s="4"/>
+    <row r="303" ht="15.75" customHeight="1" s="4"/>
+    <row r="304" ht="15.75" customHeight="1" s="4"/>
+    <row r="305" ht="15.75" customHeight="1" s="4"/>
+    <row r="306" ht="15.75" customHeight="1" s="4"/>
+    <row r="307" ht="15.75" customHeight="1" s="4"/>
+    <row r="308" ht="15.75" customHeight="1" s="4"/>
+    <row r="309" ht="15.75" customHeight="1" s="4"/>
+    <row r="310" ht="15.75" customHeight="1" s="4"/>
+    <row r="311" ht="15.75" customHeight="1" s="4"/>
+    <row r="312" ht="15.75" customHeight="1" s="4"/>
+    <row r="313" ht="15.75" customHeight="1" s="4"/>
+    <row r="314" ht="15.75" customHeight="1" s="4"/>
+    <row r="315" ht="15.75" customHeight="1" s="4"/>
+    <row r="316" ht="15.75" customHeight="1" s="4"/>
+    <row r="317" ht="15.75" customHeight="1" s="4"/>
+    <row r="318" ht="15.75" customHeight="1" s="4"/>
+    <row r="319" ht="15.75" customHeight="1" s="4"/>
+    <row r="320" ht="15.75" customHeight="1" s="4"/>
+    <row r="321" ht="15.75" customHeight="1" s="4"/>
+    <row r="322" ht="15.75" customHeight="1" s="4"/>
+    <row r="323" ht="15.75" customHeight="1" s="4"/>
+    <row r="324" ht="15.75" customHeight="1" s="4"/>
+    <row r="325" ht="15.75" customHeight="1" s="4"/>
+    <row r="326" ht="15.75" customHeight="1" s="4"/>
+    <row r="327" ht="15.75" customHeight="1" s="4"/>
+    <row r="328" ht="15.75" customHeight="1" s="4"/>
+    <row r="329" ht="15.75" customHeight="1" s="4"/>
+    <row r="330" ht="15.75" customHeight="1" s="4"/>
+    <row r="331" ht="15.75" customHeight="1" s="4"/>
+    <row r="332" ht="15.75" customHeight="1" s="4"/>
+    <row r="333" ht="15.75" customHeight="1" s="4"/>
+    <row r="334" ht="15.75" customHeight="1" s="4"/>
+    <row r="335" ht="15.75" customHeight="1" s="4"/>
+    <row r="336" ht="15.75" customHeight="1" s="4"/>
+    <row r="337" ht="15.75" customHeight="1" s="4"/>
+    <row r="338" ht="15.75" customHeight="1" s="4"/>
+    <row r="339" ht="15.75" customHeight="1" s="4"/>
+    <row r="340" ht="15.75" customHeight="1" s="4"/>
+    <row r="341" ht="15.75" customHeight="1" s="4"/>
+    <row r="342" ht="15.75" customHeight="1" s="4"/>
+    <row r="343" ht="15.75" customHeight="1" s="4"/>
+    <row r="344" ht="15.75" customHeight="1" s="4"/>
+    <row r="345" ht="15.75" customHeight="1" s="4"/>
+    <row r="346" ht="15.75" customHeight="1" s="4"/>
+    <row r="347" ht="15.75" customHeight="1" s="4"/>
+    <row r="348" ht="15.75" customHeight="1" s="4"/>
+    <row r="349" ht="15.75" customHeight="1" s="4"/>
+    <row r="350" ht="15.75" customHeight="1" s="4"/>
+    <row r="351" ht="15.75" customHeight="1" s="4"/>
+    <row r="352" ht="15.75" customHeight="1" s="4"/>
+    <row r="353" ht="15.75" customHeight="1" s="4"/>
+    <row r="354" ht="15.75" customHeight="1" s="4"/>
+    <row r="355" ht="15.75" customHeight="1" s="4"/>
+    <row r="356" ht="15.75" customHeight="1" s="4"/>
+    <row r="357" ht="15.75" customHeight="1" s="4"/>
+    <row r="358" ht="15.75" customHeight="1" s="4"/>
+    <row r="359" ht="15.75" customHeight="1" s="4"/>
+    <row r="360" ht="15.75" customHeight="1" s="4"/>
+    <row r="361" ht="15.75" customHeight="1" s="4"/>
+    <row r="362" ht="15.75" customHeight="1" s="4"/>
+    <row r="363" ht="15.75" customHeight="1" s="4"/>
+    <row r="364" ht="15.75" customHeight="1" s="4"/>
+    <row r="365" ht="15.75" customHeight="1" s="4"/>
+    <row r="366" ht="15.75" customHeight="1" s="4"/>
+    <row r="367" ht="15.75" customHeight="1" s="4"/>
+    <row r="368" ht="15.75" customHeight="1" s="4"/>
+    <row r="369" ht="15.75" customHeight="1" s="4"/>
+    <row r="370" ht="15.75" customHeight="1" s="4"/>
+    <row r="371" ht="15.75" customHeight="1" s="4"/>
+    <row r="372" ht="15.75" customHeight="1" s="4"/>
+    <row r="373" ht="15.75" customHeight="1" s="4"/>
+    <row r="374" ht="15.75" customHeight="1" s="4"/>
+    <row r="375" ht="15.75" customHeight="1" s="4"/>
+    <row r="376" ht="15.75" customHeight="1" s="4"/>
+    <row r="377" ht="15.75" customHeight="1" s="4"/>
+    <row r="378" ht="15.75" customHeight="1" s="4"/>
+    <row r="379" ht="15.75" customHeight="1" s="4"/>
+    <row r="380" ht="15.75" customHeight="1" s="4"/>
+    <row r="381" ht="15.75" customHeight="1" s="4"/>
+    <row r="382" ht="15.75" customHeight="1" s="4"/>
+    <row r="383" ht="15.75" customHeight="1" s="4"/>
+    <row r="384" ht="15.75" customHeight="1" s="4"/>
+    <row r="385" ht="15.75" customHeight="1" s="4"/>
+    <row r="386" ht="15.75" customHeight="1" s="4"/>
+    <row r="387" ht="15.75" customHeight="1" s="4"/>
+    <row r="388" ht="15.75" customHeight="1" s="4"/>
+    <row r="389" ht="15.75" customHeight="1" s="4"/>
+    <row r="390" ht="15.75" customHeight="1" s="4"/>
+    <row r="391" ht="15.75" customHeight="1" s="4"/>
+    <row r="392" ht="15.75" customHeight="1" s="4"/>
+    <row r="393" ht="15.75" customHeight="1" s="4"/>
+    <row r="394" ht="15.75" customHeight="1" s="4"/>
+    <row r="395" ht="15.75" customHeight="1" s="4"/>
+    <row r="396" ht="15.75" customHeight="1" s="4"/>
+    <row r="397" ht="15.75" customHeight="1" s="4"/>
+    <row r="398" ht="15.75" customHeight="1" s="4"/>
+    <row r="399" ht="15.75" customHeight="1" s="4"/>
+    <row r="400" ht="15.75" customHeight="1" s="4"/>
+    <row r="401" ht="15.75" customHeight="1" s="4"/>
+    <row r="402" ht="15.75" customHeight="1" s="4"/>
+    <row r="403" ht="15.75" customHeight="1" s="4"/>
+    <row r="404" ht="15.75" customHeight="1" s="4"/>
+    <row r="405" ht="15.75" customHeight="1" s="4"/>
+    <row r="406" ht="15.75" customHeight="1" s="4"/>
+    <row r="407" ht="15.75" customHeight="1" s="4"/>
+    <row r="408" ht="15.75" customHeight="1" s="4"/>
+    <row r="409" ht="15.75" customHeight="1" s="4"/>
+    <row r="410" ht="15.75" customHeight="1" s="4"/>
+    <row r="411" ht="15.75" customHeight="1" s="4"/>
+    <row r="412" ht="15.75" customHeight="1" s="4"/>
+    <row r="413" ht="15.75" customHeight="1" s="4"/>
+    <row r="414" ht="15.75" customHeight="1" s="4"/>
+    <row r="415" ht="15.75" customHeight="1" s="4"/>
+    <row r="416" ht="15.75" customHeight="1" s="4"/>
+    <row r="417" ht="15.75" customHeight="1" s="4"/>
+    <row r="418" ht="15.75" customHeight="1" s="4"/>
+    <row r="419" ht="15.75" customHeight="1" s="4"/>
+    <row r="420" ht="15.75" customHeight="1" s="4"/>
+    <row r="421" ht="15.75" customHeight="1" s="4"/>
+    <row r="422" ht="15.75" customHeight="1" s="4"/>
+    <row r="423" ht="15.75" customHeight="1" s="4"/>
+    <row r="424" ht="15.75" customHeight="1" s="4"/>
+    <row r="425" ht="15.75" customHeight="1" s="4"/>
+    <row r="426" ht="15.75" customHeight="1" s="4"/>
+    <row r="427" ht="15.75" customHeight="1" s="4"/>
+    <row r="428" ht="15.75" customHeight="1" s="4"/>
+    <row r="429" ht="15.75" customHeight="1" s="4"/>
+    <row r="430" ht="15.75" customHeight="1" s="4"/>
+    <row r="431" ht="15.75" customHeight="1" s="4"/>
+    <row r="432" ht="15.75" customHeight="1" s="4"/>
+    <row r="433" ht="15.75" customHeight="1" s="4"/>
+    <row r="434" ht="15.75" customHeight="1" s="4"/>
+    <row r="435" ht="15.75" customHeight="1" s="4"/>
+    <row r="436" ht="15.75" customHeight="1" s="4"/>
+    <row r="437" ht="15.75" customHeight="1" s="4"/>
+    <row r="438" ht="15.75" customHeight="1" s="4"/>
+    <row r="439" ht="15.75" customHeight="1" s="4"/>
+    <row r="440" ht="15.75" customHeight="1" s="4"/>
+    <row r="441" ht="15.75" customHeight="1" s="4"/>
+    <row r="442" ht="15.75" customHeight="1" s="4"/>
+    <row r="443" ht="15.75" customHeight="1" s="4"/>
+    <row r="444" ht="15.75" customHeight="1" s="4"/>
+    <row r="445" ht="15.75" customHeight="1" s="4"/>
+    <row r="446" ht="15.75" customHeight="1" s="4"/>
+    <row r="447" ht="15.75" customHeight="1" s="4"/>
+    <row r="448" ht="15.75" customHeight="1" s="4"/>
+    <row r="449" ht="15.75" customHeight="1" s="4"/>
+    <row r="450" ht="15.75" customHeight="1" s="4"/>
+    <row r="451" ht="15.75" customHeight="1" s="4"/>
+    <row r="452" ht="15.75" customHeight="1" s="4"/>
+    <row r="453" ht="15.75" customHeight="1" s="4"/>
+    <row r="454" ht="15.75" customHeight="1" s="4"/>
+    <row r="455" ht="15.75" customHeight="1" s="4"/>
+    <row r="456" ht="15.75" customHeight="1" s="4"/>
+    <row r="457" ht="15.75" customHeight="1" s="4"/>
+    <row r="458" ht="15.75" customHeight="1" s="4"/>
+    <row r="459" ht="15.75" customHeight="1" s="4"/>
+    <row r="460" ht="15.75" customHeight="1" s="4"/>
+    <row r="461" ht="15.75" customHeight="1" s="4"/>
+    <row r="462" ht="15.75" customHeight="1" s="4"/>
+    <row r="463" ht="15.75" customHeight="1" s="4"/>
+    <row r="464" ht="15.75" customHeight="1" s="4"/>
+    <row r="465" ht="15.75" customHeight="1" s="4"/>
+    <row r="466" ht="15.75" customHeight="1" s="4"/>
+    <row r="467" ht="15.75" customHeight="1" s="4"/>
+    <row r="468" ht="15.75" customHeight="1" s="4"/>
+    <row r="469" ht="15.75" customHeight="1" s="4"/>
+    <row r="470" ht="15.75" customHeight="1" s="4"/>
+    <row r="471" ht="15.75" customHeight="1" s="4"/>
+    <row r="472" ht="15.75" customHeight="1" s="4"/>
+    <row r="473" ht="15.75" customHeight="1" s="4"/>
+    <row r="474" ht="15.75" customHeight="1" s="4"/>
+    <row r="475" ht="15.75" customHeight="1" s="4"/>
+    <row r="476" ht="15.75" customHeight="1" s="4"/>
+    <row r="477" ht="15.75" customHeight="1" s="4"/>
+    <row r="478" ht="15.75" customHeight="1" s="4"/>
+    <row r="479" ht="15.75" customHeight="1" s="4"/>
+    <row r="480" ht="15.75" customHeight="1" s="4"/>
+    <row r="481" ht="15.75" customHeight="1" s="4"/>
+    <row r="482" ht="15.75" customHeight="1" s="4"/>
+    <row r="483" ht="15.75" customHeight="1" s="4"/>
+    <row r="484" ht="15.75" customHeight="1" s="4"/>
+    <row r="485" ht="15.75" customHeight="1" s="4"/>
+    <row r="486" ht="15.75" customHeight="1" s="4"/>
+    <row r="487" ht="15.75" customHeight="1" s="4"/>
+    <row r="488" ht="15.75" customHeight="1" s="4"/>
+    <row r="489" ht="15.75" customHeight="1" s="4"/>
+    <row r="490" ht="15.75" customHeight="1" s="4"/>
+    <row r="491" ht="15.75" customHeight="1" s="4"/>
+    <row r="492" ht="15.75" customHeight="1" s="4"/>
+    <row r="493" ht="15.75" customHeight="1" s="4"/>
+    <row r="494" ht="15.75" customHeight="1" s="4"/>
+    <row r="495" ht="15.75" customHeight="1" s="4"/>
+    <row r="496" ht="15.75" customHeight="1" s="4"/>
+    <row r="497" ht="15.75" customHeight="1" s="4"/>
+    <row r="498" ht="15.75" customHeight="1" s="4"/>
+    <row r="499" ht="15.75" customHeight="1" s="4"/>
+    <row r="500" ht="15.75" customHeight="1" s="4"/>
+    <row r="501" ht="15.75" customHeight="1" s="4"/>
+    <row r="502" ht="15.75" customHeight="1" s="4"/>
+    <row r="503" ht="15.75" customHeight="1" s="4"/>
+    <row r="504" ht="15.75" customHeight="1" s="4"/>
+    <row r="505" ht="15.75" customHeight="1" s="4"/>
+    <row r="506" ht="15.75" customHeight="1" s="4"/>
+    <row r="507" ht="15.75" customHeight="1" s="4"/>
+    <row r="508" ht="15.75" customHeight="1" s="4"/>
+    <row r="509" ht="15.75" customHeight="1" s="4"/>
+    <row r="510" ht="15.75" customHeight="1" s="4"/>
+    <row r="511" ht="15.75" customHeight="1" s="4"/>
+    <row r="512" ht="15.75" customHeight="1" s="4"/>
+    <row r="513" ht="15.75" customHeight="1" s="4"/>
+    <row r="514" ht="15.75" customHeight="1" s="4"/>
+    <row r="515" ht="15.75" customHeight="1" s="4"/>
+    <row r="516" ht="15.75" customHeight="1" s="4"/>
+    <row r="517" ht="15.75" customHeight="1" s="4"/>
+    <row r="518" ht="15.75" customHeight="1" s="4"/>
+    <row r="519" ht="15.75" customHeight="1" s="4"/>
+    <row r="520" ht="15.75" customHeight="1" s="4"/>
+    <row r="521" ht="15.75" customHeight="1" s="4"/>
+    <row r="522" ht="15.75" customHeight="1" s="4"/>
+    <row r="523" ht="15.75" customHeight="1" s="4"/>
+    <row r="524" ht="15.75" customHeight="1" s="4"/>
+    <row r="525" ht="15.75" customHeight="1" s="4"/>
+    <row r="526" ht="15.75" customHeight="1" s="4"/>
+    <row r="527" ht="15.75" customHeight="1" s="4"/>
+    <row r="528" ht="15.75" customHeight="1" s="4"/>
+    <row r="529" ht="15.75" customHeight="1" s="4"/>
+    <row r="530" ht="15.75" customHeight="1" s="4"/>
+    <row r="531" ht="15.75" customHeight="1" s="4"/>
+    <row r="532" ht="15.75" customHeight="1" s="4"/>
+    <row r="533" ht="15.75" customHeight="1" s="4"/>
+    <row r="534" ht="15.75" customHeight="1" s="4"/>
+    <row r="535" ht="15.75" customHeight="1" s="4"/>
+    <row r="536" ht="15.75" customHeight="1" s="4"/>
+    <row r="537" ht="15.75" customHeight="1" s="4"/>
+    <row r="538" ht="15.75" customHeight="1" s="4"/>
+    <row r="539" ht="15.75" customHeight="1" s="4"/>
+    <row r="540" ht="15.75" customHeight="1" s="4"/>
+    <row r="541" ht="15.75" customHeight="1" s="4"/>
+    <row r="542" ht="15.75" customHeight="1" s="4"/>
+    <row r="543" ht="15.75" customHeight="1" s="4"/>
+    <row r="544" ht="15.75" customHeight="1" s="4"/>
+    <row r="545" ht="15.75" customHeight="1" s="4"/>
+    <row r="546" ht="15.75" customHeight="1" s="4"/>
+    <row r="547" ht="15.75" customHeight="1" s="4"/>
+    <row r="548" ht="15.75" customHeight="1" s="4"/>
+    <row r="549" ht="15.75" customHeight="1" s="4"/>
+    <row r="550" ht="15.75" customHeight="1" s="4"/>
+    <row r="551" ht="15.75" customHeight="1" s="4"/>
+    <row r="552" ht="15.75" customHeight="1" s="4"/>
+    <row r="553" ht="15.75" customHeight="1" s="4"/>
+    <row r="554" ht="15.75" customHeight="1" s="4"/>
+    <row r="555" ht="15.75" customHeight="1" s="4"/>
+    <row r="556" ht="15.75" customHeight="1" s="4"/>
+    <row r="557" ht="15.75" customHeight="1" s="4"/>
+    <row r="558" ht="15.75" customHeight="1" s="4"/>
+    <row r="559" ht="15.75" customHeight="1" s="4"/>
+    <row r="560" ht="15.75" customHeight="1" s="4"/>
+    <row r="561" ht="15.75" customHeight="1" s="4"/>
+    <row r="562" ht="15.75" customHeight="1" s="4"/>
+    <row r="563" ht="15.75" customHeight="1" s="4"/>
+    <row r="564" ht="15.75" customHeight="1" s="4"/>
+    <row r="565" ht="15.75" customHeight="1" s="4"/>
+    <row r="566" ht="15.75" customHeight="1" s="4"/>
+    <row r="567" ht="15.75" customHeight="1" s="4"/>
+    <row r="568" ht="15.75" customHeight="1" s="4"/>
+    <row r="569" ht="15.75" customHeight="1" s="4"/>
+    <row r="570" ht="15.75" customHeight="1" s="4"/>
+    <row r="571" ht="15.75" customHeight="1" s="4"/>
+    <row r="572" ht="15.75" customHeight="1" s="4"/>
+    <row r="573" ht="15.75" customHeight="1" s="4"/>
+    <row r="574" ht="15.75" customHeight="1" s="4"/>
+    <row r="575" ht="15.75" customHeight="1" s="4"/>
+    <row r="576" ht="15.75" customHeight="1" s="4"/>
+    <row r="577" ht="15.75" customHeight="1" s="4"/>
+    <row r="578" ht="15.75" customHeight="1" s="4"/>
+    <row r="579" ht="15.75" customHeight="1" s="4"/>
+    <row r="580" ht="15.75" customHeight="1" s="4"/>
+    <row r="581" ht="15.75" customHeight="1" s="4"/>
+    <row r="582" ht="15.75" customHeight="1" s="4"/>
+    <row r="583" ht="15.75" customHeight="1" s="4"/>
+    <row r="584" ht="15.75" customHeight="1" s="4"/>
+    <row r="585" ht="15.75" customHeight="1" s="4"/>
+    <row r="586" ht="15.75" customHeight="1" s="4"/>
+    <row r="587" ht="15.75" customHeight="1" s="4"/>
+    <row r="588" ht="15.75" customHeight="1" s="4"/>
+    <row r="589" ht="15.75" customHeight="1" s="4"/>
+    <row r="590" ht="15.75" customHeight="1" s="4"/>
+    <row r="591" ht="15.75" customHeight="1" s="4"/>
+    <row r="592" ht="15.75" customHeight="1" s="4"/>
+    <row r="593" ht="15.75" customHeight="1" s="4"/>
+    <row r="594" ht="15.75" customHeight="1" s="4"/>
+    <row r="595" ht="15.75" customHeight="1" s="4"/>
+    <row r="596" ht="15.75" customHeight="1" s="4"/>
+    <row r="597" ht="15.75" customHeight="1" s="4"/>
+    <row r="598" ht="15.75" customHeight="1" s="4"/>
+    <row r="599" ht="15.75" customHeight="1" s="4"/>
+    <row r="600" ht="15.75" customHeight="1" s="4"/>
+    <row r="601" ht="15.75" customHeight="1" s="4"/>
+    <row r="602" ht="15.75" customHeight="1" s="4"/>
+    <row r="603" ht="15.75" customHeight="1" s="4"/>
+    <row r="604" ht="15.75" customHeight="1" s="4"/>
+    <row r="605" ht="15.75" customHeight="1" s="4"/>
+    <row r="606" ht="15.75" customHeight="1" s="4"/>
+    <row r="607" ht="15.75" customHeight="1" s="4"/>
+    <row r="608" ht="15.75" customHeight="1" s="4"/>
+    <row r="609" ht="15.75" customHeight="1" s="4"/>
+    <row r="610" ht="15.75" customHeight="1" s="4"/>
+    <row r="611" ht="15.75" customHeight="1" s="4"/>
+    <row r="612" ht="15.75" customHeight="1" s="4"/>
+    <row r="613" ht="15.75" customHeight="1" s="4"/>
+    <row r="614" ht="15.75" customHeight="1" s="4"/>
+    <row r="615" ht="15.75" customHeight="1" s="4"/>
+    <row r="616" ht="15.75" customHeight="1" s="4"/>
+    <row r="617" ht="15.75" customHeight="1" s="4"/>
+    <row r="618" ht="15.75" customHeight="1" s="4"/>
+    <row r="619" ht="15.75" customHeight="1" s="4"/>
+    <row r="620" ht="15.75" customHeight="1" s="4"/>
+    <row r="621" ht="15.75" customHeight="1" s="4"/>
+    <row r="622" ht="15.75" customHeight="1" s="4"/>
+    <row r="623" ht="15.75" customHeight="1" s="4"/>
+    <row r="624" ht="15.75" customHeight="1" s="4"/>
+    <row r="625" ht="15.75" customHeight="1" s="4"/>
+    <row r="626" ht="15.75" customHeight="1" s="4"/>
+    <row r="627" ht="15.75" customHeight="1" s="4"/>
+    <row r="628" ht="15.75" customHeight="1" s="4"/>
+    <row r="629" ht="15.75" customHeight="1" s="4"/>
+    <row r="630" ht="15.75" customHeight="1" s="4"/>
+    <row r="631" ht="15.75" customHeight="1" s="4"/>
+    <row r="632" ht="15.75" customHeight="1" s="4"/>
+    <row r="633" ht="15.75" customHeight="1" s="4"/>
+    <row r="634" ht="15.75" customHeight="1" s="4"/>
+    <row r="635" ht="15.75" customHeight="1" s="4"/>
+    <row r="636" ht="15.75" customHeight="1" s="4"/>
+    <row r="637" ht="15.75" customHeight="1" s="4"/>
+    <row r="638" ht="15.75" customHeight="1" s="4"/>
+    <row r="639" ht="15.75" customHeight="1" s="4"/>
+    <row r="640" ht="15.75" customHeight="1" s="4"/>
+    <row r="641" ht="15.75" customHeight="1" s="4"/>
+    <row r="642" ht="15.75" customHeight="1" s="4"/>
+    <row r="643" ht="15.75" customHeight="1" s="4"/>
+    <row r="644" ht="15.75" customHeight="1" s="4"/>
+    <row r="645" ht="15.75" customHeight="1" s="4"/>
+    <row r="646" ht="15.75" customHeight="1" s="4"/>
+    <row r="647" ht="15.75" customHeight="1" s="4"/>
+    <row r="648" ht="15.75" customHeight="1" s="4"/>
+    <row r="649" ht="15.75" customHeight="1" s="4"/>
+    <row r="650" ht="15.75" customHeight="1" s="4"/>
+    <row r="651" ht="15.75" customHeight="1" s="4"/>
+    <row r="652" ht="15.75" customHeight="1" s="4"/>
+    <row r="653" ht="15.75" customHeight="1" s="4"/>
+    <row r="654" ht="15.75" customHeight="1" s="4"/>
+    <row r="655" ht="15.75" customHeight="1" s="4"/>
+    <row r="656" ht="15.75" customHeight="1" s="4"/>
+    <row r="657" ht="15.75" customHeight="1" s="4"/>
+    <row r="658" ht="15.75" customHeight="1" s="4"/>
+    <row r="659" ht="15.75" customHeight="1" s="4"/>
+    <row r="660" ht="15.75" customHeight="1" s="4"/>
+    <row r="661" ht="15.75" customHeight="1" s="4"/>
+    <row r="662" ht="15.75" customHeight="1" s="4"/>
+    <row r="663" ht="15.75" customHeight="1" s="4"/>
+    <row r="664" ht="15.75" customHeight="1" s="4"/>
+    <row r="665" ht="15.75" customHeight="1" s="4"/>
+    <row r="666" ht="15.75" customHeight="1" s="4"/>
+    <row r="667" ht="15.75" customHeight="1" s="4"/>
+    <row r="668" ht="15.75" customHeight="1" s="4"/>
+    <row r="669" ht="15.75" customHeight="1" s="4"/>
+    <row r="670" ht="15.75" customHeight="1" s="4"/>
+    <row r="671" ht="15.75" customHeight="1" s="4"/>
+    <row r="672" ht="15.75" customHeight="1" s="4"/>
+    <row r="673" ht="15.75" customHeight="1" s="4"/>
+    <row r="674" ht="15.75" customHeight="1" s="4"/>
+    <row r="675" ht="15.75" customHeight="1" s="4"/>
+    <row r="676" ht="15.75" customHeight="1" s="4"/>
+    <row r="677" ht="15.75" customHeight="1" s="4"/>
+    <row r="678" ht="15.75" customHeight="1" s="4"/>
+    <row r="679" ht="15.75" customHeight="1" s="4"/>
+    <row r="680" ht="15.75" customHeight="1" s="4"/>
+    <row r="681" ht="15.75" customHeight="1" s="4"/>
+    <row r="682" ht="15.75" customHeight="1" s="4"/>
+    <row r="683" ht="15.75" customHeight="1" s="4"/>
+    <row r="684" ht="15.75" customHeight="1" s="4"/>
+    <row r="685" ht="15.75" customHeight="1" s="4"/>
+    <row r="686" ht="15.75" customHeight="1" s="4"/>
+    <row r="687" ht="15.75" customHeight="1" s="4"/>
+    <row r="688" ht="15.75" customHeight="1" s="4"/>
+    <row r="689" ht="15.75" customHeight="1" s="4"/>
+    <row r="690" ht="15.75" customHeight="1" s="4"/>
+    <row r="691" ht="15.75" customHeight="1" s="4"/>
+    <row r="692" ht="15.75" customHeight="1" s="4"/>
+    <row r="693" ht="15.75" customHeight="1" s="4"/>
+    <row r="694" ht="15.75" customHeight="1" s="4"/>
+    <row r="695" ht="15.75" customHeight="1" s="4"/>
+    <row r="696" ht="15.75" customHeight="1" s="4"/>
+    <row r="697" ht="15.75" customHeight="1" s="4"/>
+    <row r="698" ht="15.75" customHeight="1" s="4"/>
+    <row r="699" ht="15.75" customHeight="1" s="4"/>
+    <row r="700" ht="15.75" customHeight="1" s="4"/>
+    <row r="701" ht="15.75" customHeight="1" s="4"/>
+    <row r="702" ht="15.75" customHeight="1" s="4"/>
+    <row r="703" ht="15.75" customHeight="1" s="4"/>
+    <row r="704" ht="15.75" customHeight="1" s="4"/>
+    <row r="705" ht="15.75" customHeight="1" s="4"/>
+    <row r="706" ht="15.75" customHeight="1" s="4"/>
+    <row r="707" ht="15.75" customHeight="1" s="4"/>
+    <row r="708" ht="15.75" customHeight="1" s="4"/>
+    <row r="709" ht="15.75" customHeight="1" s="4"/>
+    <row r="710" ht="15.75" customHeight="1" s="4"/>
+    <row r="711" ht="15.75" customHeight="1" s="4"/>
+    <row r="712" ht="15.75" customHeight="1" s="4"/>
+    <row r="713" ht="15.75" customHeight="1" s="4"/>
+    <row r="714" ht="15.75" customHeight="1" s="4"/>
+    <row r="715" ht="15.75" customHeight="1" s="4"/>
+    <row r="716" ht="15.75" customHeight="1" s="4"/>
+    <row r="717" ht="15.75" customHeight="1" s="4"/>
+    <row r="718" ht="15.75" customHeight="1" s="4"/>
+    <row r="719" ht="15.75" customHeight="1" s="4"/>
+    <row r="720" ht="15.75" customHeight="1" s="4"/>
+    <row r="721" ht="15.75" customHeight="1" s="4"/>
+    <row r="722" ht="15.75" customHeight="1" s="4"/>
+    <row r="723" ht="15.75" customHeight="1" s="4"/>
+    <row r="724" ht="15.75" customHeight="1" s="4"/>
+    <row r="725" ht="15.75" customHeight="1" s="4"/>
+    <row r="726" ht="15.75" customHeight="1" s="4"/>
+    <row r="727" ht="15.75" customHeight="1" s="4"/>
+    <row r="728" ht="15.75" customHeight="1" s="4"/>
+    <row r="729" ht="15.75" customHeight="1" s="4"/>
+    <row r="730" ht="15.75" customHeight="1" s="4"/>
+    <row r="731" ht="15.75" customHeight="1" s="4"/>
+    <row r="732" ht="15.75" customHeight="1" s="4"/>
+    <row r="733" ht="15.75" customHeight="1" s="4"/>
+    <row r="734" ht="15.75" customHeight="1" s="4"/>
+    <row r="735" ht="15.75" customHeight="1" s="4"/>
+    <row r="736" ht="15.75" customHeight="1" s="4"/>
+    <row r="737" ht="15.75" customHeight="1" s="4"/>
+    <row r="738" ht="15.75" customHeight="1" s="4"/>
+    <row r="739" ht="15.75" customHeight="1" s="4"/>
+    <row r="740" ht="15.75" customHeight="1" s="4"/>
+    <row r="741" ht="15.75" customHeight="1" s="4"/>
+    <row r="742" ht="15.75" customHeight="1" s="4"/>
+    <row r="743" ht="15.75" customHeight="1" s="4"/>
+    <row r="744" ht="15.75" customHeight="1" s="4"/>
+    <row r="745" ht="15.75" customHeight="1" s="4"/>
+    <row r="746" ht="15.75" customHeight="1" s="4"/>
+    <row r="747" ht="15.75" customHeight="1" s="4"/>
+    <row r="748" ht="15.75" customHeight="1" s="4"/>
+    <row r="749" ht="15.75" customHeight="1" s="4"/>
+    <row r="750" ht="15.75" customHeight="1" s="4"/>
+    <row r="751" ht="15.75" customHeight="1" s="4"/>
+    <row r="752" ht="15.75" customHeight="1" s="4"/>
+    <row r="753" ht="15.75" customHeight="1" s="4"/>
+    <row r="754" ht="15.75" customHeight="1" s="4"/>
+    <row r="755" ht="15.75" customHeight="1" s="4"/>
+    <row r="756" ht="15.75" customHeight="1" s="4"/>
+    <row r="757" ht="15.75" customHeight="1" s="4"/>
+    <row r="758" ht="15.75" customHeight="1" s="4"/>
+    <row r="759" ht="15.75" customHeight="1" s="4"/>
+    <row r="760" ht="15.75" customHeight="1" s="4"/>
+    <row r="761" ht="15.75" customHeight="1" s="4"/>
+    <row r="762" ht="15.75" customHeight="1" s="4"/>
+    <row r="763" ht="15.75" customHeight="1" s="4"/>
+    <row r="764" ht="15.75" customHeight="1" s="4"/>
+    <row r="765" ht="15.75" customHeight="1" s="4"/>
+    <row r="766" ht="15.75" customHeight="1" s="4"/>
+    <row r="767" ht="15.75" customHeight="1" s="4"/>
+    <row r="768" ht="15.75" customHeight="1" s="4"/>
+    <row r="769" ht="15.75" customHeight="1" s="4"/>
+    <row r="770" ht="15.75" customHeight="1" s="4"/>
+    <row r="771" ht="15.75" customHeight="1" s="4"/>
+    <row r="772" ht="15.75" customHeight="1" s="4"/>
+    <row r="773" ht="15.75" customHeight="1" s="4"/>
+    <row r="774" ht="15.75" customHeight="1" s="4"/>
+    <row r="775" ht="15.75" customHeight="1" s="4"/>
+    <row r="776" ht="15.75" customHeight="1" s="4"/>
+    <row r="777" ht="15.75" customHeight="1" s="4"/>
+    <row r="778" ht="15.75" customHeight="1" s="4"/>
+    <row r="779" ht="15.75" customHeight="1" s="4"/>
+    <row r="780" ht="15.75" customHeight="1" s="4"/>
+    <row r="781" ht="15.75" customHeight="1" s="4"/>
+    <row r="782" ht="15.75" customHeight="1" s="4"/>
+    <row r="783" ht="15.75" customHeight="1" s="4"/>
+    <row r="784" ht="15.75" customHeight="1" s="4"/>
+    <row r="785" ht="15.75" customHeight="1" s="4"/>
+    <row r="786" ht="15.75" customHeight="1" s="4"/>
+    <row r="787" ht="15.75" customHeight="1" s="4"/>
+    <row r="788" ht="15.75" customHeight="1" s="4"/>
+    <row r="789" ht="15.75" customHeight="1" s="4"/>
+    <row r="790" ht="15.75" customHeight="1" s="4"/>
+    <row r="791" ht="15.75" customHeight="1" s="4"/>
+    <row r="792" ht="15.75" customHeight="1" s="4"/>
+    <row r="793" ht="15.75" customHeight="1" s="4"/>
+    <row r="794" ht="15.75" customHeight="1" s="4"/>
+    <row r="795" ht="15.75" customHeight="1" s="4"/>
+    <row r="796" ht="15.75" customHeight="1" s="4"/>
+    <row r="797" ht="15.75" customHeight="1" s="4"/>
+    <row r="798" ht="15.75" customHeight="1" s="4"/>
+    <row r="799" ht="15.75" customHeight="1" s="4"/>
+    <row r="800" ht="15.75" customHeight="1" s="4"/>
+    <row r="801" ht="15.75" customHeight="1" s="4"/>
+    <row r="802" ht="15.75" customHeight="1" s="4"/>
+    <row r="803" ht="15.75" customHeight="1" s="4"/>
+    <row r="804" ht="15.75" customHeight="1" s="4"/>
+    <row r="805" ht="15.75" customHeight="1" s="4"/>
+    <row r="806" ht="15.75" customHeight="1" s="4"/>
+    <row r="807" ht="15.75" customHeight="1" s="4"/>
+    <row r="808" ht="15.75" customHeight="1" s="4"/>
+    <row r="809" ht="15.75" customHeight="1" s="4"/>
+    <row r="810" ht="15.75" customHeight="1" s="4"/>
+    <row r="811" ht="15.75" customHeight="1" s="4"/>
+    <row r="812" ht="15.75" customHeight="1" s="4"/>
+    <row r="813" ht="15.75" customHeight="1" s="4"/>
+    <row r="814" ht="15.75" customHeight="1" s="4"/>
+    <row r="815" ht="15.75" customHeight="1" s="4"/>
+    <row r="816" ht="15.75" customHeight="1" s="4"/>
+    <row r="817" ht="15.75" customHeight="1" s="4"/>
+    <row r="818" ht="15.75" customHeight="1" s="4"/>
+    <row r="819" ht="15.75" customHeight="1" s="4"/>
+    <row r="820" ht="15.75" customHeight="1" s="4"/>
+    <row r="821" ht="15.75" customHeight="1" s="4"/>
+    <row r="822" ht="15.75" customHeight="1" s="4"/>
+    <row r="823" ht="15.75" customHeight="1" s="4"/>
+    <row r="824" ht="15.75" customHeight="1" s="4"/>
+    <row r="825" ht="15.75" customHeight="1" s="4"/>
+    <row r="826" ht="15.75" customHeight="1" s="4"/>
+    <row r="827" ht="15.75" customHeight="1" s="4"/>
+    <row r="828" ht="15.75" customHeight="1" s="4"/>
+    <row r="829" ht="15.75" customHeight="1" s="4"/>
+    <row r="830" ht="15.75" customHeight="1" s="4"/>
+    <row r="831" ht="15.75" customHeight="1" s="4"/>
+    <row r="832" ht="15.75" customHeight="1" s="4"/>
+    <row r="833" ht="15.75" customHeight="1" s="4"/>
+    <row r="834" ht="15.75" customHeight="1" s="4"/>
+    <row r="835" ht="15.75" customHeight="1" s="4"/>
+    <row r="836" ht="15.75" customHeight="1" s="4"/>
+    <row r="837" ht="15.75" customHeight="1" s="4"/>
+    <row r="838" ht="15.75" customHeight="1" s="4"/>
+    <row r="839" ht="15.75" customHeight="1" s="4"/>
+    <row r="840" ht="15.75" customHeight="1" s="4"/>
+    <row r="841" ht="15.75" customHeight="1" s="4"/>
+    <row r="842" ht="15.75" customHeight="1" s="4"/>
+    <row r="843" ht="15.75" customHeight="1" s="4"/>
+    <row r="844" ht="15.75" customHeight="1" s="4"/>
+    <row r="845" ht="15.75" customHeight="1" s="4"/>
+    <row r="846" ht="15.75" customHeight="1" s="4"/>
+    <row r="847" ht="15.75" customHeight="1" s="4"/>
+    <row r="848" ht="15.75" customHeight="1" s="4"/>
+    <row r="849" ht="15.75" customHeight="1" s="4"/>
+    <row r="850" ht="15.75" customHeight="1" s="4"/>
+    <row r="851" ht="15.75" customHeight="1" s="4"/>
+    <row r="852" ht="15.75" customHeight="1" s="4"/>
+    <row r="853" ht="15.75" customHeight="1" s="4"/>
+    <row r="854" ht="15.75" customHeight="1" s="4"/>
+    <row r="855" ht="15.75" customHeight="1" s="4"/>
+    <row r="856" ht="15.75" customHeight="1" s="4"/>
+    <row r="857" ht="15.75" customHeight="1" s="4"/>
+    <row r="858" ht="15.75" customHeight="1" s="4"/>
+    <row r="859" ht="15.75" customHeight="1" s="4"/>
+    <row r="860" ht="15.75" customHeight="1" s="4"/>
+    <row r="861" ht="15.75" customHeight="1" s="4"/>
+    <row r="862" ht="15.75" customHeight="1" s="4"/>
+    <row r="863" ht="15.75" customHeight="1" s="4"/>
+    <row r="864" ht="15.75" customHeight="1" s="4"/>
+    <row r="865" ht="15.75" customHeight="1" s="4"/>
+    <row r="866" ht="15.75" customHeight="1" s="4"/>
+    <row r="867" ht="15.75" customHeight="1" s="4"/>
+    <row r="868" ht="15.75" customHeight="1" s="4"/>
+    <row r="869" ht="15.75" customHeight="1" s="4"/>
+    <row r="870" ht="15.75" customHeight="1" s="4"/>
+    <row r="871" ht="15.75" customHeight="1" s="4"/>
+    <row r="872" ht="15.75" customHeight="1" s="4"/>
+    <row r="873" ht="15.75" customHeight="1" s="4"/>
+    <row r="874" ht="15.75" customHeight="1" s="4"/>
+    <row r="875" ht="15.75" customHeight="1" s="4"/>
+    <row r="876" ht="15.75" customHeight="1" s="4"/>
+    <row r="877" ht="15.75" customHeight="1" s="4"/>
+    <row r="878" ht="15.75" customHeight="1" s="4"/>
+    <row r="879" ht="15.75" customHeight="1" s="4"/>
+    <row r="880" ht="15.75" customHeight="1" s="4"/>
+    <row r="881" ht="15.75" customHeight="1" s="4"/>
+    <row r="882" ht="15.75" customHeight="1" s="4"/>
+    <row r="883" ht="15.75" customHeight="1" s="4"/>
+    <row r="884" ht="15.75" customHeight="1" s="4"/>
+    <row r="885" ht="15.75" customHeight="1" s="4"/>
+    <row r="886" ht="15.75" customHeight="1" s="4"/>
+    <row r="887" ht="15.75" customHeight="1" s="4"/>
+    <row r="888" ht="15.75" customHeight="1" s="4"/>
+    <row r="889" ht="15.75" customHeight="1" s="4"/>
+    <row r="890" ht="15.75" customHeight="1" s="4"/>
+    <row r="891" ht="15.75" customHeight="1" s="4"/>
+    <row r="892" ht="15.75" customHeight="1" s="4"/>
+    <row r="893" ht="15.75" customHeight="1" s="4"/>
+    <row r="894" ht="15.75" customHeight="1" s="4"/>
+    <row r="895" ht="15.75" customHeight="1" s="4"/>
+    <row r="896" ht="15.75" customHeight="1" s="4"/>
+    <row r="897" ht="15.75" customHeight="1" s="4"/>
+    <row r="898" ht="15.75" customHeight="1" s="4"/>
+    <row r="899" ht="15.75" customHeight="1" s="4"/>
+    <row r="900" ht="15.75" customHeight="1" s="4"/>
+    <row r="901" ht="15.75" customHeight="1" s="4"/>
+    <row r="902" ht="15.75" customHeight="1" s="4"/>
+    <row r="903" ht="15.75" customHeight="1" s="4"/>
+    <row r="904" ht="15.75" customHeight="1" s="4"/>
+    <row r="905" ht="15.75" customHeight="1" s="4"/>
+    <row r="906" ht="15.75" customHeight="1" s="4"/>
+    <row r="907" ht="15.75" customHeight="1" s="4"/>
+    <row r="908" ht="15.75" customHeight="1" s="4"/>
+    <row r="909" ht="15.75" customHeight="1" s="4"/>
+    <row r="910" ht="15.75" customHeight="1" s="4"/>
+    <row r="911" ht="15.75" customHeight="1" s="4"/>
+    <row r="912" ht="15.75" customHeight="1" s="4"/>
+    <row r="913" ht="15.75" customHeight="1" s="4"/>
+    <row r="914" ht="15.75" customHeight="1" s="4"/>
+    <row r="915" ht="15.75" customHeight="1" s="4"/>
+    <row r="916" ht="15.75" customHeight="1" s="4"/>
+    <row r="917" ht="15.75" customHeight="1" s="4"/>
+    <row r="918" ht="15.75" customHeight="1" s="4"/>
+    <row r="919" ht="15.75" customHeight="1" s="4"/>
+    <row r="920" ht="15.75" customHeight="1" s="4"/>
+    <row r="921" ht="15.75" customHeight="1" s="4"/>
+    <row r="922" ht="15.75" customHeight="1" s="4"/>
+    <row r="923" ht="15.75" customHeight="1" s="4"/>
+    <row r="924" ht="15.75" customHeight="1" s="4"/>
+    <row r="925" ht="15.75" customHeight="1" s="4"/>
+    <row r="926" ht="15.75" customHeight="1" s="4"/>
+    <row r="927" ht="15.75" customHeight="1" s="4"/>
+    <row r="928" ht="15.75" customHeight="1" s="4"/>
+    <row r="929" ht="15.75" customHeight="1" s="4"/>
+    <row r="930" ht="15.75" customHeight="1" s="4"/>
+    <row r="931" ht="15.75" customHeight="1" s="4"/>
+    <row r="932" ht="15.75" customHeight="1" s="4"/>
+    <row r="933" ht="15.75" customHeight="1" s="4"/>
+    <row r="934" ht="15.75" customHeight="1" s="4"/>
+    <row r="935" ht="15.75" customHeight="1" s="4"/>
+    <row r="936" ht="15.75" customHeight="1" s="4"/>
+    <row r="937" ht="15.75" customHeight="1" s="4"/>
+    <row r="938" ht="15.75" customHeight="1" s="4"/>
+    <row r="939" ht="15.75" customHeight="1" s="4"/>
+    <row r="940" ht="15.75" customHeight="1" s="4"/>
+    <row r="941" ht="15.75" customHeight="1" s="4"/>
+    <row r="942" ht="15.75" customHeight="1" s="4"/>
+    <row r="943" ht="15.75" customHeight="1" s="4"/>
+    <row r="944" ht="15.75" customHeight="1" s="4"/>
+    <row r="945" ht="15.75" customHeight="1" s="4"/>
+    <row r="946" ht="15.75" customHeight="1" s="4"/>
+    <row r="947" ht="15.75" customHeight="1" s="4"/>
+    <row r="948" ht="15.75" customHeight="1" s="4"/>
+    <row r="949" ht="15.75" customHeight="1" s="4"/>
+    <row r="950" ht="15.75" customHeight="1" s="4"/>
+    <row r="951" ht="15.75" customHeight="1" s="4"/>
+    <row r="952" ht="15.75" customHeight="1" s="4"/>
+    <row r="953" ht="15.75" customHeight="1" s="4"/>
+    <row r="954" ht="15.75" customHeight="1" s="4"/>
+    <row r="955" ht="15.75" customHeight="1" s="4"/>
+    <row r="956" ht="15.75" customHeight="1" s="4"/>
+    <row r="957" ht="15.75" customHeight="1" s="4"/>
+    <row r="958" ht="15.75" customHeight="1" s="4"/>
+    <row r="959" ht="15.75" customHeight="1" s="4"/>
+    <row r="960" ht="15.75" customHeight="1" s="4"/>
+    <row r="961" ht="15.75" customHeight="1" s="4"/>
+    <row r="962" ht="15.75" customHeight="1" s="4"/>
+    <row r="963" ht="15.75" customHeight="1" s="4"/>
+    <row r="964" ht="15.75" customHeight="1" s="4"/>
+    <row r="965" ht="15.75" customHeight="1" s="4"/>
+    <row r="966" ht="15.75" customHeight="1" s="4"/>
+    <row r="967" ht="15.75" customHeight="1" s="4"/>
+    <row r="968" ht="15.75" customHeight="1" s="4"/>
+    <row r="969" ht="15.75" customHeight="1" s="4"/>
+    <row r="970" ht="15.75" customHeight="1" s="4"/>
+    <row r="971" ht="15.75" customHeight="1" s="4"/>
+    <row r="972" ht="15.75" customHeight="1" s="4"/>
+    <row r="973" ht="15.75" customHeight="1" s="4"/>
+    <row r="974" ht="15.75" customHeight="1" s="4"/>
+    <row r="975" ht="15.75" customHeight="1" s="4"/>
+    <row r="976" ht="15.75" customHeight="1" s="4"/>
+    <row r="977" ht="15.75" customHeight="1" s="4"/>
+    <row r="978" ht="15.75" customHeight="1" s="4"/>
+    <row r="979" ht="15.75" customHeight="1" s="4"/>
+    <row r="980" ht="15.75" customHeight="1" s="4"/>
+    <row r="981" ht="15.75" customHeight="1" s="4"/>
+    <row r="982" ht="15.75" customHeight="1" s="4"/>
+    <row r="983" ht="15.75" customHeight="1" s="4"/>
+    <row r="984" ht="15.75" customHeight="1" s="4"/>
+    <row r="985" ht="15.75" customHeight="1" s="4"/>
+    <row r="986" ht="15.75" customHeight="1" s="4"/>
+    <row r="987" ht="15.75" customHeight="1" s="4"/>
+    <row r="988" ht="15.75" customHeight="1" s="4"/>
+    <row r="989" ht="15.75" customHeight="1" s="4"/>
+    <row r="990" ht="15.75" customHeight="1" s="4"/>
+    <row r="991" ht="15.75" customHeight="1" s="4"/>
+    <row r="992" ht="15.75" customHeight="1" s="4"/>
+    <row r="993" ht="15.75" customHeight="1" s="4"/>
+    <row r="994" ht="15.75" customHeight="1" s="4"/>
+    <row r="995" ht="15.75" customHeight="1" s="4"/>
+    <row r="996" ht="15.75" customHeight="1" s="4"/>
+    <row r="997" ht="15.75" customHeight="1" s="4"/>
+    <row r="998" ht="15.75" customHeight="1" s="4"/>
+    <row r="999" ht="15.75" customHeight="1" s="4"/>
+    <row r="1000" ht="15.75" customHeight="1" s="4"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -8024,9 +9796,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" style="4" min="1" max="1"/>
+    <col width="8.710000000000001" customWidth="1" style="4" min="2" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8044,7 +9817,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8054,7 +9827,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8064,7 +9837,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8102,7 +9875,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8147,61 +9920,1034 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="A20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="4">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>How to use this sheet:</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1" s="4">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>1. Start from the top (highest Hive Count = most-engaged people, best first targets).</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1" s="4">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2. For rows with a usable Email, copy the Email Template tab's Subject/Body, swap in the bracketed placeholders using that row's data, and send.</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1" s="4">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>3. For rows with Email Status "needs verification", "unrecoverable", or "missing", do a quick web search (name + "beekeeper"/"apiary"/state) before giving up — a few of these may turn up a current email or a way to reach them through a local beekeeping association.</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1" s="4">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>4. Update Status, Date Emailed, and Follow-up Date as you go.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>4. Update Status, Date Emailed/Scheduled, and Follow-up Date as you go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="4">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>5. Use Notes for anything short and specific (a reply, a bounce, a correction to their email, etc).</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
+    <row r="27" ht="15.75" customHeight="1" s="4">
+      <c r="A27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="4">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>This list is separate from KEY_PEOPLE_CONTACTS.md and University_Bee_Research_Contacts.xlsx in the project repo — Debbie Delaney is the one confirmed overlap so far; mirror any status update for her in both places so they don't drift apart.</t>
         </is>
       </c>
     </row>
+    <row r="29" ht="15.75" customHeight="1" s="4"/>
+    <row r="30" ht="15.75" customHeight="1" s="4"/>
+    <row r="31" ht="15.75" customHeight="1" s="4"/>
+    <row r="32" ht="15.75" customHeight="1" s="4"/>
+    <row r="33" ht="15.75" customHeight="1" s="4"/>
+    <row r="34" ht="15.75" customHeight="1" s="4"/>
+    <row r="35" ht="15.75" customHeight="1" s="4"/>
+    <row r="36" ht="15.75" customHeight="1" s="4"/>
+    <row r="37" ht="15.75" customHeight="1" s="4"/>
+    <row r="38" ht="15.75" customHeight="1" s="4"/>
+    <row r="39" ht="15.75" customHeight="1" s="4"/>
+    <row r="40" ht="15.75" customHeight="1" s="4"/>
+    <row r="41" ht="15.75" customHeight="1" s="4"/>
+    <row r="42" ht="15.75" customHeight="1" s="4"/>
+    <row r="43" ht="15.75" customHeight="1" s="4"/>
+    <row r="44" ht="15.75" customHeight="1" s="4"/>
+    <row r="45" ht="15.75" customHeight="1" s="4"/>
+    <row r="46" ht="15.75" customHeight="1" s="4"/>
+    <row r="47" ht="15.75" customHeight="1" s="4"/>
+    <row r="48" ht="15.75" customHeight="1" s="4"/>
+    <row r="49" ht="15.75" customHeight="1" s="4"/>
+    <row r="50" ht="15.75" customHeight="1" s="4"/>
+    <row r="51" ht="15.75" customHeight="1" s="4"/>
+    <row r="52" ht="15.75" customHeight="1" s="4"/>
+    <row r="53" ht="15.75" customHeight="1" s="4"/>
+    <row r="54" ht="15.75" customHeight="1" s="4"/>
+    <row r="55" ht="15.75" customHeight="1" s="4"/>
+    <row r="56" ht="15.75" customHeight="1" s="4"/>
+    <row r="57" ht="15.75" customHeight="1" s="4"/>
+    <row r="58" ht="15.75" customHeight="1" s="4"/>
+    <row r="59" ht="15.75" customHeight="1" s="4"/>
+    <row r="60" ht="15.75" customHeight="1" s="4"/>
+    <row r="61" ht="15.75" customHeight="1" s="4"/>
+    <row r="62" ht="15.75" customHeight="1" s="4"/>
+    <row r="63" ht="15.75" customHeight="1" s="4"/>
+    <row r="64" ht="15.75" customHeight="1" s="4"/>
+    <row r="65" ht="15.75" customHeight="1" s="4"/>
+    <row r="66" ht="15.75" customHeight="1" s="4"/>
+    <row r="67" ht="15.75" customHeight="1" s="4"/>
+    <row r="68" ht="15.75" customHeight="1" s="4"/>
+    <row r="69" ht="15.75" customHeight="1" s="4"/>
+    <row r="70" ht="15.75" customHeight="1" s="4"/>
+    <row r="71" ht="15.75" customHeight="1" s="4"/>
+    <row r="72" ht="15.75" customHeight="1" s="4"/>
+    <row r="73" ht="15.75" customHeight="1" s="4"/>
+    <row r="74" ht="15.75" customHeight="1" s="4"/>
+    <row r="75" ht="15.75" customHeight="1" s="4"/>
+    <row r="76" ht="15.75" customHeight="1" s="4"/>
+    <row r="77" ht="15.75" customHeight="1" s="4"/>
+    <row r="78" ht="15.75" customHeight="1" s="4"/>
+    <row r="79" ht="15.75" customHeight="1" s="4"/>
+    <row r="80" ht="15.75" customHeight="1" s="4"/>
+    <row r="81" ht="15.75" customHeight="1" s="4"/>
+    <row r="82" ht="15.75" customHeight="1" s="4"/>
+    <row r="83" ht="15.75" customHeight="1" s="4"/>
+    <row r="84" ht="15.75" customHeight="1" s="4"/>
+    <row r="85" ht="15.75" customHeight="1" s="4"/>
+    <row r="86" ht="15.75" customHeight="1" s="4"/>
+    <row r="87" ht="15.75" customHeight="1" s="4"/>
+    <row r="88" ht="15.75" customHeight="1" s="4"/>
+    <row r="89" ht="15.75" customHeight="1" s="4"/>
+    <row r="90" ht="15.75" customHeight="1" s="4"/>
+    <row r="91" ht="15.75" customHeight="1" s="4"/>
+    <row r="92" ht="15.75" customHeight="1" s="4"/>
+    <row r="93" ht="15.75" customHeight="1" s="4"/>
+    <row r="94" ht="15.75" customHeight="1" s="4"/>
+    <row r="95" ht="15.75" customHeight="1" s="4"/>
+    <row r="96" ht="15.75" customHeight="1" s="4"/>
+    <row r="97" ht="15.75" customHeight="1" s="4"/>
+    <row r="98" ht="15.75" customHeight="1" s="4"/>
+    <row r="99" ht="15.75" customHeight="1" s="4"/>
+    <row r="100" ht="15.75" customHeight="1" s="4"/>
+    <row r="101" ht="15.75" customHeight="1" s="4"/>
+    <row r="102" ht="15.75" customHeight="1" s="4"/>
+    <row r="103" ht="15.75" customHeight="1" s="4"/>
+    <row r="104" ht="15.75" customHeight="1" s="4"/>
+    <row r="105" ht="15.75" customHeight="1" s="4"/>
+    <row r="106" ht="15.75" customHeight="1" s="4"/>
+    <row r="107" ht="15.75" customHeight="1" s="4"/>
+    <row r="108" ht="15.75" customHeight="1" s="4"/>
+    <row r="109" ht="15.75" customHeight="1" s="4"/>
+    <row r="110" ht="15.75" customHeight="1" s="4"/>
+    <row r="111" ht="15.75" customHeight="1" s="4"/>
+    <row r="112" ht="15.75" customHeight="1" s="4"/>
+    <row r="113" ht="15.75" customHeight="1" s="4"/>
+    <row r="114" ht="15.75" customHeight="1" s="4"/>
+    <row r="115" ht="15.75" customHeight="1" s="4"/>
+    <row r="116" ht="15.75" customHeight="1" s="4"/>
+    <row r="117" ht="15.75" customHeight="1" s="4"/>
+    <row r="118" ht="15.75" customHeight="1" s="4"/>
+    <row r="119" ht="15.75" customHeight="1" s="4"/>
+    <row r="120" ht="15.75" customHeight="1" s="4"/>
+    <row r="121" ht="15.75" customHeight="1" s="4"/>
+    <row r="122" ht="15.75" customHeight="1" s="4"/>
+    <row r="123" ht="15.75" customHeight="1" s="4"/>
+    <row r="124" ht="15.75" customHeight="1" s="4"/>
+    <row r="125" ht="15.75" customHeight="1" s="4"/>
+    <row r="126" ht="15.75" customHeight="1" s="4"/>
+    <row r="127" ht="15.75" customHeight="1" s="4"/>
+    <row r="128" ht="15.75" customHeight="1" s="4"/>
+    <row r="129" ht="15.75" customHeight="1" s="4"/>
+    <row r="130" ht="15.75" customHeight="1" s="4"/>
+    <row r="131" ht="15.75" customHeight="1" s="4"/>
+    <row r="132" ht="15.75" customHeight="1" s="4"/>
+    <row r="133" ht="15.75" customHeight="1" s="4"/>
+    <row r="134" ht="15.75" customHeight="1" s="4"/>
+    <row r="135" ht="15.75" customHeight="1" s="4"/>
+    <row r="136" ht="15.75" customHeight="1" s="4"/>
+    <row r="137" ht="15.75" customHeight="1" s="4"/>
+    <row r="138" ht="15.75" customHeight="1" s="4"/>
+    <row r="139" ht="15.75" customHeight="1" s="4"/>
+    <row r="140" ht="15.75" customHeight="1" s="4"/>
+    <row r="141" ht="15.75" customHeight="1" s="4"/>
+    <row r="142" ht="15.75" customHeight="1" s="4"/>
+    <row r="143" ht="15.75" customHeight="1" s="4"/>
+    <row r="144" ht="15.75" customHeight="1" s="4"/>
+    <row r="145" ht="15.75" customHeight="1" s="4"/>
+    <row r="146" ht="15.75" customHeight="1" s="4"/>
+    <row r="147" ht="15.75" customHeight="1" s="4"/>
+    <row r="148" ht="15.75" customHeight="1" s="4"/>
+    <row r="149" ht="15.75" customHeight="1" s="4"/>
+    <row r="150" ht="15.75" customHeight="1" s="4"/>
+    <row r="151" ht="15.75" customHeight="1" s="4"/>
+    <row r="152" ht="15.75" customHeight="1" s="4"/>
+    <row r="153" ht="15.75" customHeight="1" s="4"/>
+    <row r="154" ht="15.75" customHeight="1" s="4"/>
+    <row r="155" ht="15.75" customHeight="1" s="4"/>
+    <row r="156" ht="15.75" customHeight="1" s="4"/>
+    <row r="157" ht="15.75" customHeight="1" s="4"/>
+    <row r="158" ht="15.75" customHeight="1" s="4"/>
+    <row r="159" ht="15.75" customHeight="1" s="4"/>
+    <row r="160" ht="15.75" customHeight="1" s="4"/>
+    <row r="161" ht="15.75" customHeight="1" s="4"/>
+    <row r="162" ht="15.75" customHeight="1" s="4"/>
+    <row r="163" ht="15.75" customHeight="1" s="4"/>
+    <row r="164" ht="15.75" customHeight="1" s="4"/>
+    <row r="165" ht="15.75" customHeight="1" s="4"/>
+    <row r="166" ht="15.75" customHeight="1" s="4"/>
+    <row r="167" ht="15.75" customHeight="1" s="4"/>
+    <row r="168" ht="15.75" customHeight="1" s="4"/>
+    <row r="169" ht="15.75" customHeight="1" s="4"/>
+    <row r="170" ht="15.75" customHeight="1" s="4"/>
+    <row r="171" ht="15.75" customHeight="1" s="4"/>
+    <row r="172" ht="15.75" customHeight="1" s="4"/>
+    <row r="173" ht="15.75" customHeight="1" s="4"/>
+    <row r="174" ht="15.75" customHeight="1" s="4"/>
+    <row r="175" ht="15.75" customHeight="1" s="4"/>
+    <row r="176" ht="15.75" customHeight="1" s="4"/>
+    <row r="177" ht="15.75" customHeight="1" s="4"/>
+    <row r="178" ht="15.75" customHeight="1" s="4"/>
+    <row r="179" ht="15.75" customHeight="1" s="4"/>
+    <row r="180" ht="15.75" customHeight="1" s="4"/>
+    <row r="181" ht="15.75" customHeight="1" s="4"/>
+    <row r="182" ht="15.75" customHeight="1" s="4"/>
+    <row r="183" ht="15.75" customHeight="1" s="4"/>
+    <row r="184" ht="15.75" customHeight="1" s="4"/>
+    <row r="185" ht="15.75" customHeight="1" s="4"/>
+    <row r="186" ht="15.75" customHeight="1" s="4"/>
+    <row r="187" ht="15.75" customHeight="1" s="4"/>
+    <row r="188" ht="15.75" customHeight="1" s="4"/>
+    <row r="189" ht="15.75" customHeight="1" s="4"/>
+    <row r="190" ht="15.75" customHeight="1" s="4"/>
+    <row r="191" ht="15.75" customHeight="1" s="4"/>
+    <row r="192" ht="15.75" customHeight="1" s="4"/>
+    <row r="193" ht="15.75" customHeight="1" s="4"/>
+    <row r="194" ht="15.75" customHeight="1" s="4"/>
+    <row r="195" ht="15.75" customHeight="1" s="4"/>
+    <row r="196" ht="15.75" customHeight="1" s="4"/>
+    <row r="197" ht="15.75" customHeight="1" s="4"/>
+    <row r="198" ht="15.75" customHeight="1" s="4"/>
+    <row r="199" ht="15.75" customHeight="1" s="4"/>
+    <row r="200" ht="15.75" customHeight="1" s="4"/>
+    <row r="201" ht="15.75" customHeight="1" s="4"/>
+    <row r="202" ht="15.75" customHeight="1" s="4"/>
+    <row r="203" ht="15.75" customHeight="1" s="4"/>
+    <row r="204" ht="15.75" customHeight="1" s="4"/>
+    <row r="205" ht="15.75" customHeight="1" s="4"/>
+    <row r="206" ht="15.75" customHeight="1" s="4"/>
+    <row r="207" ht="15.75" customHeight="1" s="4"/>
+    <row r="208" ht="15.75" customHeight="1" s="4"/>
+    <row r="209" ht="15.75" customHeight="1" s="4"/>
+    <row r="210" ht="15.75" customHeight="1" s="4"/>
+    <row r="211" ht="15.75" customHeight="1" s="4"/>
+    <row r="212" ht="15.75" customHeight="1" s="4"/>
+    <row r="213" ht="15.75" customHeight="1" s="4"/>
+    <row r="214" ht="15.75" customHeight="1" s="4"/>
+    <row r="215" ht="15.75" customHeight="1" s="4"/>
+    <row r="216" ht="15.75" customHeight="1" s="4"/>
+    <row r="217" ht="15.75" customHeight="1" s="4"/>
+    <row r="218" ht="15.75" customHeight="1" s="4"/>
+    <row r="219" ht="15.75" customHeight="1" s="4"/>
+    <row r="220" ht="15.75" customHeight="1" s="4"/>
+    <row r="221" ht="15.75" customHeight="1" s="4"/>
+    <row r="222" ht="15.75" customHeight="1" s="4"/>
+    <row r="223" ht="15.75" customHeight="1" s="4"/>
+    <row r="224" ht="15.75" customHeight="1" s="4"/>
+    <row r="225" ht="15.75" customHeight="1" s="4"/>
+    <row r="226" ht="15.75" customHeight="1" s="4"/>
+    <row r="227" ht="15.75" customHeight="1" s="4"/>
+    <row r="228" ht="15.75" customHeight="1" s="4"/>
+    <row r="229" ht="15.75" customHeight="1" s="4"/>
+    <row r="230" ht="15.75" customHeight="1" s="4"/>
+    <row r="231" ht="15.75" customHeight="1" s="4"/>
+    <row r="232" ht="15.75" customHeight="1" s="4"/>
+    <row r="233" ht="15.75" customHeight="1" s="4"/>
+    <row r="234" ht="15.75" customHeight="1" s="4"/>
+    <row r="235" ht="15.75" customHeight="1" s="4"/>
+    <row r="236" ht="15.75" customHeight="1" s="4"/>
+    <row r="237" ht="15.75" customHeight="1" s="4"/>
+    <row r="238" ht="15.75" customHeight="1" s="4"/>
+    <row r="239" ht="15.75" customHeight="1" s="4"/>
+    <row r="240" ht="15.75" customHeight="1" s="4"/>
+    <row r="241" ht="15.75" customHeight="1" s="4"/>
+    <row r="242" ht="15.75" customHeight="1" s="4"/>
+    <row r="243" ht="15.75" customHeight="1" s="4"/>
+    <row r="244" ht="15.75" customHeight="1" s="4"/>
+    <row r="245" ht="15.75" customHeight="1" s="4"/>
+    <row r="246" ht="15.75" customHeight="1" s="4"/>
+    <row r="247" ht="15.75" customHeight="1" s="4"/>
+    <row r="248" ht="15.75" customHeight="1" s="4"/>
+    <row r="249" ht="15.75" customHeight="1" s="4"/>
+    <row r="250" ht="15.75" customHeight="1" s="4"/>
+    <row r="251" ht="15.75" customHeight="1" s="4"/>
+    <row r="252" ht="15.75" customHeight="1" s="4"/>
+    <row r="253" ht="15.75" customHeight="1" s="4"/>
+    <row r="254" ht="15.75" customHeight="1" s="4"/>
+    <row r="255" ht="15.75" customHeight="1" s="4"/>
+    <row r="256" ht="15.75" customHeight="1" s="4"/>
+    <row r="257" ht="15.75" customHeight="1" s="4"/>
+    <row r="258" ht="15.75" customHeight="1" s="4"/>
+    <row r="259" ht="15.75" customHeight="1" s="4"/>
+    <row r="260" ht="15.75" customHeight="1" s="4"/>
+    <row r="261" ht="15.75" customHeight="1" s="4"/>
+    <row r="262" ht="15.75" customHeight="1" s="4"/>
+    <row r="263" ht="15.75" customHeight="1" s="4"/>
+    <row r="264" ht="15.75" customHeight="1" s="4"/>
+    <row r="265" ht="15.75" customHeight="1" s="4"/>
+    <row r="266" ht="15.75" customHeight="1" s="4"/>
+    <row r="267" ht="15.75" customHeight="1" s="4"/>
+    <row r="268" ht="15.75" customHeight="1" s="4"/>
+    <row r="269" ht="15.75" customHeight="1" s="4"/>
+    <row r="270" ht="15.75" customHeight="1" s="4"/>
+    <row r="271" ht="15.75" customHeight="1" s="4"/>
+    <row r="272" ht="15.75" customHeight="1" s="4"/>
+    <row r="273" ht="15.75" customHeight="1" s="4"/>
+    <row r="274" ht="15.75" customHeight="1" s="4"/>
+    <row r="275" ht="15.75" customHeight="1" s="4"/>
+    <row r="276" ht="15.75" customHeight="1" s="4"/>
+    <row r="277" ht="15.75" customHeight="1" s="4"/>
+    <row r="278" ht="15.75" customHeight="1" s="4"/>
+    <row r="279" ht="15.75" customHeight="1" s="4"/>
+    <row r="280" ht="15.75" customHeight="1" s="4"/>
+    <row r="281" ht="15.75" customHeight="1" s="4"/>
+    <row r="282" ht="15.75" customHeight="1" s="4"/>
+    <row r="283" ht="15.75" customHeight="1" s="4"/>
+    <row r="284" ht="15.75" customHeight="1" s="4"/>
+    <row r="285" ht="15.75" customHeight="1" s="4"/>
+    <row r="286" ht="15.75" customHeight="1" s="4"/>
+    <row r="287" ht="15.75" customHeight="1" s="4"/>
+    <row r="288" ht="15.75" customHeight="1" s="4"/>
+    <row r="289" ht="15.75" customHeight="1" s="4"/>
+    <row r="290" ht="15.75" customHeight="1" s="4"/>
+    <row r="291" ht="15.75" customHeight="1" s="4"/>
+    <row r="292" ht="15.75" customHeight="1" s="4"/>
+    <row r="293" ht="15.75" customHeight="1" s="4"/>
+    <row r="294" ht="15.75" customHeight="1" s="4"/>
+    <row r="295" ht="15.75" customHeight="1" s="4"/>
+    <row r="296" ht="15.75" customHeight="1" s="4"/>
+    <row r="297" ht="15.75" customHeight="1" s="4"/>
+    <row r="298" ht="15.75" customHeight="1" s="4"/>
+    <row r="299" ht="15.75" customHeight="1" s="4"/>
+    <row r="300" ht="15.75" customHeight="1" s="4"/>
+    <row r="301" ht="15.75" customHeight="1" s="4"/>
+    <row r="302" ht="15.75" customHeight="1" s="4"/>
+    <row r="303" ht="15.75" customHeight="1" s="4"/>
+    <row r="304" ht="15.75" customHeight="1" s="4"/>
+    <row r="305" ht="15.75" customHeight="1" s="4"/>
+    <row r="306" ht="15.75" customHeight="1" s="4"/>
+    <row r="307" ht="15.75" customHeight="1" s="4"/>
+    <row r="308" ht="15.75" customHeight="1" s="4"/>
+    <row r="309" ht="15.75" customHeight="1" s="4"/>
+    <row r="310" ht="15.75" customHeight="1" s="4"/>
+    <row r="311" ht="15.75" customHeight="1" s="4"/>
+    <row r="312" ht="15.75" customHeight="1" s="4"/>
+    <row r="313" ht="15.75" customHeight="1" s="4"/>
+    <row r="314" ht="15.75" customHeight="1" s="4"/>
+    <row r="315" ht="15.75" customHeight="1" s="4"/>
+    <row r="316" ht="15.75" customHeight="1" s="4"/>
+    <row r="317" ht="15.75" customHeight="1" s="4"/>
+    <row r="318" ht="15.75" customHeight="1" s="4"/>
+    <row r="319" ht="15.75" customHeight="1" s="4"/>
+    <row r="320" ht="15.75" customHeight="1" s="4"/>
+    <row r="321" ht="15.75" customHeight="1" s="4"/>
+    <row r="322" ht="15.75" customHeight="1" s="4"/>
+    <row r="323" ht="15.75" customHeight="1" s="4"/>
+    <row r="324" ht="15.75" customHeight="1" s="4"/>
+    <row r="325" ht="15.75" customHeight="1" s="4"/>
+    <row r="326" ht="15.75" customHeight="1" s="4"/>
+    <row r="327" ht="15.75" customHeight="1" s="4"/>
+    <row r="328" ht="15.75" customHeight="1" s="4"/>
+    <row r="329" ht="15.75" customHeight="1" s="4"/>
+    <row r="330" ht="15.75" customHeight="1" s="4"/>
+    <row r="331" ht="15.75" customHeight="1" s="4"/>
+    <row r="332" ht="15.75" customHeight="1" s="4"/>
+    <row r="333" ht="15.75" customHeight="1" s="4"/>
+    <row r="334" ht="15.75" customHeight="1" s="4"/>
+    <row r="335" ht="15.75" customHeight="1" s="4"/>
+    <row r="336" ht="15.75" customHeight="1" s="4"/>
+    <row r="337" ht="15.75" customHeight="1" s="4"/>
+    <row r="338" ht="15.75" customHeight="1" s="4"/>
+    <row r="339" ht="15.75" customHeight="1" s="4"/>
+    <row r="340" ht="15.75" customHeight="1" s="4"/>
+    <row r="341" ht="15.75" customHeight="1" s="4"/>
+    <row r="342" ht="15.75" customHeight="1" s="4"/>
+    <row r="343" ht="15.75" customHeight="1" s="4"/>
+    <row r="344" ht="15.75" customHeight="1" s="4"/>
+    <row r="345" ht="15.75" customHeight="1" s="4"/>
+    <row r="346" ht="15.75" customHeight="1" s="4"/>
+    <row r="347" ht="15.75" customHeight="1" s="4"/>
+    <row r="348" ht="15.75" customHeight="1" s="4"/>
+    <row r="349" ht="15.75" customHeight="1" s="4"/>
+    <row r="350" ht="15.75" customHeight="1" s="4"/>
+    <row r="351" ht="15.75" customHeight="1" s="4"/>
+    <row r="352" ht="15.75" customHeight="1" s="4"/>
+    <row r="353" ht="15.75" customHeight="1" s="4"/>
+    <row r="354" ht="15.75" customHeight="1" s="4"/>
+    <row r="355" ht="15.75" customHeight="1" s="4"/>
+    <row r="356" ht="15.75" customHeight="1" s="4"/>
+    <row r="357" ht="15.75" customHeight="1" s="4"/>
+    <row r="358" ht="15.75" customHeight="1" s="4"/>
+    <row r="359" ht="15.75" customHeight="1" s="4"/>
+    <row r="360" ht="15.75" customHeight="1" s="4"/>
+    <row r="361" ht="15.75" customHeight="1" s="4"/>
+    <row r="362" ht="15.75" customHeight="1" s="4"/>
+    <row r="363" ht="15.75" customHeight="1" s="4"/>
+    <row r="364" ht="15.75" customHeight="1" s="4"/>
+    <row r="365" ht="15.75" customHeight="1" s="4"/>
+    <row r="366" ht="15.75" customHeight="1" s="4"/>
+    <row r="367" ht="15.75" customHeight="1" s="4"/>
+    <row r="368" ht="15.75" customHeight="1" s="4"/>
+    <row r="369" ht="15.75" customHeight="1" s="4"/>
+    <row r="370" ht="15.75" customHeight="1" s="4"/>
+    <row r="371" ht="15.75" customHeight="1" s="4"/>
+    <row r="372" ht="15.75" customHeight="1" s="4"/>
+    <row r="373" ht="15.75" customHeight="1" s="4"/>
+    <row r="374" ht="15.75" customHeight="1" s="4"/>
+    <row r="375" ht="15.75" customHeight="1" s="4"/>
+    <row r="376" ht="15.75" customHeight="1" s="4"/>
+    <row r="377" ht="15.75" customHeight="1" s="4"/>
+    <row r="378" ht="15.75" customHeight="1" s="4"/>
+    <row r="379" ht="15.75" customHeight="1" s="4"/>
+    <row r="380" ht="15.75" customHeight="1" s="4"/>
+    <row r="381" ht="15.75" customHeight="1" s="4"/>
+    <row r="382" ht="15.75" customHeight="1" s="4"/>
+    <row r="383" ht="15.75" customHeight="1" s="4"/>
+    <row r="384" ht="15.75" customHeight="1" s="4"/>
+    <row r="385" ht="15.75" customHeight="1" s="4"/>
+    <row r="386" ht="15.75" customHeight="1" s="4"/>
+    <row r="387" ht="15.75" customHeight="1" s="4"/>
+    <row r="388" ht="15.75" customHeight="1" s="4"/>
+    <row r="389" ht="15.75" customHeight="1" s="4"/>
+    <row r="390" ht="15.75" customHeight="1" s="4"/>
+    <row r="391" ht="15.75" customHeight="1" s="4"/>
+    <row r="392" ht="15.75" customHeight="1" s="4"/>
+    <row r="393" ht="15.75" customHeight="1" s="4"/>
+    <row r="394" ht="15.75" customHeight="1" s="4"/>
+    <row r="395" ht="15.75" customHeight="1" s="4"/>
+    <row r="396" ht="15.75" customHeight="1" s="4"/>
+    <row r="397" ht="15.75" customHeight="1" s="4"/>
+    <row r="398" ht="15.75" customHeight="1" s="4"/>
+    <row r="399" ht="15.75" customHeight="1" s="4"/>
+    <row r="400" ht="15.75" customHeight="1" s="4"/>
+    <row r="401" ht="15.75" customHeight="1" s="4"/>
+    <row r="402" ht="15.75" customHeight="1" s="4"/>
+    <row r="403" ht="15.75" customHeight="1" s="4"/>
+    <row r="404" ht="15.75" customHeight="1" s="4"/>
+    <row r="405" ht="15.75" customHeight="1" s="4"/>
+    <row r="406" ht="15.75" customHeight="1" s="4"/>
+    <row r="407" ht="15.75" customHeight="1" s="4"/>
+    <row r="408" ht="15.75" customHeight="1" s="4"/>
+    <row r="409" ht="15.75" customHeight="1" s="4"/>
+    <row r="410" ht="15.75" customHeight="1" s="4"/>
+    <row r="411" ht="15.75" customHeight="1" s="4"/>
+    <row r="412" ht="15.75" customHeight="1" s="4"/>
+    <row r="413" ht="15.75" customHeight="1" s="4"/>
+    <row r="414" ht="15.75" customHeight="1" s="4"/>
+    <row r="415" ht="15.75" customHeight="1" s="4"/>
+    <row r="416" ht="15.75" customHeight="1" s="4"/>
+    <row r="417" ht="15.75" customHeight="1" s="4"/>
+    <row r="418" ht="15.75" customHeight="1" s="4"/>
+    <row r="419" ht="15.75" customHeight="1" s="4"/>
+    <row r="420" ht="15.75" customHeight="1" s="4"/>
+    <row r="421" ht="15.75" customHeight="1" s="4"/>
+    <row r="422" ht="15.75" customHeight="1" s="4"/>
+    <row r="423" ht="15.75" customHeight="1" s="4"/>
+    <row r="424" ht="15.75" customHeight="1" s="4"/>
+    <row r="425" ht="15.75" customHeight="1" s="4"/>
+    <row r="426" ht="15.75" customHeight="1" s="4"/>
+    <row r="427" ht="15.75" customHeight="1" s="4"/>
+    <row r="428" ht="15.75" customHeight="1" s="4"/>
+    <row r="429" ht="15.75" customHeight="1" s="4"/>
+    <row r="430" ht="15.75" customHeight="1" s="4"/>
+    <row r="431" ht="15.75" customHeight="1" s="4"/>
+    <row r="432" ht="15.75" customHeight="1" s="4"/>
+    <row r="433" ht="15.75" customHeight="1" s="4"/>
+    <row r="434" ht="15.75" customHeight="1" s="4"/>
+    <row r="435" ht="15.75" customHeight="1" s="4"/>
+    <row r="436" ht="15.75" customHeight="1" s="4"/>
+    <row r="437" ht="15.75" customHeight="1" s="4"/>
+    <row r="438" ht="15.75" customHeight="1" s="4"/>
+    <row r="439" ht="15.75" customHeight="1" s="4"/>
+    <row r="440" ht="15.75" customHeight="1" s="4"/>
+    <row r="441" ht="15.75" customHeight="1" s="4"/>
+    <row r="442" ht="15.75" customHeight="1" s="4"/>
+    <row r="443" ht="15.75" customHeight="1" s="4"/>
+    <row r="444" ht="15.75" customHeight="1" s="4"/>
+    <row r="445" ht="15.75" customHeight="1" s="4"/>
+    <row r="446" ht="15.75" customHeight="1" s="4"/>
+    <row r="447" ht="15.75" customHeight="1" s="4"/>
+    <row r="448" ht="15.75" customHeight="1" s="4"/>
+    <row r="449" ht="15.75" customHeight="1" s="4"/>
+    <row r="450" ht="15.75" customHeight="1" s="4"/>
+    <row r="451" ht="15.75" customHeight="1" s="4"/>
+    <row r="452" ht="15.75" customHeight="1" s="4"/>
+    <row r="453" ht="15.75" customHeight="1" s="4"/>
+    <row r="454" ht="15.75" customHeight="1" s="4"/>
+    <row r="455" ht="15.75" customHeight="1" s="4"/>
+    <row r="456" ht="15.75" customHeight="1" s="4"/>
+    <row r="457" ht="15.75" customHeight="1" s="4"/>
+    <row r="458" ht="15.75" customHeight="1" s="4"/>
+    <row r="459" ht="15.75" customHeight="1" s="4"/>
+    <row r="460" ht="15.75" customHeight="1" s="4"/>
+    <row r="461" ht="15.75" customHeight="1" s="4"/>
+    <row r="462" ht="15.75" customHeight="1" s="4"/>
+    <row r="463" ht="15.75" customHeight="1" s="4"/>
+    <row r="464" ht="15.75" customHeight="1" s="4"/>
+    <row r="465" ht="15.75" customHeight="1" s="4"/>
+    <row r="466" ht="15.75" customHeight="1" s="4"/>
+    <row r="467" ht="15.75" customHeight="1" s="4"/>
+    <row r="468" ht="15.75" customHeight="1" s="4"/>
+    <row r="469" ht="15.75" customHeight="1" s="4"/>
+    <row r="470" ht="15.75" customHeight="1" s="4"/>
+    <row r="471" ht="15.75" customHeight="1" s="4"/>
+    <row r="472" ht="15.75" customHeight="1" s="4"/>
+    <row r="473" ht="15.75" customHeight="1" s="4"/>
+    <row r="474" ht="15.75" customHeight="1" s="4"/>
+    <row r="475" ht="15.75" customHeight="1" s="4"/>
+    <row r="476" ht="15.75" customHeight="1" s="4"/>
+    <row r="477" ht="15.75" customHeight="1" s="4"/>
+    <row r="478" ht="15.75" customHeight="1" s="4"/>
+    <row r="479" ht="15.75" customHeight="1" s="4"/>
+    <row r="480" ht="15.75" customHeight="1" s="4"/>
+    <row r="481" ht="15.75" customHeight="1" s="4"/>
+    <row r="482" ht="15.75" customHeight="1" s="4"/>
+    <row r="483" ht="15.75" customHeight="1" s="4"/>
+    <row r="484" ht="15.75" customHeight="1" s="4"/>
+    <row r="485" ht="15.75" customHeight="1" s="4"/>
+    <row r="486" ht="15.75" customHeight="1" s="4"/>
+    <row r="487" ht="15.75" customHeight="1" s="4"/>
+    <row r="488" ht="15.75" customHeight="1" s="4"/>
+    <row r="489" ht="15.75" customHeight="1" s="4"/>
+    <row r="490" ht="15.75" customHeight="1" s="4"/>
+    <row r="491" ht="15.75" customHeight="1" s="4"/>
+    <row r="492" ht="15.75" customHeight="1" s="4"/>
+    <row r="493" ht="15.75" customHeight="1" s="4"/>
+    <row r="494" ht="15.75" customHeight="1" s="4"/>
+    <row r="495" ht="15.75" customHeight="1" s="4"/>
+    <row r="496" ht="15.75" customHeight="1" s="4"/>
+    <row r="497" ht="15.75" customHeight="1" s="4"/>
+    <row r="498" ht="15.75" customHeight="1" s="4"/>
+    <row r="499" ht="15.75" customHeight="1" s="4"/>
+    <row r="500" ht="15.75" customHeight="1" s="4"/>
+    <row r="501" ht="15.75" customHeight="1" s="4"/>
+    <row r="502" ht="15.75" customHeight="1" s="4"/>
+    <row r="503" ht="15.75" customHeight="1" s="4"/>
+    <row r="504" ht="15.75" customHeight="1" s="4"/>
+    <row r="505" ht="15.75" customHeight="1" s="4"/>
+    <row r="506" ht="15.75" customHeight="1" s="4"/>
+    <row r="507" ht="15.75" customHeight="1" s="4"/>
+    <row r="508" ht="15.75" customHeight="1" s="4"/>
+    <row r="509" ht="15.75" customHeight="1" s="4"/>
+    <row r="510" ht="15.75" customHeight="1" s="4"/>
+    <row r="511" ht="15.75" customHeight="1" s="4"/>
+    <row r="512" ht="15.75" customHeight="1" s="4"/>
+    <row r="513" ht="15.75" customHeight="1" s="4"/>
+    <row r="514" ht="15.75" customHeight="1" s="4"/>
+    <row r="515" ht="15.75" customHeight="1" s="4"/>
+    <row r="516" ht="15.75" customHeight="1" s="4"/>
+    <row r="517" ht="15.75" customHeight="1" s="4"/>
+    <row r="518" ht="15.75" customHeight="1" s="4"/>
+    <row r="519" ht="15.75" customHeight="1" s="4"/>
+    <row r="520" ht="15.75" customHeight="1" s="4"/>
+    <row r="521" ht="15.75" customHeight="1" s="4"/>
+    <row r="522" ht="15.75" customHeight="1" s="4"/>
+    <row r="523" ht="15.75" customHeight="1" s="4"/>
+    <row r="524" ht="15.75" customHeight="1" s="4"/>
+    <row r="525" ht="15.75" customHeight="1" s="4"/>
+    <row r="526" ht="15.75" customHeight="1" s="4"/>
+    <row r="527" ht="15.75" customHeight="1" s="4"/>
+    <row r="528" ht="15.75" customHeight="1" s="4"/>
+    <row r="529" ht="15.75" customHeight="1" s="4"/>
+    <row r="530" ht="15.75" customHeight="1" s="4"/>
+    <row r="531" ht="15.75" customHeight="1" s="4"/>
+    <row r="532" ht="15.75" customHeight="1" s="4"/>
+    <row r="533" ht="15.75" customHeight="1" s="4"/>
+    <row r="534" ht="15.75" customHeight="1" s="4"/>
+    <row r="535" ht="15.75" customHeight="1" s="4"/>
+    <row r="536" ht="15.75" customHeight="1" s="4"/>
+    <row r="537" ht="15.75" customHeight="1" s="4"/>
+    <row r="538" ht="15.75" customHeight="1" s="4"/>
+    <row r="539" ht="15.75" customHeight="1" s="4"/>
+    <row r="540" ht="15.75" customHeight="1" s="4"/>
+    <row r="541" ht="15.75" customHeight="1" s="4"/>
+    <row r="542" ht="15.75" customHeight="1" s="4"/>
+    <row r="543" ht="15.75" customHeight="1" s="4"/>
+    <row r="544" ht="15.75" customHeight="1" s="4"/>
+    <row r="545" ht="15.75" customHeight="1" s="4"/>
+    <row r="546" ht="15.75" customHeight="1" s="4"/>
+    <row r="547" ht="15.75" customHeight="1" s="4"/>
+    <row r="548" ht="15.75" customHeight="1" s="4"/>
+    <row r="549" ht="15.75" customHeight="1" s="4"/>
+    <row r="550" ht="15.75" customHeight="1" s="4"/>
+    <row r="551" ht="15.75" customHeight="1" s="4"/>
+    <row r="552" ht="15.75" customHeight="1" s="4"/>
+    <row r="553" ht="15.75" customHeight="1" s="4"/>
+    <row r="554" ht="15.75" customHeight="1" s="4"/>
+    <row r="555" ht="15.75" customHeight="1" s="4"/>
+    <row r="556" ht="15.75" customHeight="1" s="4"/>
+    <row r="557" ht="15.75" customHeight="1" s="4"/>
+    <row r="558" ht="15.75" customHeight="1" s="4"/>
+    <row r="559" ht="15.75" customHeight="1" s="4"/>
+    <row r="560" ht="15.75" customHeight="1" s="4"/>
+    <row r="561" ht="15.75" customHeight="1" s="4"/>
+    <row r="562" ht="15.75" customHeight="1" s="4"/>
+    <row r="563" ht="15.75" customHeight="1" s="4"/>
+    <row r="564" ht="15.75" customHeight="1" s="4"/>
+    <row r="565" ht="15.75" customHeight="1" s="4"/>
+    <row r="566" ht="15.75" customHeight="1" s="4"/>
+    <row r="567" ht="15.75" customHeight="1" s="4"/>
+    <row r="568" ht="15.75" customHeight="1" s="4"/>
+    <row r="569" ht="15.75" customHeight="1" s="4"/>
+    <row r="570" ht="15.75" customHeight="1" s="4"/>
+    <row r="571" ht="15.75" customHeight="1" s="4"/>
+    <row r="572" ht="15.75" customHeight="1" s="4"/>
+    <row r="573" ht="15.75" customHeight="1" s="4"/>
+    <row r="574" ht="15.75" customHeight="1" s="4"/>
+    <row r="575" ht="15.75" customHeight="1" s="4"/>
+    <row r="576" ht="15.75" customHeight="1" s="4"/>
+    <row r="577" ht="15.75" customHeight="1" s="4"/>
+    <row r="578" ht="15.75" customHeight="1" s="4"/>
+    <row r="579" ht="15.75" customHeight="1" s="4"/>
+    <row r="580" ht="15.75" customHeight="1" s="4"/>
+    <row r="581" ht="15.75" customHeight="1" s="4"/>
+    <row r="582" ht="15.75" customHeight="1" s="4"/>
+    <row r="583" ht="15.75" customHeight="1" s="4"/>
+    <row r="584" ht="15.75" customHeight="1" s="4"/>
+    <row r="585" ht="15.75" customHeight="1" s="4"/>
+    <row r="586" ht="15.75" customHeight="1" s="4"/>
+    <row r="587" ht="15.75" customHeight="1" s="4"/>
+    <row r="588" ht="15.75" customHeight="1" s="4"/>
+    <row r="589" ht="15.75" customHeight="1" s="4"/>
+    <row r="590" ht="15.75" customHeight="1" s="4"/>
+    <row r="591" ht="15.75" customHeight="1" s="4"/>
+    <row r="592" ht="15.75" customHeight="1" s="4"/>
+    <row r="593" ht="15.75" customHeight="1" s="4"/>
+    <row r="594" ht="15.75" customHeight="1" s="4"/>
+    <row r="595" ht="15.75" customHeight="1" s="4"/>
+    <row r="596" ht="15.75" customHeight="1" s="4"/>
+    <row r="597" ht="15.75" customHeight="1" s="4"/>
+    <row r="598" ht="15.75" customHeight="1" s="4"/>
+    <row r="599" ht="15.75" customHeight="1" s="4"/>
+    <row r="600" ht="15.75" customHeight="1" s="4"/>
+    <row r="601" ht="15.75" customHeight="1" s="4"/>
+    <row r="602" ht="15.75" customHeight="1" s="4"/>
+    <row r="603" ht="15.75" customHeight="1" s="4"/>
+    <row r="604" ht="15.75" customHeight="1" s="4"/>
+    <row r="605" ht="15.75" customHeight="1" s="4"/>
+    <row r="606" ht="15.75" customHeight="1" s="4"/>
+    <row r="607" ht="15.75" customHeight="1" s="4"/>
+    <row r="608" ht="15.75" customHeight="1" s="4"/>
+    <row r="609" ht="15.75" customHeight="1" s="4"/>
+    <row r="610" ht="15.75" customHeight="1" s="4"/>
+    <row r="611" ht="15.75" customHeight="1" s="4"/>
+    <row r="612" ht="15.75" customHeight="1" s="4"/>
+    <row r="613" ht="15.75" customHeight="1" s="4"/>
+    <row r="614" ht="15.75" customHeight="1" s="4"/>
+    <row r="615" ht="15.75" customHeight="1" s="4"/>
+    <row r="616" ht="15.75" customHeight="1" s="4"/>
+    <row r="617" ht="15.75" customHeight="1" s="4"/>
+    <row r="618" ht="15.75" customHeight="1" s="4"/>
+    <row r="619" ht="15.75" customHeight="1" s="4"/>
+    <row r="620" ht="15.75" customHeight="1" s="4"/>
+    <row r="621" ht="15.75" customHeight="1" s="4"/>
+    <row r="622" ht="15.75" customHeight="1" s="4"/>
+    <row r="623" ht="15.75" customHeight="1" s="4"/>
+    <row r="624" ht="15.75" customHeight="1" s="4"/>
+    <row r="625" ht="15.75" customHeight="1" s="4"/>
+    <row r="626" ht="15.75" customHeight="1" s="4"/>
+    <row r="627" ht="15.75" customHeight="1" s="4"/>
+    <row r="628" ht="15.75" customHeight="1" s="4"/>
+    <row r="629" ht="15.75" customHeight="1" s="4"/>
+    <row r="630" ht="15.75" customHeight="1" s="4"/>
+    <row r="631" ht="15.75" customHeight="1" s="4"/>
+    <row r="632" ht="15.75" customHeight="1" s="4"/>
+    <row r="633" ht="15.75" customHeight="1" s="4"/>
+    <row r="634" ht="15.75" customHeight="1" s="4"/>
+    <row r="635" ht="15.75" customHeight="1" s="4"/>
+    <row r="636" ht="15.75" customHeight="1" s="4"/>
+    <row r="637" ht="15.75" customHeight="1" s="4"/>
+    <row r="638" ht="15.75" customHeight="1" s="4"/>
+    <row r="639" ht="15.75" customHeight="1" s="4"/>
+    <row r="640" ht="15.75" customHeight="1" s="4"/>
+    <row r="641" ht="15.75" customHeight="1" s="4"/>
+    <row r="642" ht="15.75" customHeight="1" s="4"/>
+    <row r="643" ht="15.75" customHeight="1" s="4"/>
+    <row r="644" ht="15.75" customHeight="1" s="4"/>
+    <row r="645" ht="15.75" customHeight="1" s="4"/>
+    <row r="646" ht="15.75" customHeight="1" s="4"/>
+    <row r="647" ht="15.75" customHeight="1" s="4"/>
+    <row r="648" ht="15.75" customHeight="1" s="4"/>
+    <row r="649" ht="15.75" customHeight="1" s="4"/>
+    <row r="650" ht="15.75" customHeight="1" s="4"/>
+    <row r="651" ht="15.75" customHeight="1" s="4"/>
+    <row r="652" ht="15.75" customHeight="1" s="4"/>
+    <row r="653" ht="15.75" customHeight="1" s="4"/>
+    <row r="654" ht="15.75" customHeight="1" s="4"/>
+    <row r="655" ht="15.75" customHeight="1" s="4"/>
+    <row r="656" ht="15.75" customHeight="1" s="4"/>
+    <row r="657" ht="15.75" customHeight="1" s="4"/>
+    <row r="658" ht="15.75" customHeight="1" s="4"/>
+    <row r="659" ht="15.75" customHeight="1" s="4"/>
+    <row r="660" ht="15.75" customHeight="1" s="4"/>
+    <row r="661" ht="15.75" customHeight="1" s="4"/>
+    <row r="662" ht="15.75" customHeight="1" s="4"/>
+    <row r="663" ht="15.75" customHeight="1" s="4"/>
+    <row r="664" ht="15.75" customHeight="1" s="4"/>
+    <row r="665" ht="15.75" customHeight="1" s="4"/>
+    <row r="666" ht="15.75" customHeight="1" s="4"/>
+    <row r="667" ht="15.75" customHeight="1" s="4"/>
+    <row r="668" ht="15.75" customHeight="1" s="4"/>
+    <row r="669" ht="15.75" customHeight="1" s="4"/>
+    <row r="670" ht="15.75" customHeight="1" s="4"/>
+    <row r="671" ht="15.75" customHeight="1" s="4"/>
+    <row r="672" ht="15.75" customHeight="1" s="4"/>
+    <row r="673" ht="15.75" customHeight="1" s="4"/>
+    <row r="674" ht="15.75" customHeight="1" s="4"/>
+    <row r="675" ht="15.75" customHeight="1" s="4"/>
+    <row r="676" ht="15.75" customHeight="1" s="4"/>
+    <row r="677" ht="15.75" customHeight="1" s="4"/>
+    <row r="678" ht="15.75" customHeight="1" s="4"/>
+    <row r="679" ht="15.75" customHeight="1" s="4"/>
+    <row r="680" ht="15.75" customHeight="1" s="4"/>
+    <row r="681" ht="15.75" customHeight="1" s="4"/>
+    <row r="682" ht="15.75" customHeight="1" s="4"/>
+    <row r="683" ht="15.75" customHeight="1" s="4"/>
+    <row r="684" ht="15.75" customHeight="1" s="4"/>
+    <row r="685" ht="15.75" customHeight="1" s="4"/>
+    <row r="686" ht="15.75" customHeight="1" s="4"/>
+    <row r="687" ht="15.75" customHeight="1" s="4"/>
+    <row r="688" ht="15.75" customHeight="1" s="4"/>
+    <row r="689" ht="15.75" customHeight="1" s="4"/>
+    <row r="690" ht="15.75" customHeight="1" s="4"/>
+    <row r="691" ht="15.75" customHeight="1" s="4"/>
+    <row r="692" ht="15.75" customHeight="1" s="4"/>
+    <row r="693" ht="15.75" customHeight="1" s="4"/>
+    <row r="694" ht="15.75" customHeight="1" s="4"/>
+    <row r="695" ht="15.75" customHeight="1" s="4"/>
+    <row r="696" ht="15.75" customHeight="1" s="4"/>
+    <row r="697" ht="15.75" customHeight="1" s="4"/>
+    <row r="698" ht="15.75" customHeight="1" s="4"/>
+    <row r="699" ht="15.75" customHeight="1" s="4"/>
+    <row r="700" ht="15.75" customHeight="1" s="4"/>
+    <row r="701" ht="15.75" customHeight="1" s="4"/>
+    <row r="702" ht="15.75" customHeight="1" s="4"/>
+    <row r="703" ht="15.75" customHeight="1" s="4"/>
+    <row r="704" ht="15.75" customHeight="1" s="4"/>
+    <row r="705" ht="15.75" customHeight="1" s="4"/>
+    <row r="706" ht="15.75" customHeight="1" s="4"/>
+    <row r="707" ht="15.75" customHeight="1" s="4"/>
+    <row r="708" ht="15.75" customHeight="1" s="4"/>
+    <row r="709" ht="15.75" customHeight="1" s="4"/>
+    <row r="710" ht="15.75" customHeight="1" s="4"/>
+    <row r="711" ht="15.75" customHeight="1" s="4"/>
+    <row r="712" ht="15.75" customHeight="1" s="4"/>
+    <row r="713" ht="15.75" customHeight="1" s="4"/>
+    <row r="714" ht="15.75" customHeight="1" s="4"/>
+    <row r="715" ht="15.75" customHeight="1" s="4"/>
+    <row r="716" ht="15.75" customHeight="1" s="4"/>
+    <row r="717" ht="15.75" customHeight="1" s="4"/>
+    <row r="718" ht="15.75" customHeight="1" s="4"/>
+    <row r="719" ht="15.75" customHeight="1" s="4"/>
+    <row r="720" ht="15.75" customHeight="1" s="4"/>
+    <row r="721" ht="15.75" customHeight="1" s="4"/>
+    <row r="722" ht="15.75" customHeight="1" s="4"/>
+    <row r="723" ht="15.75" customHeight="1" s="4"/>
+    <row r="724" ht="15.75" customHeight="1" s="4"/>
+    <row r="725" ht="15.75" customHeight="1" s="4"/>
+    <row r="726" ht="15.75" customHeight="1" s="4"/>
+    <row r="727" ht="15.75" customHeight="1" s="4"/>
+    <row r="728" ht="15.75" customHeight="1" s="4"/>
+    <row r="729" ht="15.75" customHeight="1" s="4"/>
+    <row r="730" ht="15.75" customHeight="1" s="4"/>
+    <row r="731" ht="15.75" customHeight="1" s="4"/>
+    <row r="732" ht="15.75" customHeight="1" s="4"/>
+    <row r="733" ht="15.75" customHeight="1" s="4"/>
+    <row r="734" ht="15.75" customHeight="1" s="4"/>
+    <row r="735" ht="15.75" customHeight="1" s="4"/>
+    <row r="736" ht="15.75" customHeight="1" s="4"/>
+    <row r="737" ht="15.75" customHeight="1" s="4"/>
+    <row r="738" ht="15.75" customHeight="1" s="4"/>
+    <row r="739" ht="15.75" customHeight="1" s="4"/>
+    <row r="740" ht="15.75" customHeight="1" s="4"/>
+    <row r="741" ht="15.75" customHeight="1" s="4"/>
+    <row r="742" ht="15.75" customHeight="1" s="4"/>
+    <row r="743" ht="15.75" customHeight="1" s="4"/>
+    <row r="744" ht="15.75" customHeight="1" s="4"/>
+    <row r="745" ht="15.75" customHeight="1" s="4"/>
+    <row r="746" ht="15.75" customHeight="1" s="4"/>
+    <row r="747" ht="15.75" customHeight="1" s="4"/>
+    <row r="748" ht="15.75" customHeight="1" s="4"/>
+    <row r="749" ht="15.75" customHeight="1" s="4"/>
+    <row r="750" ht="15.75" customHeight="1" s="4"/>
+    <row r="751" ht="15.75" customHeight="1" s="4"/>
+    <row r="752" ht="15.75" customHeight="1" s="4"/>
+    <row r="753" ht="15.75" customHeight="1" s="4"/>
+    <row r="754" ht="15.75" customHeight="1" s="4"/>
+    <row r="755" ht="15.75" customHeight="1" s="4"/>
+    <row r="756" ht="15.75" customHeight="1" s="4"/>
+    <row r="757" ht="15.75" customHeight="1" s="4"/>
+    <row r="758" ht="15.75" customHeight="1" s="4"/>
+    <row r="759" ht="15.75" customHeight="1" s="4"/>
+    <row r="760" ht="15.75" customHeight="1" s="4"/>
+    <row r="761" ht="15.75" customHeight="1" s="4"/>
+    <row r="762" ht="15.75" customHeight="1" s="4"/>
+    <row r="763" ht="15.75" customHeight="1" s="4"/>
+    <row r="764" ht="15.75" customHeight="1" s="4"/>
+    <row r="765" ht="15.75" customHeight="1" s="4"/>
+    <row r="766" ht="15.75" customHeight="1" s="4"/>
+    <row r="767" ht="15.75" customHeight="1" s="4"/>
+    <row r="768" ht="15.75" customHeight="1" s="4"/>
+    <row r="769" ht="15.75" customHeight="1" s="4"/>
+    <row r="770" ht="15.75" customHeight="1" s="4"/>
+    <row r="771" ht="15.75" customHeight="1" s="4"/>
+    <row r="772" ht="15.75" customHeight="1" s="4"/>
+    <row r="773" ht="15.75" customHeight="1" s="4"/>
+    <row r="774" ht="15.75" customHeight="1" s="4"/>
+    <row r="775" ht="15.75" customHeight="1" s="4"/>
+    <row r="776" ht="15.75" customHeight="1" s="4"/>
+    <row r="777" ht="15.75" customHeight="1" s="4"/>
+    <row r="778" ht="15.75" customHeight="1" s="4"/>
+    <row r="779" ht="15.75" customHeight="1" s="4"/>
+    <row r="780" ht="15.75" customHeight="1" s="4"/>
+    <row r="781" ht="15.75" customHeight="1" s="4"/>
+    <row r="782" ht="15.75" customHeight="1" s="4"/>
+    <row r="783" ht="15.75" customHeight="1" s="4"/>
+    <row r="784" ht="15.75" customHeight="1" s="4"/>
+    <row r="785" ht="15.75" customHeight="1" s="4"/>
+    <row r="786" ht="15.75" customHeight="1" s="4"/>
+    <row r="787" ht="15.75" customHeight="1" s="4"/>
+    <row r="788" ht="15.75" customHeight="1" s="4"/>
+    <row r="789" ht="15.75" customHeight="1" s="4"/>
+    <row r="790" ht="15.75" customHeight="1" s="4"/>
+    <row r="791" ht="15.75" customHeight="1" s="4"/>
+    <row r="792" ht="15.75" customHeight="1" s="4"/>
+    <row r="793" ht="15.75" customHeight="1" s="4"/>
+    <row r="794" ht="15.75" customHeight="1" s="4"/>
+    <row r="795" ht="15.75" customHeight="1" s="4"/>
+    <row r="796" ht="15.75" customHeight="1" s="4"/>
+    <row r="797" ht="15.75" customHeight="1" s="4"/>
+    <row r="798" ht="15.75" customHeight="1" s="4"/>
+    <row r="799" ht="15.75" customHeight="1" s="4"/>
+    <row r="800" ht="15.75" customHeight="1" s="4"/>
+    <row r="801" ht="15.75" customHeight="1" s="4"/>
+    <row r="802" ht="15.75" customHeight="1" s="4"/>
+    <row r="803" ht="15.75" customHeight="1" s="4"/>
+    <row r="804" ht="15.75" customHeight="1" s="4"/>
+    <row r="805" ht="15.75" customHeight="1" s="4"/>
+    <row r="806" ht="15.75" customHeight="1" s="4"/>
+    <row r="807" ht="15.75" customHeight="1" s="4"/>
+    <row r="808" ht="15.75" customHeight="1" s="4"/>
+    <row r="809" ht="15.75" customHeight="1" s="4"/>
+    <row r="810" ht="15.75" customHeight="1" s="4"/>
+    <row r="811" ht="15.75" customHeight="1" s="4"/>
+    <row r="812" ht="15.75" customHeight="1" s="4"/>
+    <row r="813" ht="15.75" customHeight="1" s="4"/>
+    <row r="814" ht="15.75" customHeight="1" s="4"/>
+    <row r="815" ht="15.75" customHeight="1" s="4"/>
+    <row r="816" ht="15.75" customHeight="1" s="4"/>
+    <row r="817" ht="15.75" customHeight="1" s="4"/>
+    <row r="818" ht="15.75" customHeight="1" s="4"/>
+    <row r="819" ht="15.75" customHeight="1" s="4"/>
+    <row r="820" ht="15.75" customHeight="1" s="4"/>
+    <row r="821" ht="15.75" customHeight="1" s="4"/>
+    <row r="822" ht="15.75" customHeight="1" s="4"/>
+    <row r="823" ht="15.75" customHeight="1" s="4"/>
+    <row r="824" ht="15.75" customHeight="1" s="4"/>
+    <row r="825" ht="15.75" customHeight="1" s="4"/>
+    <row r="826" ht="15.75" customHeight="1" s="4"/>
+    <row r="827" ht="15.75" customHeight="1" s="4"/>
+    <row r="828" ht="15.75" customHeight="1" s="4"/>
+    <row r="829" ht="15.75" customHeight="1" s="4"/>
+    <row r="830" ht="15.75" customHeight="1" s="4"/>
+    <row r="831" ht="15.75" customHeight="1" s="4"/>
+    <row r="832" ht="15.75" customHeight="1" s="4"/>
+    <row r="833" ht="15.75" customHeight="1" s="4"/>
+    <row r="834" ht="15.75" customHeight="1" s="4"/>
+    <row r="835" ht="15.75" customHeight="1" s="4"/>
+    <row r="836" ht="15.75" customHeight="1" s="4"/>
+    <row r="837" ht="15.75" customHeight="1" s="4"/>
+    <row r="838" ht="15.75" customHeight="1" s="4"/>
+    <row r="839" ht="15.75" customHeight="1" s="4"/>
+    <row r="840" ht="15.75" customHeight="1" s="4"/>
+    <row r="841" ht="15.75" customHeight="1" s="4"/>
+    <row r="842" ht="15.75" customHeight="1" s="4"/>
+    <row r="843" ht="15.75" customHeight="1" s="4"/>
+    <row r="844" ht="15.75" customHeight="1" s="4"/>
+    <row r="845" ht="15.75" customHeight="1" s="4"/>
+    <row r="846" ht="15.75" customHeight="1" s="4"/>
+    <row r="847" ht="15.75" customHeight="1" s="4"/>
+    <row r="848" ht="15.75" customHeight="1" s="4"/>
+    <row r="849" ht="15.75" customHeight="1" s="4"/>
+    <row r="850" ht="15.75" customHeight="1" s="4"/>
+    <row r="851" ht="15.75" customHeight="1" s="4"/>
+    <row r="852" ht="15.75" customHeight="1" s="4"/>
+    <row r="853" ht="15.75" customHeight="1" s="4"/>
+    <row r="854" ht="15.75" customHeight="1" s="4"/>
+    <row r="855" ht="15.75" customHeight="1" s="4"/>
+    <row r="856" ht="15.75" customHeight="1" s="4"/>
+    <row r="857" ht="15.75" customHeight="1" s="4"/>
+    <row r="858" ht="15.75" customHeight="1" s="4"/>
+    <row r="859" ht="15.75" customHeight="1" s="4"/>
+    <row r="860" ht="15.75" customHeight="1" s="4"/>
+    <row r="861" ht="15.75" customHeight="1" s="4"/>
+    <row r="862" ht="15.75" customHeight="1" s="4"/>
+    <row r="863" ht="15.75" customHeight="1" s="4"/>
+    <row r="864" ht="15.75" customHeight="1" s="4"/>
+    <row r="865" ht="15.75" customHeight="1" s="4"/>
+    <row r="866" ht="15.75" customHeight="1" s="4"/>
+    <row r="867" ht="15.75" customHeight="1" s="4"/>
+    <row r="868" ht="15.75" customHeight="1" s="4"/>
+    <row r="869" ht="15.75" customHeight="1" s="4"/>
+    <row r="870" ht="15.75" customHeight="1" s="4"/>
+    <row r="871" ht="15.75" customHeight="1" s="4"/>
+    <row r="872" ht="15.75" customHeight="1" s="4"/>
+    <row r="873" ht="15.75" customHeight="1" s="4"/>
+    <row r="874" ht="15.75" customHeight="1" s="4"/>
+    <row r="875" ht="15.75" customHeight="1" s="4"/>
+    <row r="876" ht="15.75" customHeight="1" s="4"/>
+    <row r="877" ht="15.75" customHeight="1" s="4"/>
+    <row r="878" ht="15.75" customHeight="1" s="4"/>
+    <row r="879" ht="15.75" customHeight="1" s="4"/>
+    <row r="880" ht="15.75" customHeight="1" s="4"/>
+    <row r="881" ht="15.75" customHeight="1" s="4"/>
+    <row r="882" ht="15.75" customHeight="1" s="4"/>
+    <row r="883" ht="15.75" customHeight="1" s="4"/>
+    <row r="884" ht="15.75" customHeight="1" s="4"/>
+    <row r="885" ht="15.75" customHeight="1" s="4"/>
+    <row r="886" ht="15.75" customHeight="1" s="4"/>
+    <row r="887" ht="15.75" customHeight="1" s="4"/>
+    <row r="888" ht="15.75" customHeight="1" s="4"/>
+    <row r="889" ht="15.75" customHeight="1" s="4"/>
+    <row r="890" ht="15.75" customHeight="1" s="4"/>
+    <row r="891" ht="15.75" customHeight="1" s="4"/>
+    <row r="892" ht="15.75" customHeight="1" s="4"/>
+    <row r="893" ht="15.75" customHeight="1" s="4"/>
+    <row r="894" ht="15.75" customHeight="1" s="4"/>
+    <row r="895" ht="15.75" customHeight="1" s="4"/>
+    <row r="896" ht="15.75" customHeight="1" s="4"/>
+    <row r="897" ht="15.75" customHeight="1" s="4"/>
+    <row r="898" ht="15.75" customHeight="1" s="4"/>
+    <row r="899" ht="15.75" customHeight="1" s="4"/>
+    <row r="900" ht="15.75" customHeight="1" s="4"/>
+    <row r="901" ht="15.75" customHeight="1" s="4"/>
+    <row r="902" ht="15.75" customHeight="1" s="4"/>
+    <row r="903" ht="15.75" customHeight="1" s="4"/>
+    <row r="904" ht="15.75" customHeight="1" s="4"/>
+    <row r="905" ht="15.75" customHeight="1" s="4"/>
+    <row r="906" ht="15.75" customHeight="1" s="4"/>
+    <row r="907" ht="15.75" customHeight="1" s="4"/>
+    <row r="908" ht="15.75" customHeight="1" s="4"/>
+    <row r="909" ht="15.75" customHeight="1" s="4"/>
+    <row r="910" ht="15.75" customHeight="1" s="4"/>
+    <row r="911" ht="15.75" customHeight="1" s="4"/>
+    <row r="912" ht="15.75" customHeight="1" s="4"/>
+    <row r="913" ht="15.75" customHeight="1" s="4"/>
+    <row r="914" ht="15.75" customHeight="1" s="4"/>
+    <row r="915" ht="15.75" customHeight="1" s="4"/>
+    <row r="916" ht="15.75" customHeight="1" s="4"/>
+    <row r="917" ht="15.75" customHeight="1" s="4"/>
+    <row r="918" ht="15.75" customHeight="1" s="4"/>
+    <row r="919" ht="15.75" customHeight="1" s="4"/>
+    <row r="920" ht="15.75" customHeight="1" s="4"/>
+    <row r="921" ht="15.75" customHeight="1" s="4"/>
+    <row r="922" ht="15.75" customHeight="1" s="4"/>
+    <row r="923" ht="15.75" customHeight="1" s="4"/>
+    <row r="924" ht="15.75" customHeight="1" s="4"/>
+    <row r="925" ht="15.75" customHeight="1" s="4"/>
+    <row r="926" ht="15.75" customHeight="1" s="4"/>
+    <row r="927" ht="15.75" customHeight="1" s="4"/>
+    <row r="928" ht="15.75" customHeight="1" s="4"/>
+    <row r="929" ht="15.75" customHeight="1" s="4"/>
+    <row r="930" ht="15.75" customHeight="1" s="4"/>
+    <row r="931" ht="15.75" customHeight="1" s="4"/>
+    <row r="932" ht="15.75" customHeight="1" s="4"/>
+    <row r="933" ht="15.75" customHeight="1" s="4"/>
+    <row r="934" ht="15.75" customHeight="1" s="4"/>
+    <row r="935" ht="15.75" customHeight="1" s="4"/>
+    <row r="936" ht="15.75" customHeight="1" s="4"/>
+    <row r="937" ht="15.75" customHeight="1" s="4"/>
+    <row r="938" ht="15.75" customHeight="1" s="4"/>
+    <row r="939" ht="15.75" customHeight="1" s="4"/>
+    <row r="940" ht="15.75" customHeight="1" s="4"/>
+    <row r="941" ht="15.75" customHeight="1" s="4"/>
+    <row r="942" ht="15.75" customHeight="1" s="4"/>
+    <row r="943" ht="15.75" customHeight="1" s="4"/>
+    <row r="944" ht="15.75" customHeight="1" s="4"/>
+    <row r="945" ht="15.75" customHeight="1" s="4"/>
+    <row r="946" ht="15.75" customHeight="1" s="4"/>
+    <row r="947" ht="15.75" customHeight="1" s="4"/>
+    <row r="948" ht="15.75" customHeight="1" s="4"/>
+    <row r="949" ht="15.75" customHeight="1" s="4"/>
+    <row r="950" ht="15.75" customHeight="1" s="4"/>
+    <row r="951" ht="15.75" customHeight="1" s="4"/>
+    <row r="952" ht="15.75" customHeight="1" s="4"/>
+    <row r="953" ht="15.75" customHeight="1" s="4"/>
+    <row r="954" ht="15.75" customHeight="1" s="4"/>
+    <row r="955" ht="15.75" customHeight="1" s="4"/>
+    <row r="956" ht="15.75" customHeight="1" s="4"/>
+    <row r="957" ht="15.75" customHeight="1" s="4"/>
+    <row r="958" ht="15.75" customHeight="1" s="4"/>
+    <row r="959" ht="15.75" customHeight="1" s="4"/>
+    <row r="960" ht="15.75" customHeight="1" s="4"/>
+    <row r="961" ht="15.75" customHeight="1" s="4"/>
+    <row r="962" ht="15.75" customHeight="1" s="4"/>
+    <row r="963" ht="15.75" customHeight="1" s="4"/>
+    <row r="964" ht="15.75" customHeight="1" s="4"/>
+    <row r="965" ht="15.75" customHeight="1" s="4"/>
+    <row r="966" ht="15.75" customHeight="1" s="4"/>
+    <row r="967" ht="15.75" customHeight="1" s="4"/>
+    <row r="968" ht="15.75" customHeight="1" s="4"/>
+    <row r="969" ht="15.75" customHeight="1" s="4"/>
+    <row r="970" ht="15.75" customHeight="1" s="4"/>
+    <row r="971" ht="15.75" customHeight="1" s="4"/>
+    <row r="972" ht="15.75" customHeight="1" s="4"/>
+    <row r="973" ht="15.75" customHeight="1" s="4"/>
+    <row r="974" ht="15.75" customHeight="1" s="4"/>
+    <row r="975" ht="15.75" customHeight="1" s="4"/>
+    <row r="976" ht="15.75" customHeight="1" s="4"/>
+    <row r="977" ht="15.75" customHeight="1" s="4"/>
+    <row r="978" ht="15.75" customHeight="1" s="4"/>
+    <row r="979" ht="15.75" customHeight="1" s="4"/>
+    <row r="980" ht="15.75" customHeight="1" s="4"/>
+    <row r="981" ht="15.75" customHeight="1" s="4"/>
+    <row r="982" ht="15.75" customHeight="1" s="4"/>
+    <row r="983" ht="15.75" customHeight="1" s="4"/>
+    <row r="984" ht="15.75" customHeight="1" s="4"/>
+    <row r="985" ht="15.75" customHeight="1" s="4"/>
+    <row r="986" ht="15.75" customHeight="1" s="4"/>
+    <row r="987" ht="15.75" customHeight="1" s="4"/>
+    <row r="988" ht="15.75" customHeight="1" s="4"/>
+    <row r="989" ht="15.75" customHeight="1" s="4"/>
+    <row r="990" ht="15.75" customHeight="1" s="4"/>
+    <row r="991" ht="15.75" customHeight="1" s="4"/>
+    <row r="992" ht="15.75" customHeight="1" s="4"/>
+    <row r="993" ht="15.75" customHeight="1" s="4"/>
+    <row r="994" ht="15.75" customHeight="1" s="4"/>
+    <row r="995" ht="15.75" customHeight="1" s="4"/>
+    <row r="996" ht="15.75" customHeight="1" s="4"/>
+    <row r="997" ht="15.75" customHeight="1" s="4"/>
+    <row r="998" ht="15.75" customHeight="1" s="4"/>
+    <row r="999" ht="15.75" customHeight="1" s="4"/>
+    <row r="1000" ht="15.75" customHeight="1" s="4"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
--- a/Legacy_Submitter_Outreach_Tracker.xlsx
+++ b/Legacy_Submitter_Outreach_Tracker.xlsx
@@ -14,8 +14,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -68,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -81,6 +82,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,12 +524,18 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="n">
+        <v>46244</v>
+      </c>
       <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>CORRECTED 2026-09-03: tracker wrongly showed Not yet contacted — actually emailed Mon Aug 10, 2026 3:00 PM (generic legacy template, old hello@savethehives.org signature). Discovered when a duplicate send was scheduled for today; that duplicate was cancelled. IMPORTANT CONTEXT: Falco has a real prior relationship with Ronnie from Mar 2015 — he is/was president of the Haarlem Beekeepers Association (Netherlands, blog ImkerijHaarlem.nl) and wanted to onboard his whole association onto the registration system. Ronnie replied enthusiastically at the time. A personalized follow-up (not the generic template) referencing this history is being drafted separately — do not send the generic template to Falco again.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1726,14 +1736,16 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>46248</v>
+      </c>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent.</t>
+          <t>CORRECTED 2026-09-03: tracker wrongly showed Not yet contacted — actually emailed Fri Aug 14, 2026 ~9:39 AM (generic legacy template), no reply yet. Discovered during pre-send duplicate check; pulled from today's batch to avoid re-sending the same email. No known special history — fine to fold into a later, differently-worded follow-up round rather than urgent personalized outreach.</t>
         </is>
       </c>
     </row>
@@ -2225,14 +2237,16 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>46248</v>
+      </c>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Draft created in Gmail 2026-08-11 (trimmed template, no [PERSONAL NOTE], all hive links included), not yet sent.</t>
+          <t>CORRECTED 2026-09-03: tracker wrongly showed Not yet contacted — actually emailed Fri Aug 14, 2026 1:00 PM (generic legacy template), no reply yet. Discovered during pre-send duplicate check; pulled from today's batch to avoid re-sending the same email. No known special history — fine to fold into a later, differently-worded follow-up round rather than urgent personalized outreach.</t>
         </is>
       </c>
     </row>
@@ -2367,10 +2381,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n"/>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
     </row>
@@ -2440,10 +2456,12 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
@@ -2517,10 +2535,12 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
     </row>
@@ -2586,10 +2606,12 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
     </row>
@@ -2647,10 +2669,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
     </row>
@@ -2720,10 +2744,12 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
@@ -2797,10 +2823,12 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
     </row>
@@ -2858,10 +2886,12 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
     </row>
@@ -2931,10 +2961,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
     </row>
@@ -2992,10 +3024,12 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
     </row>
@@ -3053,10 +3087,12 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n"/>
     </row>
@@ -3126,10 +3162,12 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="n"/>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
@@ -3203,10 +3241,12 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
     </row>
@@ -3276,10 +3316,12 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n"/>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
@@ -3353,10 +3395,12 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
     </row>
@@ -3426,10 +3470,12 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n"/>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
@@ -3503,10 +3549,12 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
@@ -3580,10 +3628,12 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P44" s="2" t="n"/>
       <c r="Q44" s="2" t="n"/>
     </row>
@@ -3653,10 +3703,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="n"/>
     </row>
@@ -3726,10 +3778,12 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
     </row>
@@ -3787,10 +3841,12 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="n"/>
     </row>
@@ -3860,10 +3916,12 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P48" s="2" t="n"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
@@ -3990,10 +4048,12 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="n"/>
+          <t>Emailed - Bounced</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>46268</v>
+      </c>
       <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
@@ -4067,10 +4127,12 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
@@ -4144,10 +4206,12 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P52" s="2" t="n"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
@@ -4221,10 +4285,12 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P53" s="2" t="n"/>
       <c r="Q53" s="2" t="n"/>
     </row>
@@ -4282,10 +4348,12 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P54" s="2" t="n"/>
       <c r="Q54" s="2" t="n"/>
     </row>
@@ -4355,10 +4423,12 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P55" s="2" t="n"/>
       <c r="Q55" s="2" t="n"/>
     </row>
@@ -4428,10 +4498,12 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P56" s="2" t="n"/>
       <c r="Q56" s="2" t="n"/>
     </row>
@@ -4501,10 +4573,12 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P57" s="2" t="n"/>
       <c r="Q57" s="2" t="n"/>
     </row>
@@ -4574,10 +4648,12 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>46272</v>
+      </c>
       <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
@@ -4651,10 +4727,14 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
@@ -4716,10 +4796,14 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P60" s="2" t="n"/>
       <c r="Q60" s="2" t="n"/>
     </row>
@@ -4785,10 +4869,14 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P61" s="2" t="n"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
@@ -4862,10 +4950,14 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P62" s="2" t="n"/>
       <c r="Q62" s="2" t="n"/>
     </row>
@@ -4935,10 +5027,14 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P63" s="2" t="n"/>
       <c r="Q63" s="2" t="inlineStr">
         <is>
@@ -5012,10 +5108,14 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P64" s="2" t="n"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
@@ -5089,10 +5189,14 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="n"/>
     </row>
@@ -5162,10 +5266,14 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="n"/>
     </row>
@@ -5223,10 +5331,14 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="n"/>
     </row>
@@ -5296,10 +5408,14 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P68" s="2" t="n"/>
       <c r="Q68" s="2" t="n"/>
     </row>
@@ -5369,10 +5485,14 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
@@ -5446,10 +5566,14 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="n"/>
     </row>
@@ -5519,10 +5643,14 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="n"/>
     </row>
@@ -5592,10 +5720,14 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P72" s="2" t="n"/>
       <c r="Q72" s="2" t="n"/>
     </row>
@@ -5653,10 +5785,14 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="inlineStr">
         <is>
@@ -5718,10 +5854,14 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P74" s="2" t="n"/>
       <c r="Q74" s="2" t="n"/>
     </row>
@@ -5787,10 +5927,14 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P75" s="2" t="n"/>
       <c r="Q75" s="2" t="inlineStr">
         <is>
@@ -5864,10 +6008,14 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P76" s="2" t="n"/>
       <c r="Q76" s="2" t="inlineStr">
         <is>
@@ -5937,10 +6085,14 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="n"/>
     </row>
@@ -6010,10 +6162,14 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="n"/>
     </row>
@@ -6083,10 +6239,14 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="inlineStr">
         <is>
@@ -6160,10 +6320,14 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P80" s="2" t="n"/>
       <c r="Q80" s="2" t="inlineStr">
         <is>
@@ -6237,10 +6401,14 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="inlineStr">
         <is>
@@ -6302,10 +6470,14 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P82" s="2" t="n"/>
       <c r="Q82" s="2" t="n"/>
     </row>
@@ -6375,10 +6547,14 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P83" s="2" t="n"/>
       <c r="Q83" s="2" t="inlineStr">
         <is>
@@ -6440,10 +6616,14 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P84" s="2" t="n"/>
       <c r="Q84" s="2" t="n"/>
     </row>
@@ -6501,10 +6681,14 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="n"/>
     </row>
@@ -6562,10 +6746,14 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="n"/>
     </row>
@@ -6635,10 +6823,14 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="n"/>
     </row>
@@ -6696,10 +6888,14 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P88" s="2" t="n"/>
       <c r="Q88" s="2" t="n"/>
     </row>
@@ -6769,10 +6965,14 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O89" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P89" s="2" t="n"/>
       <c r="Q89" s="2" t="inlineStr">
         <is>
@@ -6846,10 +7046,14 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P90" s="2" t="n"/>
       <c r="Q90" s="2" t="inlineStr">
         <is>
@@ -6911,10 +7115,14 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P91" s="2" t="n"/>
       <c r="Q91" s="2" t="n"/>
     </row>
@@ -6972,10 +7180,14 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
     </row>
@@ -7045,10 +7257,14 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O93" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P93" s="2" t="n"/>
       <c r="Q93" s="2" t="n"/>
     </row>
@@ -7118,10 +7334,14 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="inlineStr">
         <is>
@@ -7195,10 +7415,14 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O95" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="inlineStr">
         <is>
@@ -7272,10 +7496,14 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="n"/>
     </row>
@@ -7333,10 +7561,14 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n"/>
     </row>
@@ -7463,10 +7695,14 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="2" t="n"/>
     </row>
@@ -7536,10 +7772,14 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P100" s="2" t="n"/>
       <c r="Q100" s="2" t="inlineStr">
         <is>
@@ -7613,10 +7853,14 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O101" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P101" s="2" t="n"/>
       <c r="Q101" s="2" t="n"/>
     </row>
@@ -7686,10 +7930,14 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P102" s="2" t="n"/>
       <c r="Q102" s="2" t="n"/>
     </row>
@@ -7747,10 +7995,14 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Not yet contacted</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="n"/>
+          <t>Emailed</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
     </row>
@@ -8799,7 +9051,7 @@
 Thanks for being part of this from early on,
 Ronnie Bouchon
 SaveTheHives — savethehives.org
-hello@savethehives.org</t>
+ronniebouchon@gmail.com</t>
         </is>
       </c>
     </row>
